--- a/Yesterday.xlsx
+++ b/Yesterday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H591"/>
+  <dimension ref="A1:H593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,22 +473,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1305153</t>
+          <t>1327099</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1305153</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327099</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACE Program | Spanish Talent Acquisition Specialist</t>
+          <t>ACE Program | French Accounts Receivable Specialist</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -515,22 +515,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1327099</t>
+          <t>1335242</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327099</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335242</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACE Program | French Accounts Receivable Specialist</t>
+          <t>ACE Program | Arabic Financial Analyst</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Thane, Maharashtra, India</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,22 +557,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1334767</t>
+          <t>1336389</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334767</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336389</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing Intern | Infosys Instep Program</t>
+          <t>[EXP NL] Growth Marketing Intern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56 applicants</t>
+          <t>87 applicants</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>DHL Group</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -683,22 +683,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1336433</t>
+          <t>1336439</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336433</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336439</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Corporate Industrial Engineering Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Joinville - Pirabeiraba, Joinville - SC, Brasil</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,39 +708,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nidec Global Appliance</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1336426</t>
+          <t>1336433</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336426</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336433</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>[Impact Brazil] - Corporate Industrial Engineering Intern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ahangama, Sri Lanka</t>
+          <t>Joinville - Pirabeiraba, Joinville - SC, Brasil</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,39 +750,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Surfing Wombats</t>
+          <t>Nidec Global Appliance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1336425</t>
+          <t>1336426</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336425</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336426</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sales and Marketing Manager</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Ahangama, Sri Lanka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -792,34 +792,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Weblook International Private Limited</t>
+          <t>Surfing Wombats</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1336424</t>
+          <t>1336425</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336424</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336425</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Business Development Manager</t>
+          <t>Sales and Marketing Manager</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -851,22 +851,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1336414</t>
+          <t>1336424</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336414</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336424</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CRM Assistant</t>
+          <t>Business Development Manager</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -886,29 +886,29 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamérica (Zona Libre) S.A (SELA)</t>
+          <t>Weblook International Private Limited</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1336404</t>
+          <t>1336414</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Performance &amp; Entertainment Intern</t>
+          <t>CRM Assistant</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -918,59 +918,59 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Starbeans Ceylon (Pvt ) Ltd</t>
+          <t>Samsung Electronics Latinoamérica (Zona Libre) S.A (SELA)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1336389</t>
+          <t>1336404</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336389</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[EXP NL] Growth Marketing Intern</t>
+          <t>Performance &amp; Entertainment Intern</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DHL Group</t>
+          <t>Starbeans Ceylon (Pvt ) Ltd</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2153,22 +2153,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1336151</t>
+          <t>1336148</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336148</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AI Internship</t>
+          <t>Renewable Energy Systems &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Dehradun, Uttarakhand, India</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Graphic era (Deemed to be university)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1336148</t>
+          <t>1336146</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336148</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336146</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Renewable Energy Systems &amp; Analytics Intern</t>
+          <t>Financial Analyst Intern</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2237,17 +2237,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1336146</t>
+          <t>1336145</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336146</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336145</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Financial Analyst Intern</t>
+          <t>Aerospace Engineering Intern</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2279,22 +2279,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1336145</t>
+          <t>1336142</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336145</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336142</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Intern</t>
+          <t>[Partly Remote] Executive Search Analyst</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Dehradun, Uttarakhand, India</t>
+          <t>Santiago de Chile, Región Metropolitana, Chile</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2304,39 +2304,39 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>Partly Remote</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Graphic era (Deemed to be university)</t>
+          <t>KOVACIC EXECUTIVE TALENT RESEARCH SPA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1336142</t>
+          <t>1336136</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336142</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336136</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[Partly Remote] Executive Search Analyst</t>
+          <t>Graphic design</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Santiago de Chile, Región Metropolitana, Chile</t>
+          <t>El Sheikh Zayed City, Giza Governorate, Egypt</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2346,34 +2346,34 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Partly Remote</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KOVACIC EXECUTIVE TALENT RESEARCH SPA</t>
+          <t>Correct Real Estate</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1336136</t>
+          <t>1336134</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336136</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336134</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Graphic design</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2405,106 +2405,106 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1336134</t>
+          <t>1336129</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336134</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336129</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>[EXP] Post Opportunity Review Analyst</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>El Sheikh Zayed City, Giza Governorate, Egypt</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>138 applicants</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Correct Real Estate</t>
+          <t>DHL Group</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1336129</t>
+          <t>1336126</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336129</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336126</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[EXP] Post Opportunity Review Analyst</t>
+          <t>Accelerate Romania - Strategic Development Assistant</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>133 applicants</t>
+          <t>32 applicants</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DHL Group</t>
+          <t>Meteo Control</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1336126</t>
+          <t>1336121</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336126</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336121</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Strategic Development Assistant</t>
+          <t>Economics Research Intern</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Sohna, Haryana 122103, India</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>31 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2524,24 +2524,24 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Meteo Control</t>
+          <t>K.R. Mangalam University</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1336121</t>
+          <t>1336119</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336121</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336119</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Economics Research Intern</t>
+          <t>Game Design Research Intern</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2573,17 +2573,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1336119</t>
+          <t>1336118</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336119</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336118</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Game Design Research Intern</t>
+          <t>Forensic Science Research Intern</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2615,17 +2615,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1336118</t>
+          <t>1336117</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336118</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336117</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Forensic Science Research Intern</t>
+          <t>UI/UX Research Intern</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2657,17 +2657,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1336117</t>
+          <t>1336116</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336117</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336116</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UI/UX Research Intern</t>
+          <t>Hotel Management Research Intern</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2699,17 +2699,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1336116</t>
+          <t>1336115</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336116</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336115</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hotel Management Research Intern</t>
+          <t>Law Research Intern</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2741,17 +2741,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1336115</t>
+          <t>1336114</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336115</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336114</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Law Research Intern</t>
+          <t>Pharmacy Research Intern</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2783,17 +2783,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1336114</t>
+          <t>1336113</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336114</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336113</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pharmacy Research Intern</t>
+          <t>International Accounting Research Intern</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2825,17 +2825,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1336113</t>
+          <t>1336112</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336113</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336112</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>International Accounting Research Intern</t>
+          <t>Business Administration Research Intern</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2867,17 +2867,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1336112</t>
+          <t>1336111</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336112</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336111</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Business Administration Research Intern</t>
+          <t>Computer Science Engineering Research Intern</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2909,17 +2909,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1336111</t>
+          <t>1336110</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336111</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336110</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Computer Science Engineering Research Intern</t>
+          <t>Human Resource Research Intern</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2951,17 +2951,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1336110</t>
+          <t>1336109</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336110</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336109</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Human Resource Research Intern</t>
+          <t>Data Science Research Intern</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1336109</t>
+          <t>1336108</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336109</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Data Science Research Intern</t>
+          <t>Full Stack Development Research Intern</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3035,17 +3035,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1336108</t>
+          <t>1336107</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336107</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Full Stack Development Research Intern</t>
+          <t>Cyber Security Research Intern</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3077,17 +3077,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1336107</t>
+          <t>1336106</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336107</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336106</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cyber Security Research Intern</t>
+          <t>Artificial Intelligence Research Intern</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1336106</t>
+          <t>1336104</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336106</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336104</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Research Intern</t>
+          <t>Finance Research Intern</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3161,22 +3161,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1336104</t>
+          <t>1336079</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336104</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336079</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Finance Research Intern</t>
+          <t>Brand Partner</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sohna, Haryana 122103, India</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3186,34 +3186,34 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>K.R. Mangalam University</t>
+          <t>Rediffusion Brand Solutions Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1336079</t>
+          <t>1336078</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336079</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336078</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brand Partner</t>
+          <t>Design Intern</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3245,22 +3245,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1336078</t>
+          <t>1336076</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336078</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336076</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Design Intern</t>
+          <t>Medical Information Solutions Trainee</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Bruxelles, Belgio</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3270,39 +3270,39 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Rediffusion Brand Solutions Pvt Ltd</t>
+          <t>UCB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1336076</t>
+          <t>1336054</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336076</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336054</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Medical Information Solutions Trainee</t>
+          <t>C# Developer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bruxelles, Belgio</t>
+          <t>Alexandria, Alexandria Governorate, Egypt</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3312,39 +3312,39 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>DotNet</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1336054</t>
+          <t>1336047</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336054</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336047</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>C# Developer</t>
+          <t>Customer Service</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Alexandria, Alexandria Governorate, Egypt</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3364,24 +3364,24 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>DotNet</t>
+          <t>NOYO For Cosmetics</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1336047</t>
+          <t>1336045</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336047</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336045</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Motion Graphics Designer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3413,17 +3413,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1336045</t>
+          <t>1336043</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336045</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336043</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Motion Graphics Designer</t>
+          <t>Digital Marketing &amp; Media Buying Specialist</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3455,22 +3455,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1336043</t>
+          <t>1336041</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336043</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336041</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Media Buying Specialist</t>
+          <t>Administrative, Marketing &amp; E-Marketing (Fairs, Events &amp;  Customer Follow-up)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3480,34 +3480,34 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>NOYO For Cosmetics</t>
+          <t>NAGEH ENGINEERING CO.- LLC شركة ناجح الهندسية</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1336041</t>
+          <t>1336040</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336041</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336040</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Administrative, Marketing &amp; E-Marketing (Fairs, Events &amp;  Customer Follow-up)</t>
+          <t>Aviation Engineer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3539,22 +3539,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1336040</t>
+          <t>1336013</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336040</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336013</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Aviation Engineer</t>
+          <t>Front Office Executive</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Weligama, Sri Lanka</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3564,39 +3564,39 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NAGEH ENGINEERING CO.- LLC شركة ناجح الهندسية</t>
+          <t>Weligama Cliff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1336013</t>
+          <t>1336010</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336013</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336010</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Front Office Executive</t>
+          <t>Marketing Analyst Intern</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Weligama, Sri Lanka</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>59 applicants</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Weligama Cliff</t>
+          <t>Sanfer Panama</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1336010</t>
+          <t>1336007</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336010</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336007</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Marketing Analyst Intern</t>
+          <t>graphic design</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3648,39 +3648,39 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>57 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sanfer Panama</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1336007</t>
+          <t>1336006</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336007</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336006</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>graphic design</t>
+          <t>ESG &amp; Sustainability Track</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1336006</t>
+          <t>1336005</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336006</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ESG &amp; Sustainability Track</t>
+          <t>HR Track</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3749,17 +3749,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1336005</t>
+          <t>1336004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336005</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336004</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HR Track</t>
+          <t>Marketing &amp; Brand Track</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3791,17 +3791,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1336004</t>
+          <t>1336003</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336004</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336003</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand Track</t>
+          <t>Rural Immersion Track</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1336003</t>
+          <t>1336002</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336003</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336002</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rural Immersion Track</t>
+          <t>Retail Strategy Track</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3875,17 +3875,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1336002</t>
+          <t>1336001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336002</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336001</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Retail Strategy Track</t>
+          <t>Product Track – Digital &amp; Banking Products</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3917,17 +3917,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1336001</t>
+          <t>1336000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336001</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336000</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Product Track – Digital &amp; Banking Products</t>
+          <t>Technology Track – AI, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3959,22 +3959,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1336000</t>
+          <t>1335994</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336000</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335994</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Technology Track – AI, Data &amp; Analytics</t>
+          <t>Business developement</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3994,29 +3994,29 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1335994</t>
+          <t>1335970</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335994</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335970</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Business developement</t>
+          <t>HVAC &amp; Mechanical Systems Intern</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Dehradun, Uttarakhand, India</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4036,24 +4036,24 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>Graphic era (Deemed to be university)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1335970</t>
+          <t>1335969</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335970</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335969</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HVAC &amp; Mechanical Systems Intern</t>
+          <t>Mobile development Intern</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4085,17 +4085,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1335969</t>
+          <t>1335968</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335969</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335968</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mobile development Intern</t>
+          <t>Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4127,22 +4127,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1335968</t>
+          <t>1335952</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335968</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335952</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dehradun, Uttarakhand, India</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4152,39 +4152,39 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Graphic era (Deemed to be university)</t>
+          <t>Automation Genie</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1335952</t>
+          <t>1335943</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335952</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335943</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Social Media Specialist</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4194,34 +4194,34 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Automation Genie</t>
+          <t>Akhtaboot Advertising</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1335943</t>
+          <t>1335942</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335943</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335942</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Social Media Specialist</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4253,22 +4253,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1335942</t>
+          <t>1335929</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335942</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335929</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4278,39 +4278,39 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Akhtaboot Advertising</t>
+          <t>NOYO For Cosmetics</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1335929</t>
+          <t>1335925</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335929</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335925</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Digital Business &amp; Technology Intern</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Surat, Gujarat, India</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4320,39 +4320,39 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>NOYO For Cosmetics</t>
+          <t>AlignSoul Connect Pvt. Ltd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1335925</t>
+          <t>1335911</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335925</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335911</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Digital Business &amp; Technology Intern</t>
+          <t>Guest Relations and Service Captain</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Surat, Gujarat, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4362,39 +4362,39 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>AlignSoul Connect Pvt. Ltd</t>
+          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1335911</t>
+          <t>1335880</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335911</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335880</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Guest Relations and Service Captain</t>
+          <t>Accelerate Romania - Community Manager</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4404,17 +4404,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
+          <t>EdTech Cluj</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>128 applicants</t>
+          <t>133 applicants</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>79 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>51 applicants</t>
+          <t>52 applicants</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>76 applicants</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7235,32 +7235,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1335242</t>
+          <t>1335237</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335237</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ACE Program | Arabic Financial Analyst</t>
+          <t>IT Field Service Assistance</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Thane, Maharashtra, India</t>
+          <t>Panama City, Panamá Province, Panama</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>93 applicants</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7270,29 +7270,29 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>NESTRADE S.A, PANAMA BRANCH</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1335237</t>
+          <t>1335231</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335237</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335231</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IT Field Service Assistance</t>
+          <t>Accelerate Romania|Drone Software Development Intern</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Panama City, Panamá Province, Panama</t>
+          <t>Timișoara, România</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7302,34 +7302,34 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>91 applicants</t>
+          <t>64 applicants</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>NESTRADE S.A, PANAMA BRANCH</t>
+          <t>Crystal Matrix Design SRL</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1335231</t>
+          <t>1335230</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335231</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335230</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Accelerate Romania|Drone Software Development Intern</t>
+          <t>Accelerate Romania|Drone Hardware Development Intern</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>63 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7354,29 +7354,29 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Crystal Matrix Design SRL</t>
+          <t>Crystal Matrix SRL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1335230</t>
+          <t>1335188</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335230</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335188</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Accelerate Romania|Drone Hardware Development Intern</t>
+          <t>Business Developer (German speaking)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Timișoara, România</t>
+          <t>Groningen, Nederland</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7386,39 +7386,39 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Crystal Matrix SRL</t>
+          <t>Trayler B.V.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1335188</t>
+          <t>1335187</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335188</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335187</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Business Developer (German speaking)</t>
+          <t>digital Marketing</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Groningen, Nederland</t>
+          <t>Lac De Tunis, Tunisie</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7428,39 +7428,39 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Trayler B.V.</t>
+          <t>EDUWORLD</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1335187</t>
+          <t>1335180</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335187</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335180</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>digital Marketing</t>
+          <t>AI Motion Designer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Lac De Tunis, Tunisie</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7470,34 +7470,34 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>EDUWORLD</t>
+          <t>Snakup content</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1335180</t>
+          <t>1335179</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335180</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335179</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AI Motion Designer</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7529,17 +7529,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1335179</t>
+          <t>1335178</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335179</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335178</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Content Creator</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7571,17 +7571,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1335178</t>
+          <t>1335177</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335178</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335177</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Content Creator</t>
+          <t>Cultural Events &amp; Space Coordinator</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Snakup content</t>
+          <t>JAM Music Academy</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1335177</t>
+          <t>1335129</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335177</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335129</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cultural Events &amp; Space Coordinator</t>
+          <t>social media associate</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7648,24 +7648,24 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>JAM Music Academy</t>
+          <t>Insight Canadian Business Development</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1335129</t>
+          <t>1335125</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335129</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335125</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>social media associate</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7697,22 +7697,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1335125</t>
+          <t>1335097</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335125</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335097</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Interior architect</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Sousse, Tunisie</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7732,29 +7732,29 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Insight Canadian Business Development</t>
+          <t>NGA Architecture</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1335097</t>
+          <t>1335092</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335097</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335092</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Interior architect</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Sousse, Tunisie</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>68 applicants</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7774,24 +7774,24 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>NGA Architecture</t>
+          <t>Reach Technologies Operations Europe Single Member P.C.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1335092</t>
+          <t>1335091</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335092</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335091</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>67 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7823,22 +7823,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1335091</t>
+          <t>1335084</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335091</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335084</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Athens, Greece</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7858,29 +7858,29 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Reach Technologies Operations Europe Single Member P.C.</t>
+          <t>JWframe Networks</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1335084</t>
+          <t>1335082</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335084</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335082</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Admissions Agent</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7900,24 +7900,24 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>JWframe Networks</t>
+          <t>iteam</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1335082</t>
+          <t>1335081</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335082</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335081</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Admissions Agent</t>
+          <t>marketing Agent</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7949,17 +7949,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1335081</t>
+          <t>1335080</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335081</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335080</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>marketing Agent</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7991,22 +7991,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1335080</t>
+          <t>1335061</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335080</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335061</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Cybersecurity Intern</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -8026,29 +8026,29 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>iteam</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1335061</t>
+          <t>1335060</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335061</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335060</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cybersecurity Intern</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Ariana, Tunisie</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>lab916</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1335060</t>
+          <t>1335044</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335060</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335044</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Marketing and Strategy Intern</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Ariana, Tunisie</t>
+          <t>Mayur Vihar, Delhi, India</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8100,39 +8100,39 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>lab916</t>
+          <t>Credifin Limited</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1335044</t>
+          <t>1334993</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335044</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334993</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Marketing and Strategy Intern</t>
+          <t>EXPORT MANAGER ASSISTANT</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Mayur Vihar, Delhi, India</t>
+          <t>İzmir, Türkiye</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8142,39 +8142,39 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>73 applicants</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Credifin Limited</t>
+          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1334993</t>
+          <t>1334972</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334993</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334972</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>EXPORT MANAGER ASSISTANT</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>İzmir, Türkiye</t>
+          <t>Tunis, Tunisie</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8184,39 +8184,39 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
+          <t>Declitech</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1334972</t>
+          <t>1334962</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334972</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334962</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Content Creator</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Tunis, Tunisie</t>
+          <t>Ad Doqi, Dokki, Giza Governorate, Egypt</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8226,34 +8226,34 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Declitech</t>
+          <t>Nuit Fragrances</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1334962</t>
+          <t>1334961</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334962</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334961</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Content Creator</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -8285,12 +8285,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1334961</t>
+          <t>1334959</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334961</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334959</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Ad Doqi, Dokki, Giza Governorate, Egypt</t>
+          <t>Giza, El Omraniya, Giza Governorate, Egypt</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8320,29 +8320,29 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Nuit Fragrances</t>
+          <t>EA2 Communication</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1334959</t>
+          <t>1334943</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334959</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334943</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Video Editor</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Giza, El Omraniya, Giza Governorate, Egypt</t>
+          <t>Gabes, Tunisia</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>EA2 Communication</t>
+          <t>Studio Seberna</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1334943</t>
+          <t>1334906</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334943</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334906</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Multimedia Designer (Graphics, Video &amp; AI Content Creation)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Gabes, Tunisia</t>
+          <t>Visakhapatnam, Andhra Pradesh, India</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -8394,39 +8394,39 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Studio Seberna</t>
+          <t>PROJECT SALES CORPORATION,Vizag</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1334906</t>
+          <t>1334900</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334906</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334900</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Multimedia Designer (Graphics, Video &amp; AI Content Creation)</t>
+          <t>Medical Affairs Operations Trainee</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Visakhapatnam, Andhra Pradesh, India</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8436,39 +8436,39 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>59 applicants</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>PROJECT SALES CORPORATION,Vizag</t>
+          <t>UCB</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1334900</t>
+          <t>1334876</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334900</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334876</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Medical Affairs Operations Trainee</t>
+          <t>Marketing Coordinator- Mid term</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
+          <t>Kolkata, West Bengal, India</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8478,39 +8478,39 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>59 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>Crizac Limited</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1334876</t>
+          <t>1334874</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334876</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334874</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Marketing Coordinator- Mid term</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal, India</t>
+          <t>Gampola, Sri Lanka</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8520,39 +8520,39 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Crizac Limited</t>
+          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1334874</t>
+          <t>1334872</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334874</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334872</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Language Specialist - Spanish &amp; Portuguese</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Gampola, Sri Lanka</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8562,39 +8562,39 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
+          <t>Aitken Spence Travels (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1334872</t>
+          <t>1334852</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334872</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334852</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Language Specialist - Spanish &amp; Portuguese</t>
+          <t>International Relations Coordinator</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Kolkata, West Bengal, India</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -8604,39 +8604,39 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Aitken Spence Travels (Pvt) Ltd</t>
+          <t>Euroasia Minmet Corp.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1334852</t>
+          <t>1334846</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334852</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334846</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>International Relations Coordinator</t>
+          <t>Social media manager</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal, India</t>
+          <t>Gabès, Tunisie</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -8646,39 +8646,39 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Euroasia Minmet Corp.</t>
+          <t>iParadise Training Center</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1334846</t>
+          <t>1334791</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334846</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334791</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Social media manager</t>
+          <t>Information Technology Intern</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Gabès, Tunisie</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8698,49 +8698,49 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>iParadise Training Center</t>
+          <t>SKIPS University</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1334791</t>
+          <t>1334767</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1334791</t>
+          <t>https://aiesec.org/opportunity/global-talent/1334767</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Information Technology Intern</t>
+          <t>Marketing Intern | Infosys Instep Program</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>57 applicants</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>SKIPS University</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>108 applicants</t>
+          <t>109 applicants</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>78 applicants</t>
+          <t>81 applicants</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>159 applicants</t>
+          <t>162 applicants</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>62 applicants</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>89 applicants</t>
+          <t>90 applicants</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -13955,22 +13955,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1332999</t>
+          <t>1332990</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332999</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332990</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Software developer</t>
+          <t>Sales and Produciton Planning</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Porto, Portugal</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -13980,39 +13980,39 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>105 applicants</t>
+          <t>67 applicants</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Ciberbit</t>
+          <t>METAL MARKET DIŞ TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1332990</t>
+          <t>1332988</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332990</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332988</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Sales and Produciton Planning</t>
+          <t>AI Agent Experience Specialist</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>66 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -14032,29 +14032,29 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>METAL MARKET DIŞ TİCARET ANONİM ŞİRKETİ</t>
+          <t>TERICSOFT TECHNOLOGY SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1332988</t>
+          <t>1332980</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332988</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332980</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>AI Agent Experience Specialist</t>
+          <t>Sales and Produciton Planning</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -14074,29 +14074,29 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>TERICSOFT TECHNOLOGY SOLUTIONS PVT. LTD.</t>
+          <t>METAL MARKET DIŞ TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1332980</t>
+          <t>1332970</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332980</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332970</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Sales and Produciton Planning</t>
+          <t>Biotech Research Intern</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Aronj, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -14106,39 +14106,39 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>METAL MARKET DIŞ TİCARET ANONİM ŞİRKETİ</t>
+          <t>FS University</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1332970</t>
+          <t>1332958</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332970</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332958</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biotech Research Intern</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Aronj, Uttar Pradesh, India</t>
+          <t>Hyderabad, India</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -14148,39 +14148,39 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>FS University</t>
+          <t>TERICSOFT TECHNOLOGY SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1332958</t>
+          <t>1332957</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332958</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332957</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Interior Design</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Hyderabad, India</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -14200,29 +14200,29 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>TERICSOFT TECHNOLOGY SOLUTIONS PVT. LTD.</t>
+          <t>Defactory</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1332957</t>
+          <t>1332931</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332957</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332931</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Interior Design</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -14242,29 +14242,29 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Defactory</t>
+          <t>TERICSOFT TECHNOLOGY SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1332931</t>
+          <t>1332888</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332931</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332888</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>Bio technology Intern</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -14274,39 +14274,39 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>TERICSOFT TECHNOLOGY SOLUTIONS PVT. LTD.</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1332888</t>
+          <t>1332880</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332888</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332880</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Bio technology Intern</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>Gampola, Sri Lanka</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -14316,39 +14316,39 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1332880</t>
+          <t>1332865</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332880</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332865</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Product Intern</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Gampola, Sri Lanka</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -14358,34 +14358,34 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
+          <t>Socomo Technologies Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1332865</t>
+          <t>1332853</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332865</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332853</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Product Intern</t>
+          <t>Design Intern</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -14417,22 +14417,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1332853</t>
+          <t>1332851</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332851</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Design Intern</t>
+          <t>Front Office Executive</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Ella, Sri Lanka</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -14442,39 +14442,39 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>31 applicants</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Socomo Technologies Pvt Ltd</t>
+          <t>Area 4 Eco Cubes - Ella</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1332851</t>
+          <t>1332832</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332851</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332832</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Front Office Executive</t>
+          <t>Accelerate Romania - [Romanian Only] Media Marketing</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Ella, Sri Lanka</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -14484,39 +14484,39 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>31 applicants</t>
+          <t>32 applicants</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Area 4 Eco Cubes - Ella</t>
+          <t>Arta 360</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1332832</t>
+          <t>1332818</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332832</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332818</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Accelerate Romania - [Romanian Only] Media Marketing</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -14526,39 +14526,39 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Arta 360</t>
+          <t>Socomo Technologies Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1332818</t>
+          <t>1332703</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332818</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332703</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Sales Represantive</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>104 applicants</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -14578,29 +14578,29 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Socomo Technologies Pvt Ltd</t>
+          <t>KLT ENERJİ MÜHENDİSLİK</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1332703</t>
+          <t>1332698</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332703</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332698</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Sales Represantive</t>
+          <t>Accelerate Romania - IT Networking</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -14610,39 +14610,39 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>104 applicants</t>
+          <t>54 applicants</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>KLT ENERJİ MÜHENDİSLİK</t>
+          <t>Aldi Suport</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1332698</t>
+          <t>1332687</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332698</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332687</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Accelerate Romania - IT Networking</t>
+          <t>Interpreter</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Pamukkale, 20190 Pamukkale/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -14662,29 +14662,29 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Aldi Suport</t>
+          <t>KRAFT KİMYA SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1332687</t>
+          <t>1332659</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332687</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332659</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Interpreter</t>
+          <t>DIGITAL LEARNING ARCHITECT</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Pamukkale, 20190 Pamukkale/Denizli, Türkiye</t>
+          <t>Abidjan, Côte d'Ivoire</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -14704,29 +14704,29 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>KRAFT KİMYA SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
+          <t>AS Consulting</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1332659</t>
+          <t>1332574</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332659</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332574</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>DIGITAL LEARNING ARCHITECT</t>
+          <t>Accelerate Serbia | Business development intern</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Abidjan, Côte d'Ivoire</t>
+          <t>Kladovo, Serbia</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -14746,29 +14746,29 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>AS Consulting</t>
+          <t>Djerdap Turist, Kladovo</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1332574</t>
+          <t>1332567</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332574</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332567</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Accelerate Serbia | Business development intern</t>
+          <t>Dutch-Speaking Customer Service Representative</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Kladovo, Serbia</t>
+          <t>Lisboa, Portugal</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -14778,39 +14778,39 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Djerdap Turist, Kladovo</t>
+          <t>Teleperformance Portugal</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1332567</t>
+          <t>1332558</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332567</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332558</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Dutch-Speaking Customer Service Representative</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Lisboa, Portugal</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>51 applicants</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -14830,29 +14830,29 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Teleperformance Portugal</t>
+          <t>Özçağrı Paslanmaz</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1332558</t>
+          <t>1332534</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332558</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332534</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>Corporate Branding Specialist</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Kafr El-Shaikh, Qism Kafr El-Shaikh, Kafr el-Sheikh, Gharbia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -14862,39 +14862,39 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>50 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Özçağrı Paslanmaz</t>
+          <t>SYNAPSE SOLUTIONS</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1332534</t>
+          <t>1332497</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332534</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332497</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Corporate Branding Specialist</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Kafr El-Shaikh, Qism Kafr El-Shaikh, Kafr el-Sheikh, Gharbia Governorate, Egypt</t>
+          <t>El Sheikh Zayed City, Giza Governorate, Egypt</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -14914,24 +14914,24 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>SYNAPSE SOLUTIONS</t>
+          <t>Media Nations</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1332497</t>
+          <t>1332496</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332497</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332496</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -14963,22 +14963,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1332496</t>
+          <t>1332455</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332496</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332455</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>El Sheikh Zayed City, Giza Governorate, Egypt</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -14988,39 +14988,39 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Media Nations</t>
+          <t>ÇIRALI TEKSTİL İNŞAAT MÜHENDİSLİK VE MİMARLIK LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1332455</t>
+          <t>1332443</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332455</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332443</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Digital Marketer</t>
+          <t>Intern – Marketing</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -15030,39 +15030,39 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>50 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>ÇIRALI TEKSTİL İNŞAAT MÜHENDİSLİK VE MİMARLIK LİMİTED ŞİRKETİ</t>
+          <t>ESOL College Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1332443</t>
+          <t>1332442</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332443</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332442</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Intern – Marketing</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Honaz, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -15072,39 +15072,39 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>ESOL College Pvt Ltd</t>
+          <t>PAMUKKALE KURUYEMİŞ MAKİNALARI SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1332442</t>
+          <t>1332411</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332442</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332411</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Honaz, Denizli, Türkiye</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -15114,34 +15114,34 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>PAMUKKALE KURUYEMİŞ MAKİNALARI SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Infinitum Network Solutions</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1332411</t>
+          <t>1332409</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332411</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332409</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Youtube Manager</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -15173,17 +15173,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1332409</t>
+          <t>1332408</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332409</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332408</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Youtube Manager</t>
+          <t>Content Writer</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -15215,17 +15215,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1332408</t>
+          <t>1332407</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332408</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332407</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Content Writer</t>
+          <t>Content Creator</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -15257,17 +15257,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1332407</t>
+          <t>1332403</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332407</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332403</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Content Creator</t>
+          <t>Actor</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -15299,22 +15299,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1332403</t>
+          <t>1332393</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332403</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332393</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Actor</t>
+          <t>Technology and Artificial Intelligence Manager</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>La Paz, Bolivia</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -15324,39 +15324,39 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>52 applicants</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Infinitum Network Solutions</t>
+          <t>Jawitas</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1332393</t>
+          <t>1332307</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332393</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332307</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Technology and Artificial Intelligence Manager</t>
+          <t>Front Office Assistant</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>La Paz, Bolivia</t>
+          <t>Sigiriya, Sri Lanka</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>50 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -15376,29 +15376,29 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Jawitas</t>
+          <t>Atha Resort Sigiriya</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1332307</t>
+          <t>1332227</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332307</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332227</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Front Office Assistant</t>
+          <t>CRM Manager</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Sigiriya, Sri Lanka</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -15408,34 +15408,34 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Atha Resort Sigiriya</t>
+          <t>The Circle Care</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1332227</t>
+          <t>1332181</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332227</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332181</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>CRM Manager</t>
+          <t>Social media specialist</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -15467,12 +15467,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1332181</t>
+          <t>1332179</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332181</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332179</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -15509,17 +15509,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1332179</t>
+          <t>1332177</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332179</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332177</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Social media specialist</t>
+          <t>SEO content creator &amp; google analytics</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -15551,17 +15551,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1332177</t>
+          <t>1332167</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332177</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332167</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>SEO content creator &amp; google analytics</t>
+          <t>Site / Civil Engineer</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -15586,29 +15586,29 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>The Circle Care</t>
+          <t>Phomi</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1332167</t>
+          <t>1332153</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332167</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332153</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Site / Civil Engineer</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>El Sadat City, Menofia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -15628,29 +15628,29 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Phomi</t>
+          <t>Habib Agency</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1332153</t>
+          <t>1332094</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332153</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332094</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Technical Support Engineer - ERP Software</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>El Sadat City, Menofia Governorate, Egypt</t>
+          <t>Bucharest, Romania</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>109 applicants</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -15670,29 +15670,29 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Habib Agency</t>
+          <t>Lundin</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1332094</t>
+          <t>1332032</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332094</t>
+          <t>https://aiesec.org/opportunity/global-talent/1332032</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Technical Support Engineer - ERP Software</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Bucharest, Romania</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -15702,39 +15702,39 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>108 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Lundin</t>
+          <t>Boğaziçi İhtisas Fuarcılık Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1332032</t>
+          <t>1331989</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1332032</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331989</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Guest Relations Officer</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Mirissa, Sri Lanka</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>84 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -15754,24 +15754,24 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Boğaziçi İhtisas Fuarcılık Limited Şirketi</t>
+          <t>The Loft Mirissa</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1331989</t>
+          <t>1331988</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331989</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331988</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Guest Relations Officer</t>
+          <t>Bartenders - Rooftop Bar</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -15786,12 +15786,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -15803,22 +15803,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1331988</t>
+          <t>1331964</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331988</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331964</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Bartenders - Rooftop Bar</t>
+          <t>Research &amp; Business Development Intern</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Mirissa, Sri Lanka</t>
+          <t>South Jakarta, South Jakarta City, Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>The Loft Mirissa</t>
+          <t>BOI Research Services</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>63 applicants</t>
+          <t>64 applicants</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>81 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>60 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>97 applicants</t>
+          <t>100 applicants</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>84 applicants</t>
+          <t>85 applicants</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>323 applicants</t>
+          <t>326 applicants</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>114 applicants</t>
+          <t>115 applicants</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>90 applicants</t>
+          <t>92 applicants</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>104 applicants</t>
+          <t>106 applicants</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>262 applicants</t>
+          <t>265 applicants</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>165 applicants</t>
+          <t>166 applicants</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>58 applicants</t>
+          <t>59 applicants</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>120 applicants</t>
+          <t>121 applicants</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -23111,22 +23111,22 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1322997</t>
+          <t>1323315</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322997</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323315</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales Specialist in Supply Chain</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Sfax, Tunisie</t>
+          <t>Samsun, Türkiye</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
@@ -23146,29 +23146,29 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>English Cultural Center</t>
+          <t>Yavuzlar Toptan Gıda İthalat İhracat Sanayi ve Ticaret Limit</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>1322891</t>
+          <t>1322997</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322891</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322997</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Jaipur, Rajasthan, India</t>
+          <t>Sfax, Tunisie</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -23188,29 +23188,29 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>EGNK HOME AND DESIGNS</t>
+          <t>English Cultural Center</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>1322716</t>
+          <t>1322891</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322716</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322891</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Eindhoven, Nederland</t>
+          <t>Jaipur, Rajasthan, India</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -23220,39 +23220,39 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>545 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>F19 Digital Reporting</t>
+          <t>EGNK HOME AND DESIGNS</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1322494</t>
+          <t>1322716</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322494</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322716</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Biotechnology Intern</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Eindhoven, Nederland</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -23262,34 +23262,34 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>547 applicants</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>F19 Digital Reporting</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>1322346</t>
+          <t>1322494</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322346</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322494</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Cyber Security and AI Intern</t>
+          <t>Biotechnology Intern</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -23304,12 +23304,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>63 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -23321,22 +23321,22 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>1322224</t>
+          <t>1322346</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322224</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322346</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Technical Support Sales Specialist</t>
+          <t>Cyber Security and AI Intern</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Pendik, Kaynarca, 34890 Pendik/İstanbul, Türkiye</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -23346,39 +23346,39 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>97 applicants</t>
+          <t>63 applicants</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>AYBEY ELEKTRONİK SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>1321910</t>
+          <t>1322224</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321910</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322224</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Technical Support Sales Specialist</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Pendik, Kaynarca, 34890 Pendik/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>162 applicants</t>
+          <t>97 applicants</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -23398,29 +23398,29 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Eman Agro Gıda</t>
+          <t>AYBEY ELEKTRONİK SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1321872</t>
+          <t>1321910</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321872</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321910</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Mechanical Computer Science and Electronics Engineering</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -23430,39 +23430,39 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>162 applicants</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Eman Agro Gıda</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>1321796</t>
+          <t>1321872</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321796</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321872</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>MARKET RESARCH &amp; MARKETİNG | ŞAHİNLER MARBLE</t>
+          <t>Mechanical Computer Science and Electronics Engineering</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -23472,39 +23472,39 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>ŞAHİNLER MARBLE</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>1321497</t>
+          <t>1321796</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321497</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321796</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Sales  Specialist</t>
+          <t>MARKET RESARCH &amp; MARKETİNG | ŞAHİNLER MARBLE</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Kartepe, Kocaeli, Türkiye</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>92 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -23524,29 +23524,29 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Dessa Teknoloji Sanayi Ticaret Limited Şirketi</t>
+          <t>ŞAHİNLER MARBLE</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1321450</t>
+          <t>1321497</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321450</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321497</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Sales and Business Development Intern</t>
+          <t>Sales  Specialist</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Jaipur, Rajasthan, India</t>
+          <t>Kartepe, Kocaeli, Türkiye</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -23556,39 +23556,39 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>92 applicants</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>www.Besteduonline.in (IPS Education &amp; Learning)</t>
+          <t>Dessa Teknoloji Sanayi Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>1321215</t>
+          <t>1321450</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321215</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321450</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Business Management and Analytics Intern</t>
+          <t>Sales and Business Development Intern</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Jaipur, Rajasthan, India</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>54 applicants</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -23608,29 +23608,29 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>www.Besteduonline.in (IPS Education &amp; Learning)</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>1321055</t>
+          <t>1321215</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321055</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321215</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>International Sales Representetive Italian Speaker</t>
+          <t>Business Management and Analytics Intern</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -23640,34 +23640,34 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Esvita Clinic</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>1321053</t>
+          <t>1321055</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321053</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321055</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>International Sales Representetive German Speaker</t>
+          <t>International Sales Representetive Italian Speaker</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -23699,17 +23699,17 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>1321052</t>
+          <t>1321053</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321052</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321053</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>International Sales Representetive</t>
+          <t>International Sales Representetive German Speaker</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>178 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -23741,22 +23741,22 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1320932</t>
+          <t>1321052</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1320932</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321052</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Marketing Executive</t>
+          <t>International Sales Representetive</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>259 applicants</t>
+          <t>180 applicants</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -23776,29 +23776,29 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Treehouse</t>
+          <t>Esvita Clinic</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1320725</t>
+          <t>1320932</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1320725</t>
+          <t>https://aiesec.org/opportunity/global-talent/1320932</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>International Educational Consultant</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>73 applicants</t>
+          <t>261 applicants</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -23818,29 +23818,29 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>JOHN AND JOHN EĞİTİM TEKNOLOJİ VE İNTERNET YATIRIMLARI LİMİT</t>
+          <t>Treehouse</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1317664</t>
+          <t>1320725</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317664</t>
+          <t>https://aiesec.org/opportunity/global-talent/1320725</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>SALES ATTENDED</t>
+          <t>International Educational Consultant</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>66 applicants</t>
+          <t>73 applicants</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -23860,29 +23860,29 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>JOHN AND JOHN EĞİTİM TEKNOLOJİ VE İNTERNET YATIRIMLARI LİMİT</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1317170</t>
+          <t>1317664</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317170</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317664</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Guest Relations Officer</t>
+          <t>SALES ATTENDED</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -23892,39 +23892,39 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>50 applicants</t>
+          <t>66 applicants</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Lanka Island Resorts Ltd</t>
+          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>1317128</t>
+          <t>1317170</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317128</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317170</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>BUSINESS ADMINISTRATION</t>
+          <t>Guest Relations Officer</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -23934,39 +23934,39 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>314 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Abdi İbrahim Pharmaceutical</t>
+          <t>Lanka Island Resorts Ltd</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>1317021</t>
+          <t>1317128</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317021</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317128</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Foreign trade salesman for a manufacturing company</t>
+          <t>BUSINESS ADMINISTRATION</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>中国福建省漳州市</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>101 applicants</t>
+          <t>314 applicants</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -23986,29 +23986,29 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Maxtop(FUJIAN)Industry Co.,Ltd.</t>
+          <t>Abdi İbrahim Pharmaceutical</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1317005</t>
+          <t>1317021</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317005</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317021</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Foreign trade salesman for a manufacturing company</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Manisa, Yunusemre/Manisa, Türkiye</t>
+          <t>中国福建省漳州市</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -24018,91 +24018,91 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>229 applicants</t>
+          <t>101 applicants</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>TOYO MATBAA MÜREKKEPLERİ SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Maxtop(FUJIAN)Industry Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>1316550</t>
+          <t>1317005</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1316550</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317005</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>ACE Program | Voice Spanish Translator</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal, India</t>
+          <t>Manisa, Yunusemre/Manisa, Türkiye</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>229 applicants</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>TOYO MATBAA MÜREKKEPLERİ SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1315265</t>
+          <t>1316550</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315265</t>
+          <t>https://aiesec.org/opportunity/global-talent/1316550</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Sales Attendant</t>
+          <t>ACE Program | Voice Spanish Translator</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Kolkata, West Bengal, India</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>75 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -24112,29 +24112,29 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>1315190</t>
+          <t>1315265</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315190</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315265</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Front Office Trainee</t>
+          <t>Sales Attendant</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>101 applicants</t>
+          <t>75 applicants</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -24154,29 +24154,29 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Park Hotel International Limited</t>
+          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>1315171</t>
+          <t>1315190</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315171</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315190</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>MARKET RESEARCH/ANALYST</t>
+          <t>Front Office Trainee</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>78 applicants</t>
+          <t>101 applicants</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -24196,29 +24196,29 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>ÜÇEL KAUÇUK TAŞIT ARAÇLARI OTOMOTİV</t>
+          <t>Park Hotel International Limited</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>1315102</t>
+          <t>1315171</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315102</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315171</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Food and Beverage Trainee</t>
+          <t>MARKET RESEARCH/ANALYST</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>42 applicants</t>
+          <t>78 applicants</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -24238,29 +24238,29 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Park Hotel International Limited</t>
+          <t>ÜÇEL KAUÇUK TAŞIT ARAÇLARI OTOMOTİV</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>1314760</t>
+          <t>1315102</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1314760</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315102</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Food and Beverage Trainee</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>İzmir, Türkiye</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -24270,39 +24270,39 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>253 applicants</t>
+          <t>42 applicants</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Miranda Dekorasyon Mobilya ve İnşaat Ticaret LTD. ŞTİ</t>
+          <t>Park Hotel International Limited</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>1313882</t>
+          <t>1314760</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313882</t>
+          <t>https://aiesec.org/opportunity/global-talent/1314760</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Bảo Yên, Thanh Thủy, Phú Thọ, Việt Nam</t>
+          <t>İzmir, Türkiye</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>218 applicants</t>
+          <t>253 applicants</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -24322,24 +24322,24 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>LYNN TIMES HOTELS &amp; RESORTS</t>
+          <t>Miranda Dekorasyon Mobilya ve İnşaat Ticaret LTD. ŞTİ</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>1313813</t>
+          <t>1313882</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313813</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313882</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Receptionist</t>
+          <t>Customer Service</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>167 applicants</t>
+          <t>218 applicants</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -24371,22 +24371,22 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>1313793</t>
+          <t>1313813</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313793</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313813</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>IT Sales Executive</t>
+          <t>Receptionist</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Kim Chung, Hoài Đức, Hà Nội, Việt Nam</t>
+          <t>Bảo Yên, Thanh Thủy, Phú Thọ, Việt Nam</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>139 applicants</t>
+          <t>167 applicants</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -24406,29 +24406,29 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>MOHA SOFTWARE JOINT STOCK COMPANY</t>
+          <t>LYNN TIMES HOTELS &amp; RESORTS</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>1312624</t>
+          <t>1313793</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1312624</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313793</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>MARKET RESEARCH/ANALYST</t>
+          <t>IT Sales Executive</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Kim Chung, Hoài Đức, Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -24438,39 +24438,39 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>124 applicants</t>
+          <t>139 applicants</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>YAŞALAR KALIP YEDEK PARÇA SANAYİ VE TİCARET LTD.ŞTİ.</t>
+          <t>MOHA SOFTWARE JOINT STOCK COMPANY</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>1310418</t>
+          <t>1312624</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1310418</t>
+          <t>https://aiesec.org/opportunity/global-talent/1312624</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>MARKET RESEARCH/ANALYST</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>97 applicants</t>
+          <t>124 applicants</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -24490,29 +24490,29 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>HÜNER</t>
+          <t>YAŞALAR KALIP YEDEK PARÇA SANAYİ VE TİCARET LTD.ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>1307772</t>
+          <t>1310418</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307772</t>
+          <t>https://aiesec.org/opportunity/global-talent/1310418</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>SALES and MARKETING - ZİMEK MAKİNE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Kocabaş, 20330 Honaz/Denizli, Türkiye</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>138 applicants</t>
+          <t>97 applicants</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -24532,29 +24532,29 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
+          <t>HÜNER</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>1307244</t>
+          <t>1307772</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307772</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Robotics &amp; Automation</t>
+          <t>SALES and MARKETING - ZİMEK MAKİNE</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Kocabaş, 20330 Honaz/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -24564,39 +24564,39 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>138 applicants</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Kiet group of Institutions</t>
+          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>1307242</t>
+          <t>1307244</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Automotive Mechatronics</t>
+          <t>Robotics &amp; Automation</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Ghaziabad, India</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -24616,29 +24616,29 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Kiet group of Institutions</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>1307153</t>
+          <t>1307242</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307153</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Technology Business Development Consultant</t>
+          <t>Automotive Mechatronics</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Bucharest, Romania</t>
+          <t>Ghaziabad, India</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -24648,39 +24648,39 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>183 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Rinf Tech</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1305239</t>
+          <t>1307153</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1305239</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307153</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Accelerate Romania | Technology Business Development Consultant</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Eskişehir, Türkiye</t>
+          <t>Bucharest, Romania</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>81 applicants</t>
+          <t>183 applicants</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -24700,29 +24700,29 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Esaysan Endüstriyel Metal Ürünleri Sanayi Ve Ticaret</t>
+          <t>Rinf Tech</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1304736</t>
+          <t>1305239</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304736</t>
+          <t>https://aiesec.org/opportunity/global-talent/1305239</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Hotel Entertainer</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Heraklion, Greece</t>
+          <t>Eskişehir, Türkiye</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -24732,81 +24732,81 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>233 applicants</t>
+          <t>81 applicants</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Remarc Internation</t>
+          <t>Esaysan Endüstriyel Metal Ürünleri Sanayi Ve Ticaret</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>1304488</t>
+          <t>1305153</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304488</t>
+          <t>https://aiesec.org/opportunity/global-talent/1305153</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Client Consultant | Tourism Sector (German /Dutch speaker) ( Flexible RE dates )</t>
+          <t>ACE Program | Spanish Talent Acquisition Specialist</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Athens, Greece</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>93 applicants</t>
+          <t>76 applicants</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>SpeakIT</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>1301868</t>
+          <t>1304736</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1301868</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304736</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Marketing Assistant</t>
+          <t>Hotel Entertainer</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Alor Setar, Kedah, Malaysia</t>
+          <t>Heraklion, Greece</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -24816,39 +24816,39 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>489 applicants</t>
+          <t>233 applicants</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Yonhin Sdn. Bhd</t>
+          <t>Remarc Internation</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>1301518</t>
+          <t>1304488</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1301518</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304488</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Client Consultant | Tourism Sector (German /Dutch speaker) ( Flexible RE dates )</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Yıldırım, Türkiye</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -24858,39 +24858,39 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>98 applicants</t>
+          <t>93 applicants</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>OMTEC Automotive</t>
+          <t>SpeakIT</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>1299419</t>
+          <t>1301868</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1299419</t>
+          <t>https://aiesec.org/opportunity/global-talent/1301868</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Digital marketing</t>
+          <t>Marketing Assistant</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Yıldırım, Türkiye</t>
+          <t>Alor Setar, Kedah, Malaysia</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -24900,49 +24900,49 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>163 applicants</t>
+          <t>489 applicants</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Ilya Organik</t>
+          <t>Yonhin Sdn. Bhd</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>1297124</t>
+          <t>1301518</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1297124</t>
+          <t>https://aiesec.org/opportunity/global-talent/1301518</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>ACE Program | Portuguese Talent Acquisition Specialist</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Yıldırım, Türkiye</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>98 applicants</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -24952,29 +24952,29 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>OMTEC Automotive</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>1296457</t>
+          <t>1299419</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1296457</t>
+          <t>https://aiesec.org/opportunity/global-talent/1299419</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Sales Engineering</t>
+          <t>Digital marketing</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Dilovası, Türkiye</t>
+          <t>Yıldırım, Türkiye</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -24984,49 +24984,49 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>200 applicants</t>
+          <t>163 applicants</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Eurotray Metal Elektrik Company</t>
+          <t>Ilya Organik</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>1296387</t>
+          <t>1297124</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1296387</t>
+          <t>https://aiesec.org/opportunity/global-talent/1297124</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>ACE Program | Portuguese Talent Acquisition Specialist</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Şehitkamil, Türkiye</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -25036,29 +25036,29 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Big Brands Dış Ticaret Limited Şirketi</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>1296294</t>
+          <t>1296457</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1296294</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296457</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>IT Sales</t>
+          <t>Sales Engineering</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Đống Đa, Vietnam</t>
+          <t>Dilovası, Türkiye</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -25068,39 +25068,39 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>175 applicants</t>
+          <t>201 applicants</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Vitex Vietnam Software Joint Stock Company</t>
+          <t>Eurotray Metal Elektrik Company</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>1293928</t>
+          <t>1296387</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1293928</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296387</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Odunpazarı, Türkiye</t>
+          <t>Şehitkamil, Türkiye</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>159 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -25120,29 +25120,29 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>API Prime Yazılım Teknolojileri</t>
+          <t>Big Brands Dış Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>1289378</t>
+          <t>1296294</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296294</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Medical Advisor (Spanish Speaker)</t>
+          <t>IT Sales</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Đống Đa, Vietnam</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -25152,39 +25152,39 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>141 applicants</t>
+          <t>175 applicants</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Vitex Vietnam Software Joint Stock Company</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>1289377</t>
+          <t>1293928</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
+          <t>https://aiesec.org/opportunity/global-talent/1293928</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Medical Advisor (Italian Speaker)</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Odunpazarı, Türkiye</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>159 applicants</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -25204,47 +25204,131 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>API Prime Yazılım Teknolojileri</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
+          <t>1289378</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Medical Advisor (Spanish Speaker)</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>İstanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>142 applicants</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>6 - 18 Months</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>International Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>1289377</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Medical Advisor (Italian Speaker)</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>İstanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>45 applicants</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>6 - 18 Months</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>International Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
           <t>1289375</t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>https://aiesec.org/opportunity/global-talent/1289375</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>Medical Advisor (German Speaker)</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr">
+      <c r="D593" t="inlineStr">
         <is>
           <t>İstanbul, Türkiye</t>
         </is>
       </c>
-      <c r="E591" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F591" t="inlineStr">
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
         <is>
           <t>45 applicants</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
+      <c r="G593" t="inlineStr">
         <is>
           <t>6 - 18 Months</t>
         </is>
       </c>
-      <c r="H591" t="inlineStr">
+      <c r="H593" t="inlineStr">
         <is>
           <t>International Plus</t>
         </is>

--- a/Yesterday.xlsx
+++ b/Yesterday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H530"/>
+  <dimension ref="A1:H532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51 applicants</t>
+          <t>54 applicants</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -515,17 +515,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1337027</t>
+          <t>1337025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337027</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ace Program| Senior Full-Stack Developer (Java, React)</t>
+          <t>ACE Program | IT Operations Analyst</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>74 applicants</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,22 +557,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1297124</t>
+          <t>1337023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1297124</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337023</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ACE Program | Portuguese Talent Acquisition Specialist</t>
+          <t>ACE Program | Intermediate/Senior Data Engineer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Budapeste, Hungria</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>57 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -683,22 +683,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1337572</t>
+          <t>1337577</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337572</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337577</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>People &amp; Organization Trainee</t>
+          <t>A Design Experience Through Japanese Architecture by　TERASU — Illuminating the Future of International Students</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Panama City, Panamá Province, Panama</t>
+          <t>日本、兵庫県宝塚市</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,39 +708,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Novartis Pharma Logistics, Panama</t>
+          <t>Terasu Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1337571</t>
+          <t>1337572</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337571</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337572</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>People &amp; Organization Trainee</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zefta, Madinet Zefta, Zefta, Gharbia Governorate, Egypt</t>
+          <t>Panama City, Panamá Province, Panama</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Negm store</t>
+          <t>Novartis Pharma Logistics, Panama</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>42 applicants</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>59 applicants</t>
+          <t>65 applicants</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>52 applicants</t>
+          <t>53 applicants</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>137 applicants</t>
+          <t>148 applicants</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>115 applicants</t>
+          <t>124 applicants</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>38 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2825,22 +2825,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1337243</t>
+          <t>1337247</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337247</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Medical Advisor (Serbian Speaker)</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Tunis, Tunisie</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2850,34 +2850,34 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Declitech</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1337242</t>
+          <t>1337243</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Medical Advisor (Bulgarian Speaker)</t>
+          <t>Medical Advisor (Serbian Speaker)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2909,17 +2909,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1337242</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Medical Advisor (Czech Speaker)</t>
+          <t>Medical Advisor (Bulgarian Speaker)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2951,22 +2951,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1337237</t>
+          <t>1337241</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337237</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Medical Advisor (Czech Speaker)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kartepe, Kocaeli, Türkiye</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2986,29 +2986,29 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>RHİNO TANK</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1337227</t>
+          <t>1337237</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337237</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Kartepe, Kocaeli, Türkiye</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3018,39 +3018,39 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>RHİNO TANK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1337215</t>
+          <t>1337227</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337215</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3060,39 +3060,39 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ARMEKA</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1337158</t>
+          <t>1337215</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337215</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3112,29 +3112,29 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Dirim Metal Anonim Şirketi</t>
+          <t>ARMEKA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1337113</t>
+          <t>1337158</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337113</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Architectural Marketing Intern</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Curitiba, PR, Brasil</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3154,29 +3154,29 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ATR Incorporadora</t>
+          <t>Dirim Metal Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1337107</t>
+          <t>1337113</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337107</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337113</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Business Development &amp; Research Intern (Green Agenda / EU Funds)</t>
+          <t>[Impact Brazil] - Architectural Marketing Intern</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>Curitiba, PR, Brasil</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3186,39 +3186,39 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>TOMRA COLLECTION</t>
+          <t>ATR Incorporadora</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1337103</t>
+          <t>1337107</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337107</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Education Coordinator</t>
+          <t>Business Development &amp; Research Intern (Green Agenda / EU Funds)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>41 applicants</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3238,29 +3238,29 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
+          <t>TOMRA COLLECTION</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1337100</t>
+          <t>1337103</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Education Coordinator</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3270,39 +3270,39 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1337037</t>
+          <t>1337100</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337037</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Social Media Specialist</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3312,76 +3312,76 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Moharb marketing agency</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1337026</t>
+          <t>1337037</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337026</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337037</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ace Program | Senior DevOps Engineer (Azure)</t>
+          <t>Social Media Specialist</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Budapeste, Hungria</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Moharb marketing agency</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1337025</t>
+          <t>1337027</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337025</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337027</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ACE Program | IT Operations Analyst</t>
+          <t>Ace Program| Senior Full-Stack Developer (Java, React)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3413,17 +3413,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1337023</t>
+          <t>1337026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337023</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ACE Program | Intermediate/Senior Data Engineer</t>
+          <t>Ace Program | Senior DevOps Engineer (Azure)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>52 applicants</t>
+          <t>54 applicants</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>42 applicants</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4757,22 +4757,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1336530</t>
+          <t>1336522</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336530</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336522</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>People Analytics &amp; Compensation Intern [AIESECers Only]</t>
+          <t>Guest Relations Intern</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mexico City, CDMX, Mexico</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4782,34 +4782,34 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sodexo Mexico</t>
+          <t>Welcomhotel by ITC Hotels Mohali Chandigarh</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1336522</t>
+          <t>1336514</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336522</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336514</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Guest Relations Intern</t>
+          <t>Food and Beverage Service Intern</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4841,22 +4841,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1336514</t>
+          <t>1336498</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336514</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336498</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Food and Beverage Service Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4866,39 +4866,39 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>66 applicants</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Welcomhotel by ITC Hotels Mohali Chandigarh</t>
+          <t>ERA ELEKTRONİK SANAYİ VE TİCARET A.Ş.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1336498</t>
+          <t>1336467</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336498</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336467</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Electrical Intern</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4908,39 +4908,39 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>66 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ERA ELEKTRONİK SANAYİ VE TİCARET A.Ş.</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1336467</t>
+          <t>1336453</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336467</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336453</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Electrical Intern</t>
+          <t>Animator/Video Editor</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>El Sadat City, Menofia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4950,39 +4950,39 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Organix (1)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1336453</t>
+          <t>1336441</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336453</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336441</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Animator/Video Editor</t>
+          <t>Accelerate Romania - Sales Development Representative (SDR)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>El Sadat City, Menofia Governorate, Egypt</t>
+          <t>Târgu Mureș, Romania</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5002,29 +5002,29 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Organix (1)</t>
+          <t>ProMotion Creative</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1336441</t>
+          <t>1336439</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336441</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336439</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Sales Development Representative (SDR)</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Târgu Mureș, Romania</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5034,39 +5034,39 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ProMotion Creative</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1336439</t>
+          <t>1336414</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336439</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336414</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>CRM Assistant</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5076,39 +5076,39 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>The Address</t>
+          <t>Samsung Electronics Latinoamérica (Zona Libre) S.A (SELA)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1336414</t>
+          <t>1336404</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336414</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CRM Assistant</t>
+          <t>Performance &amp; Entertainment Intern</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5118,39 +5118,39 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>82 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamérica (Zona Libre) S.A (SELA)</t>
+          <t>Starbeans Ceylon (Pvt ) Ltd</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1336404</t>
+          <t>1336380</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336380</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Performance &amp; Entertainment Intern</t>
+          <t>Business Development Executive</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5170,29 +5170,29 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Starbeans Ceylon (Pvt ) Ltd</t>
+          <t>NETGAINS</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1336380</t>
+          <t>1336369</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336380</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336369</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Business Development Executive</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5202,39 +5202,39 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>NETGAINS</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1336369</t>
+          <t>1336368</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336369</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336368</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Photographer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5254,24 +5254,24 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>GloWebMark GWM</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1336368</t>
+          <t>1336367</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336368</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336367</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Photographer</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5303,22 +5303,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1336367</t>
+          <t>1336365</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336367</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336365</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5338,29 +5338,29 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>GloWebMark GWM</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1336365</t>
+          <t>1336355</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336365</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336355</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Regional Sales Representative</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5370,49 +5370,49 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>YILMAZ MAKİNE SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1336355</t>
+          <t>1336346</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336355</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336346</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Regional Sales Representative</t>
+          <t>ACE Program | IT Operations Analyst</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Budapeste, Hungria</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5422,71 +5422,71 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>YILMAZ MAKİNE SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1336346</t>
+          <t>1336343</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336346</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336343</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ACE Program | IT Operations Analyst</t>
+          <t>Accelerate Romania -  Digital Sales &amp; Partnerships Intern</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Budapeste, Hungria</t>
+          <t>Oradea, Romania</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>82 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Cylex</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1336343</t>
+          <t>1336314</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336343</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336314</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Accelerate Romania -  Digital Sales &amp; Partnerships Intern</t>
+          <t>Finance Intern</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Oradea, Romania</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5506,24 +5506,24 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Cylex</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1336314</t>
+          <t>1336313</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336314</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336313</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Finance Intern</t>
+          <t>Business Development  Intern</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5555,22 +5555,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1336313</t>
+          <t>1336276</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336313</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336276</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Business Development  Intern</t>
+          <t>Accelerate Romania - International Research Internship in Wine Tourism &amp; Wine Studies (Database Development)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>The Address</t>
+          <t>Babeș-Bolyai University</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1336276</t>
+          <t>1336275</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336276</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336275</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Accelerate Romania - International Research Internship in Wine Tourism &amp; Wine Studies (Database Development)</t>
+          <t>Accelerate Romania - International Research Internship in Hospitality &amp; Tourism Surveys</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>32 applicants</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5639,17 +5639,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1336275</t>
+          <t>1336274</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336275</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336274</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Accelerate Romania - International Research Internship in Hospitality &amp; Tourism Surveys</t>
+          <t>Accelerate Romania - Design of negotiation and conflict management simulations</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5681,17 +5681,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1336274</t>
+          <t>1336271</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336274</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336271</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Design of negotiation and conflict management simulations</t>
+          <t>Accelerate Romania - Engagement &amp; innovation role in sustainability research projects</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5723,22 +5723,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1336271</t>
+          <t>1336259</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336271</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336259</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Engagement &amp; innovation role in sustainability research projects</t>
+          <t>Accounts Payable Clerk</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5748,39 +5748,39 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>34 applicants</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Babeș-Bolyai University</t>
+          <t>PSA Panama International Terminal, S.A.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1336259</t>
+          <t>1336245</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336259</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336245</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Accounts Payable Clerk</t>
+          <t>Front Office Admin</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5790,123 +5790,123 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>PSA Panama International Terminal, S.A.</t>
+          <t>Seven Oaks Pet Hospital</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1336245</t>
+          <t>1336219</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336245</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336219</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Front Office Admin</t>
+          <t>Business Development Intern | Infosys Instep Program</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Seven Oaks Pet Hospital</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1336219</t>
+          <t>1336164</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336219</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336164</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Business Development Intern | Infosys Instep Program</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>ÇRZ KURUYEMİŞ MAKİNALARI TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1336164</t>
+          <t>1336151</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336164</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>AI Internship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5916,39 +5916,39 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ÇRZ KURUYEMİŞ MAKİNALARI TİCARET LİMİTED ŞİRKETİ</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1336151</t>
+          <t>1336119</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336119</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AI Internship</t>
+          <t>Game Design Research Intern</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Sohna, Haryana 122103, India</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5968,24 +5968,24 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>K.R. Mangalam University</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1336119</t>
+          <t>1336115</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336119</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336115</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Game Design Research Intern</t>
+          <t>Law Research Intern</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6017,17 +6017,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1336115</t>
+          <t>1336111</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336115</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336111</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Law Research Intern</t>
+          <t>Computer Science Engineering Research Intern</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6059,17 +6059,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1336111</t>
+          <t>1336109</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336111</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336109</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Computer Science Engineering Research Intern</t>
+          <t>Data Science Research Intern</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6101,17 +6101,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1336109</t>
+          <t>1336108</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336109</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Data Science Research Intern</t>
+          <t>Full Stack Development Research Intern</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -6143,17 +6143,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1336108</t>
+          <t>1336107</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336107</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Full Stack Development Research Intern</t>
+          <t>Cyber Security Research Intern</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6185,22 +6185,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1336107</t>
+          <t>1336076</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336107</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336076</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cyber Security Research Intern</t>
+          <t>Medical Information Solutions Trainee</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sohna, Haryana 122103, India</t>
+          <t>Bruxelles, Belgio</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6210,39 +6210,39 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>43 applicants</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>K.R. Mangalam University</t>
+          <t>UCB</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1336076</t>
+          <t>1336041</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336076</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336041</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Medical Information Solutions Trainee</t>
+          <t>Administrative, Marketing &amp; E-Marketing (Fairs, Events &amp;  Customer Follow-up)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Bruxelles, Belgio</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6252,34 +6252,34 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>NAGEH ENGINEERING CO.- LLC شركة ناجح الهندسية</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1336041</t>
+          <t>1336040</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336041</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336040</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Administrative, Marketing &amp; E-Marketing (Fairs, Events &amp;  Customer Follow-up)</t>
+          <t>Aviation Engineer</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6311,22 +6311,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1336040</t>
+          <t>1336006</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336040</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336006</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Aviation Engineer</t>
+          <t>ESG &amp; Sustainability Track</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>NAGEH ENGINEERING CO.- LLC شركة ناجح الهندسية</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1336006</t>
+          <t>1336005</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336006</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336005</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ESG &amp; Sustainability Track</t>
+          <t>HR Track</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6395,17 +6395,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1336005</t>
+          <t>1336004</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336005</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336004</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HR Track</t>
+          <t>Marketing &amp; Brand Track</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6437,17 +6437,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1336004</t>
+          <t>1336003</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336004</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336003</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand Track</t>
+          <t>Rural Immersion Track</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6479,17 +6479,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1336003</t>
+          <t>1336002</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336003</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336002</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Rural Immersion Track</t>
+          <t>Retail Strategy Track</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6521,17 +6521,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1336002</t>
+          <t>1336001</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336002</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336001</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Retail Strategy Track</t>
+          <t>Product Track – Digital &amp; Banking Products</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6563,17 +6563,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1336001</t>
+          <t>1336000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336001</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336000</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Product Track – Digital &amp; Banking Products</t>
+          <t>Technology Track – AI, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>27 applicants</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6605,22 +6605,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1336000</t>
+          <t>1335994</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336000</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335994</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Technology Track – AI, Data &amp; Analytics</t>
+          <t>Business developement</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6640,29 +6640,29 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1335994</t>
+          <t>1335925</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335994</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335925</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Business developement</t>
+          <t>Digital Business &amp; Technology Intern</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Surat, Gujarat, India</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>AlignSoul Connect Pvt. Ltd</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1335925</t>
+          <t>1335911</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335925</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335911</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Digital Business &amp; Technology Intern</t>
+          <t>Guest Relations and Service Captain</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Surat, Gujarat, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6714,39 +6714,39 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>AlignSoul Connect Pvt. Ltd</t>
+          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1335911</t>
+          <t>1335803</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335911</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335803</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Guest Relations and Service Captain</t>
+          <t>Customer Success Manager Germany</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Eindhoven, Netherlands</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6756,39 +6756,39 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
+          <t>Returnless</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1335803</t>
+          <t>1335757</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335803</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335757</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Customer Success Manager Germany</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Eindhoven, Netherlands</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>34 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6808,29 +6808,29 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Returnless</t>
+          <t>Sevinçler Sağlık Ürünleri</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1335757</t>
+          <t>1335678</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335757</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335678</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Gampola, Sri Lanka</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6840,39 +6840,39 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>31 applicants</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sevinçler Sağlık Ürünleri</t>
+          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1335678</t>
+          <t>1335645</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335678</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335645</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Pharmacy Intern</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Gampola, Sri Lanka</t>
+          <t>Rajpura, Punjab, India</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>31 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6892,29 +6892,29 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
+          <t>Swami Vivekanand Institute of Engineering &amp; Technology</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1335645</t>
+          <t>1335628</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335645</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335628</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Pharmacy Intern</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Rajpura, Punjab, India</t>
+          <t>Rades, Tunisia</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6934,29 +6934,29 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Swami Vivekanand Institute of Engineering &amp; Technology</t>
+          <t>AmazingPandph Digital Media Management</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1335628</t>
+          <t>1335624</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335628</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335624</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Digital Marketer</t>
+          <t>Communications Intern</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Rades, Tunisia</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6976,29 +6976,29 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>AmazingPandph Digital Media Management</t>
+          <t>EFFIOS</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1335624</t>
+          <t>1335611</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335624</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335611</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Communications Intern</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Sfax, Tunisie</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7018,29 +7018,29 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>EFFIOS</t>
+          <t>Al rabie Gros</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1335611</t>
+          <t>1335549</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335611</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335549</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sfax, Tunisie</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7060,29 +7060,29 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Al rabie Gros</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1335549</t>
+          <t>1335547</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335549</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335547</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>New Damietta City, Damietta El-Gadeeda City, New Damietta, Damietta Governorate, Egypt</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7092,34 +7092,34 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>Business Haven Consultancy</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1335547</t>
+          <t>1335546</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335547</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335546</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Digital Marketer</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7151,22 +7151,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1335546</t>
+          <t>1335526</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335546</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335526</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Hotel Management Intern</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>New Damietta City, Damietta El-Gadeeda City, New Damietta, Damietta Governorate, Egypt</t>
+          <t>Naultha, Haryana 132145, India</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7176,39 +7176,39 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Business Haven Consultancy</t>
+          <t>Geeta University</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1335526</t>
+          <t>1335516</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335526</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335516</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hotel Management Intern</t>
+          <t>[EU/Brazil] C++ Software Development Intern (Linux and Rust)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Naultha, Haryana 132145, India</t>
+          <t>72 Tübingen, Germany</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>121 applicants</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -7228,29 +7228,29 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Geeta University</t>
+          <t>Intra2net AG</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1335516</t>
+          <t>1335474</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335516</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335474</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>[EU/Brazil] C++ Software Development Intern (Linux and Rust)</t>
+          <t>[Remote]Franchise Sales Executive</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>72 Tübingen, Germany</t>
+          <t>No location available</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7260,39 +7260,39 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>121 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Intra2net AG</t>
+          <t>Rainbucks</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1335474</t>
+          <t>1335444</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335474</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335444</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>[Remote]Franchise Sales Executive</t>
+          <t>Cardiometabolic Marketing Trainee</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>No location available</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7302,39 +7302,39 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>80 applicants</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Rainbucks</t>
+          <t>NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1335444</t>
+          <t>1335385</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335444</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335385</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cardiometabolic Marketing Trainee</t>
+          <t>Electrical Engineer</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Coimbra, Portugal</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7344,17 +7344,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>80 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NOVARTIS</t>
+          <t>CWPOWER</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>118 applicants</t>
+          <t>120 applicants</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>98 applicants</t>
+          <t>99 applicants</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>65 applicants</t>
+          <t>66 applicants</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>34 applicants</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>89 applicants</t>
+          <t>90 applicants</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>111 applicants</t>
+          <t>112 applicants</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>92 applicants</t>
+          <t>95 applicants</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>64 applicants</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>104 applicants</t>
+          <t>105 applicants</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>67 applicants</t>
+          <t>68 applicants</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -15467,22 +15467,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1331435</t>
+          <t>1331444</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331435</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331444</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SALES MANAGER</t>
+          <t>Taste Hungary | Football Data Analyst</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Kumkısık, 20060 Denizli Merkezefendi/Denizli, Türkiye</t>
+          <t>Budapest, Magyarország</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -15492,39 +15492,39 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>64 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>BEMOS OTOMASYON</t>
+          <t>ACE Advisory</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1331433</t>
+          <t>1331435</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331433</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331435</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Social Media and Content Creation</t>
+          <t>SALES MANAGER</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Jaipur, Rajasthan, India</t>
+          <t>Kumkısık, 20060 Denizli Merkezefendi/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -15534,39 +15534,39 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>65 applicants</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Boomerang Hospitality</t>
+          <t>BEMOS OTOMASYON</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1331430</t>
+          <t>1331433</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331430</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331433</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Digital Media Strategist - Mid Term</t>
+          <t>Social Media and Content Creation</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Jaipur, Rajasthan, India</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -15586,29 +15586,29 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Boomerang Hospitality</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1331425</t>
+          <t>1331430</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331425</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331430</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>SALES MANAGER</t>
+          <t>Digital Media Strategist - Mid Term</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>52 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -15628,29 +15628,29 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>DİZAYN MEDİKAL</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1331380</t>
+          <t>1331425</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331380</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331425</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Business Operations &amp; Community Development Intern</t>
+          <t>SALES MANAGER</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Jaipur, Rajasthan, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>52 applicants</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -15670,29 +15670,29 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Boomerang Hospitality</t>
+          <t>DİZAYN MEDİKAL</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1331274</t>
+          <t>1331380</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331274</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331380</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Business Operations &amp; Community Development Intern</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Phagwara, Punjab, India</t>
+          <t>Jaipur, Rajasthan, India</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -15712,29 +15712,29 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>GNA University</t>
+          <t>Boomerang Hospitality</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1331270</t>
+          <t>1331274</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331270</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331274</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Phagwara, Punjab, India</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -15754,29 +15754,29 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Requisite Technologies Pvt Ltd</t>
+          <t>GNA University</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1331174</t>
+          <t>1331270</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331174</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331270</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Graphic Designer / UI - UX Designer</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -15786,39 +15786,39 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Wavetec</t>
+          <t>Requisite Technologies Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1331172</t>
+          <t>1331174</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331172</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331174</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Marketing Communication Intern/Coordinator</t>
+          <t>Graphic Designer / UI - UX Designer</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -15828,39 +15828,39 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>64 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>OK Lucky Star</t>
+          <t>Wavetec</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1331115</t>
+          <t>1331172</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331115</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331172</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Marketing Communication Intern/Coordinator</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Jalandhar, Punjab, India</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>64 applicants</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -15880,29 +15880,29 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Lovely Professional University</t>
+          <t>OK Lucky Star</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1331070</t>
+          <t>1331115</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331070</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331115</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Performance Marketing</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Jalandhar, Punjab, India</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -15922,24 +15922,24 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Madaar</t>
+          <t>Lovely Professional University</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1331064</t>
+          <t>1331070</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331064</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331070</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Video Editor / Reels Maker</t>
+          <t>Performance Marketing</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -15971,17 +15971,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1331063</t>
+          <t>1331064</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331063</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331064</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Social Media &amp; Community Marketing</t>
+          <t>Video Editor / Reels Maker</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -16013,22 +16013,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1331015</t>
+          <t>1331063</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1331015</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331063</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Social Media &amp; Community Marketing</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Sincan, İstasyon, 06934 Sincan/Ankara, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>85 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -16048,29 +16048,29 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Maksan Lift</t>
+          <t>Madaar</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1330859</t>
+          <t>1331015</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330859</t>
+          <t>https://aiesec.org/opportunity/global-talent/1331015</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Export Sales Specialist</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Başakşehir, Başak, 34490 Başakşehir/İstanbul, Türkiye</t>
+          <t>Sincan, İstasyon, 06934 Sincan/Ankara, Türkiye</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>147 applicants</t>
+          <t>85 applicants</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -16090,29 +16090,29 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Esen Isıtma Soğutma Elektrik İnşaat Sanayi ve Ticaret</t>
+          <t>Maksan Lift</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1330856</t>
+          <t>1330859</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330856</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330859</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Business Development Intern  (Long Term)</t>
+          <t>Export Sales Specialist</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Lahore, Pakistan</t>
+          <t>Başakşehir, Başak, 34490 Başakşehir/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -16122,34 +16122,34 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>147 applicants</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Chughtaiz</t>
+          <t>Esen Isıtma Soğutma Elektrik İnşaat Sanayi ve Ticaret</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1330851</t>
+          <t>1330856</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330851</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330856</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Business Development Intern  (Long Term)</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -16164,12 +16164,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16181,74 +16181,74 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1330678</t>
+          <t>1330851</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330678</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330851</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ACE Program | Global Coordinator (AIESECers Only)</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Lahore, Pakistan</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Chughtaiz</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1330393</t>
+          <t>1330678</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330393</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330678</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>[Impact in Belo Horizonte] - Business Development</t>
+          <t>ACE Program | Global Coordinator (AIESECers Only)</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Belo Horizonte, MG, Brasil</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>108 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -16258,29 +16258,29 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Group Tech Participações LTDA</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1330365</t>
+          <t>1330393</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330365</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330393</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Creative Styling &amp; Brand Experience Intern</t>
+          <t>[Impact in Belo Horizonte] - Business Development</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Belo Horizonte, MG, Brasil</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -16290,34 +16290,34 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>108 applicants</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>MPF clothing collection PVT LTD</t>
+          <t>Group Tech Participações LTDA</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1330158</t>
+          <t>1330365</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330158</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330365</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Partnership &amp; Capacity Building Analyst Development Specialist</t>
+          <t>Creative Styling &amp; Brand Experience Intern</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -16342,24 +16342,24 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Krishna Sadan</t>
+          <t>MPF clothing collection PVT LTD</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1330157</t>
+          <t>1330158</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330157</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330158</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Sustainability Outreach &amp; Community Development Specialist</t>
+          <t>Partnership &amp; Capacity Building Analyst Development Specialist</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -16391,22 +16391,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1330155</t>
+          <t>1330157</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330155</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330157</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Content Creation and Cultural Ambassador Intern</t>
+          <t>Sustainability Outreach &amp; Community Development Specialist</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -16416,39 +16416,39 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Sunrise Immigration Consultants Pvt. Ltd.</t>
+          <t>Krishna Sadan</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1330102</t>
+          <t>1330155</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330102</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330155</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Business Development Intern – External Expansion (POS) [GERMANY ONLY]</t>
+          <t>Content Creation and Cultural Ambassador Intern</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Timișoara, Romania</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -16458,39 +16458,39 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Vectron</t>
+          <t>Sunrise Immigration Consultants Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1330069</t>
+          <t>1330102</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330069</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330102</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing Specialist</t>
+          <t>Accelerate Romania | Business Development Intern – External Expansion (POS) [GERMANY ONLY]</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Ankara, Türkiye</t>
+          <t>Timișoara, Romania</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -16510,29 +16510,29 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Sun Danışmanlık</t>
+          <t>Vectron</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1329983</t>
+          <t>1330069</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329983</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330069</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Marketing Intern</t>
+          <t>Sales &amp; Marketing Specialist</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Târgu Mureș, Romania</t>
+          <t>Ankara, Türkiye</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>102 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -16552,29 +16552,29 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>KhepriX</t>
+          <t>Sun Danışmanlık</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1329929</t>
+          <t>1329983</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329929</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329983</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES</t>
+          <t>Accelerate Romania - Marketing Intern</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Târgu Mureș, Romania</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -16584,39 +16584,39 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>102 applicants</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>DOĞAN İNŞ.MLZM.HAFR.NAK.İŞ MAK.SAN.VE TİC.LTD.ŞTİ.</t>
+          <t>KhepriX</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1329526</t>
+          <t>1329929</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329526</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329929</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Supplier Development Procurement Intern</t>
+          <t>MARKETING &amp; SALES</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Joinville - Pirabeiraba, Joinville - SC, Brasil</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -16626,39 +16626,39 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>87 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Nidec Global Appliance</t>
+          <t>DOĞAN İNŞ.MLZM.HAFR.NAK.İŞ MAK.SAN.VE TİC.LTD.ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1329520</t>
+          <t>1329526</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329520</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329526</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Sales Officer</t>
+          <t>[Impact Brazil] - Supplier Development Procurement Intern</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
+          <t>Joinville - Pirabeiraba, Joinville - SC, Brasil</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>88 applicants</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -16678,29 +16678,29 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Pedro Barn pvt ltd</t>
+          <t>Nidec Global Appliance</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1329458</t>
+          <t>1329520</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329458</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329520</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Sales Officer</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Visakhapatnam, Andhra Pradesh, India</t>
+          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -16710,34 +16710,34 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>32 applicants</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Media3 Training</t>
+          <t>Pedro Barn pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1329457</t>
+          <t>1329458</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329457</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329458</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>BA Intern</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -16769,22 +16769,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1329257</t>
+          <t>1329457</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329257</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329457</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SALES MANAGER</t>
+          <t>BA Intern</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Visakhapatnam, Andhra Pradesh, India</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -16794,39 +16794,39 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>ALKA METAL</t>
+          <t>Media3 Training</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1329177</t>
+          <t>1329257</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329177</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329257</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
+          <t>SALES MANAGER</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Porto Alegre, RS, Brazil</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -16836,39 +16836,39 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>108 applicants</t>
+          <t>69 applicants</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>ESCOLA GIORDANO BRUNO LTDA</t>
+          <t>ALKA METAL</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1329104</t>
+          <t>1329177</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329104</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329177</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Sales Intern</t>
+          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Pannipitiya, Sri Lanka</t>
+          <t>Porto Alegre, RS, Brazil</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -16878,39 +16878,39 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>108 applicants</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Frella International</t>
+          <t>ESCOLA GIORDANO BRUNO LTDA</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1329079</t>
+          <t>1329104</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329079</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329104</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Accelerate Romania - YOUNG CIVIL &amp; GEOTECHNICAL ENGINEER</t>
+          <t>Sales Intern</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Pannipitiya, Sri Lanka</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -16920,39 +16920,39 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>84 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Expert Proiect</t>
+          <t>Frella International</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1328980</t>
+          <t>1329079</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328980</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329079</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>Accelerate Romania - YOUNG CIVIL &amp; GEOTECHNICAL ENGINEER</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>132 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -16972,29 +16972,29 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Tepma MEP Design</t>
+          <t>Expert Proiect</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1328977</t>
+          <t>1328980</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328977</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328980</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Operations Coordinator</t>
+          <t>Engineering Intern</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>133 applicants</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -17014,29 +17014,29 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Infinitum Network Solutions</t>
+          <t>Tepma MEP Design</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1328792</t>
+          <t>1328977</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328792</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328977</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Marketing Specialist</t>
+          <t>Operations Coordinator</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>90 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -17056,24 +17056,24 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>GIS Solutions</t>
+          <t>Infinitum Network Solutions</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1328768</t>
+          <t>1328792</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328768</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328792</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Digital Content Intern – Social Media &amp; Website</t>
+          <t>Accelerate Romania - Marketing Specialist</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>90 applicants</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -17098,24 +17098,24 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Dog Assist</t>
+          <t>GIS Solutions</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1328762</t>
+          <t>1328768</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328762</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328768</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Accelerate - Marketing Specialist</t>
+          <t>Accelerate Romania - Digital Content Intern – Social Media &amp; Website</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>60 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -17140,29 +17140,29 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Emotionstudios</t>
+          <t>Dog Assist</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1328761</t>
+          <t>1328762</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328761</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328762</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Online Marketing Intern</t>
+          <t>Accelerate - Marketing Specialist</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Sibiu, Romania</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>93 applicants</t>
+          <t>60 applicants</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -17182,24 +17182,24 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Gads Online Marketing</t>
+          <t>Emotionstudios</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1328760</t>
+          <t>1328761</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328760</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328761</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Sales Business Manager</t>
+          <t>Accelerate Romania - Online Marketing Intern</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>74 applicants</t>
+          <t>93 applicants</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1328685</t>
+          <t>1328760</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328685</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328760</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Medical Advisor (Russian Speaker)</t>
+          <t>Accelerate Romania - Sales Business Manager</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Sibiu, Romania</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -17256,39 +17256,39 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>74 applicants</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Gads Online Marketing</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1328629</t>
+          <t>1328685</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328629</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328685</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Medical Advisor (Russian Speaker)</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -17298,34 +17298,34 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Amaavi Luxe Travels</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1328626</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328626</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328629</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Travel Advisory intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -17340,12 +17340,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -17357,12 +17357,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1328625</t>
+          <t>1328626</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328625</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328626</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -17399,22 +17399,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1328549</t>
+          <t>1328625</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328549</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328625</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Motion graphic design</t>
+          <t>Travel Advisory intern</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -17434,24 +17434,24 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>TAR - Company</t>
+          <t>Amaavi Luxe Travels</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1328548</t>
+          <t>1328549</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328548</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328549</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Motion graphic design</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -17483,17 +17483,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1328543</t>
+          <t>1328548</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328543</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328548</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>UI/UX design</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>95 applicants</t>
+          <t>41 applicants</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -17525,22 +17525,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1328514</t>
+          <t>1328543</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328514</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328543</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>UI/UX design</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>38 applicants</t>
+          <t>95 applicants</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -17560,24 +17560,24 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>CGC JHANJERI MOHALI</t>
+          <t>TAR - Company</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1328510</t>
+          <t>1328514</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328510</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328514</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Software Developer Intern</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -17609,22 +17609,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1328460</t>
+          <t>1328510</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328460</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328510</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Medical Advisor (Romanian Speaker)</t>
+          <t>Software Developer Intern</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -17634,39 +17634,39 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>CGC JHANJERI MOHALI</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1328441</t>
+          <t>1328460</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328441</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328460</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Italian-Speaking Purchasing &amp; Negotiation Specialist (EU Citizenship Required)</t>
+          <t>Medical Advisor (Romanian Speaker)</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Iași, Romania</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -17686,29 +17686,29 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Veo Wordwide Services - Iași</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1328300</t>
+          <t>1328441</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328300</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328441</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>content creator</t>
+          <t>Accelerate Romania | Italian-Speaking Purchasing &amp; Negotiation Specialist (EU Citizenship Required)</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Iași, Romania</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -17718,39 +17718,39 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Markit</t>
+          <t>Veo Wordwide Services - Iași</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1328250</t>
+          <t>1328300</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328250</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328300</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>content creator</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -17760,29 +17760,29 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Requisite Technologies Pvt Ltd</t>
+          <t>Markit</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1328130</t>
+          <t>1328250</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328130</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328250</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -17802,12 +17802,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -17819,17 +17819,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1328115</t>
+          <t>1328130</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328115</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328130</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Business Development Executive</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -17861,22 +17861,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1328091</t>
+          <t>1328115</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328091</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328115</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>AI and IOT/ Machine Learning</t>
+          <t>Business Development Executive</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -17886,39 +17886,39 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Requisite Technologies Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1328021</t>
+          <t>1328091</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328021</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328091</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Guest Relations Officer Intern</t>
+          <t>AI and IOT/ Machine Learning</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -17928,39 +17928,39 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>35 applicants</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>The Barn By Starbeans in Ella</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1327970</t>
+          <t>1328021</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327970</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328021</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Guest Relations Officer Intern</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Malabe, Sri Lanka</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>42 applicants</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -17980,7 +17980,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Ribelz Integrated Pvt Ltd</t>
+          <t>The Barn By Starbeans in Ella</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>41 applicants</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>133 applicants</t>
+          <t>134 applicants</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>52 applicants</t>
+          <t>53 applicants</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -18491,22 +18491,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1327043</t>
+          <t>1326776</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327043</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326776</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Biotechnology Intern</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Sousse, Tunisia</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -18516,34 +18516,34 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>63 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Progress Professional Center</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1326776</t>
+          <t>1326767</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326776</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326767</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Biotechnology Intern</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -18575,17 +18575,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1326767</t>
+          <t>1326765</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326767</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326765</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -18617,17 +18617,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1326765</t>
+          <t>1326761</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326765</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326761</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern</t>
+          <t>Civil Engineering Intern</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -18659,17 +18659,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1326761</t>
+          <t>1326757</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326761</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326757</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Civil Engineering Intern</t>
+          <t>Architectural Intern</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -18701,17 +18701,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1326757</t>
+          <t>1326756</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326757</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326756</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Architectural Intern</t>
+          <t>Electrical &amp; ML Intern</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -18743,22 +18743,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1326756</t>
+          <t>1326741</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326756</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326741</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Electrical &amp; ML Intern</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -18778,29 +18778,29 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Vigilare biopharma Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1326741</t>
+          <t>1326666</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326741</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326666</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Computer Engineering Intern</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -18820,29 +18820,29 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Vigilare biopharma Pvt Ltd</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1326666</t>
+          <t>1326658</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326666</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326658</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Computer Engineering Intern</t>
+          <t>Business Development Intern (Japanese Speaking Individuals Only)</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Malabe, Sri Lanka</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -18852,39 +18852,39 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>23 applicants</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Creative Technology Solutions (Private) Limited</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1326658</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326658</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326639</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Business Development Intern (Japanese Speaking Individuals Only)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Malabe, Sri Lanka</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -18894,39 +18894,39 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Creative Technology Solutions (Private) Limited</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1326639</t>
+          <t>1326538</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326639</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326538</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>[Impact in Belo Horizonte] - Digital Marketing</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Belo Horizonte, MG, Brasil</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -18936,17 +18936,17 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>116 applicants</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Onfly</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>23 applicants</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>100 applicants</t>
+          <t>101 applicants</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>623 applicants</t>
+          <t>624 applicants</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>434 applicants</t>
+          <t>440 applicants</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>173 applicants</t>
+          <t>175 applicants</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>110 applicants</t>
+          <t>111 applicants</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>96 applicants</t>
+          <t>97 applicants</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>201 applicants</t>
+          <t>203 applicants</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>88 applicants</t>
+          <t>89 applicants</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>27 applicants</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>80 applicants</t>
+          <t>81 applicants</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -21851,22 +21851,22 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1310418</t>
+          <t>1310446</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1310418</t>
+          <t>https://aiesec.org/opportunity/global-talent/1310446</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Education Coordinator</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -21876,39 +21876,39 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>116 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>HÜNER</t>
+          <t>Genç Kardelen Kindergarden</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1308897</t>
+          <t>1310418</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1308897</t>
+          <t>https://aiesec.org/opportunity/global-talent/1310418</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>86 applicants</t>
+          <t>116 applicants</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -21928,29 +21928,29 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>İNOPLAST PLASTİK ENJEKSİYON KALIP</t>
+          <t>HÜNER</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1307772</t>
+          <t>1308897</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307772</t>
+          <t>https://aiesec.org/opportunity/global-talent/1308897</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>SALES and MARKETING - ZİMEK MAKİNE</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Kocabaş, 20330 Honaz/Denizli, Türkiye</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>143 applicants</t>
+          <t>87 applicants</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -21970,29 +21970,29 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
+          <t>İNOPLAST PLASTİK ENJEKSİYON KALIP</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>1307244</t>
+          <t>1307772</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307772</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Robotics &amp; Automation</t>
+          <t>SALES and MARKETING - ZİMEK MAKİNE</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Kocabaş, 20330 Honaz/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -22002,39 +22002,39 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>143 applicants</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Kiet group of Institutions</t>
+          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1307242</t>
+          <t>1307244</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Automotive Mechatronics</t>
+          <t>Robotics &amp; Automation</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Ghaziabad, India</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -22054,29 +22054,29 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Kiet group of Institutions</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>1307150</t>
+          <t>1307242</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307150</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>Automotive Mechatronics</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Ghaziabad, India</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -22086,39 +22086,39 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>103 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Göymen Makarna</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1306470</t>
+          <t>1307150</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1306470</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307150</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>MARKETING AND SALES - BİRİZ NUTS</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Çal, Denizli, Türkiye</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>88 applicants</t>
+          <t>103 applicants</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -22138,39 +22138,39 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>BİRİZ KURUYEMİŞ</t>
+          <t>Göymen Makarna</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>1305153</t>
+          <t>1306470</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1305153</t>
+          <t>https://aiesec.org/opportunity/global-talent/1306470</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>ACE Program | Spanish Talent Acquisition Specialist</t>
+          <t>MARKETING AND SALES - BİRİZ NUTS</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Çal, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>79 applicants</t>
+          <t>88 applicants</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -22180,71 +22180,71 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>BİRİZ KURUYEMİŞ</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1304736</t>
+          <t>1305153</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304736</t>
+          <t>https://aiesec.org/opportunity/global-talent/1305153</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Hotel Entertainer</t>
+          <t>ACE Program | Spanish Talent Acquisition Specialist</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Heraklion, Greece</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>247 applicants</t>
+          <t>79 applicants</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Remarc Internation</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>1304488</t>
+          <t>1304736</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304488</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304736</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Client Consultant | Tourism Sector (German /Dutch speaker) ( Flexible RE dates )</t>
+          <t>Hotel Entertainer</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Athens, Greece</t>
+          <t>Heraklion, Greece</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -22254,39 +22254,39 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>98 applicants</t>
+          <t>247 applicants</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>SpeakIT</t>
+          <t>Remarc Internation</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1304076</t>
+          <t>1304488</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304076</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304488</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES - TOSUNOĞLU</t>
+          <t>Client Consultant | Tourism Sector (German /Dutch speaker) ( Flexible RE dates )</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Honaz, Denizli, Türkiye</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -22296,39 +22296,39 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>88 applicants</t>
+          <t>98 applicants</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>TOSUNOĞLU TEKSTİL SANAYİ VE TİC.A.Ş.</t>
+          <t>SpeakIT</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1303857</t>
+          <t>1304076</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1303857</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304076</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
+          <t>MARKETING &amp; SALES - TOSUNOĞLU</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
+          <t>Honaz, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>166 applicants</t>
+          <t>88 applicants</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -22348,19 +22348,19 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>TOSUNOĞLU TEKSTİL SANAYİ VE TİC.A.Ş.</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1303853</t>
+          <t>1303857</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1303853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1303857</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>137 applicants</t>
+          <t>166 applicants</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -22397,22 +22397,22 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1299853</t>
+          <t>1303853</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1299853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1303853</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
+          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Porto Alegre, RS, Brasil</t>
+          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -22422,39 +22422,39 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>158 applicants</t>
+          <t>137 applicants</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>ESCOLA GIORDANO BRUNO LTDA</t>
+          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1296457</t>
+          <t>1299853</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1296457</t>
+          <t>https://aiesec.org/opportunity/global-talent/1299853</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Sales Engineering</t>
+          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Dilovası, Türkiye</t>
+          <t>Porto Alegre, RS, Brasil</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -22464,49 +22464,49 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>209 applicants</t>
+          <t>158 applicants</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Eurotray Metal Elektrik Company</t>
+          <t>ESCOLA GIORDANO BRUNO LTDA</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1295935</t>
+          <t>1297124</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1295935</t>
+          <t>https://aiesec.org/opportunity/global-talent/1297124</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Business Development/HD</t>
+          <t>ACE Program | Portuguese Talent Acquisition Specialist</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Pamukkale, Türkiye</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>210 applicants</t>
+          <t>58 applicants</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -22516,29 +22516,29 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>HD Kauçuk Sanayi ve Tic. Anonim Şirketi</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1289378</t>
+          <t>1296457</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296457</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Medical Advisor (Spanish Speaker)</t>
+          <t>Sales Engineering</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Dilovası, Türkiye</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>147 applicants</t>
+          <t>209 applicants</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -22558,29 +22558,29 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Eurotray Metal Elektrik Company</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1289377</t>
+          <t>1295935</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
+          <t>https://aiesec.org/opportunity/global-talent/1295935</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Medical Advisor (Italian Speaker)</t>
+          <t>Business Development/HD</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Pamukkale, Türkiye</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>210 applicants</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -22600,24 +22600,24 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>HD Kauçuk Sanayi ve Tic. Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1289375</t>
+          <t>1289378</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289375</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Medical Advisor (German Speaker)</t>
+          <t>Medical Advisor (Spanish Speaker)</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>147 applicants</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -22649,40 +22649,124 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
+          <t>1289377</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Medical Advisor (Italian Speaker)</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>İstanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>46 applicants</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>6 - 18 Months</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>International Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>1289375</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://aiesec.org/opportunity/global-talent/1289375</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Medical Advisor (German Speaker)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>İstanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>46 applicants</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>6 - 18 Months</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>International Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
           <t>1288548</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B532" t="inlineStr">
         <is>
           <t>https://aiesec.org/opportunity/global-talent/1288548</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C532" t="inlineStr">
         <is>
           <t>Market Researcher/Sales Assistant on Ergün Özen Machine</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
+      <c r="D532" t="inlineStr">
         <is>
           <t>Honaz, Türkiye</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F530" t="inlineStr">
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
         <is>
           <t>176 applicants</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
+      <c r="G532" t="inlineStr">
         <is>
           <t>6 - 18 Months</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
+      <c r="H532" t="inlineStr">
         <is>
           <t>ERGÜN ÖZEN MACHINA</t>
         </is>

--- a/Yesterday.xlsx
+++ b/Yesterday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,22 +473,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1316550</t>
+          <t>1338050</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1316550</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338050</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACE Program | Voice Spanish Translator</t>
+          <t>[EXP NL] Data Analytics, Visualization &amp; AI Analyst</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal, India</t>
+          <t>Maastricht, Netherlands</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>DHL Group</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,22 +557,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1322238</t>
+          <t>1316550</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322238</t>
+          <t>https://aiesec.org/opportunity/global-talent/1316550</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OneERP Management Support</t>
+          <t>ACE Program | Voice Spanish Translator</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>Kolkata, West Bengal, India</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>606 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -592,39 +592,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ALFA LAVAL</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1338050</t>
+          <t>1338029</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338050</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338029</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[EXP NL] Data Analytics, Visualization &amp; AI Analyst</t>
+          <t>SCM Process Innovation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maastricht, Netherlands</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -634,24 +634,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DHL Group</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1338029</t>
+          <t>1338028</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338029</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338028</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SCM Process Innovation</t>
+          <t>Patient Support Program Analyst</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,29 +676,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Merck Group Panamá</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1338028</t>
+          <t>1338025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338028</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Patient Support Program Analyst</t>
+          <t>[Impact Brazil] - E-Commerce and International Trade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Uberlândia, MG, Brasil</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,39 +708,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Merck Group Panamá</t>
+          <t>PAT E-Commerce &amp; International Trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1338025</t>
+          <t>1337996</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338025</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337996</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - E-Commerce and International Trade</t>
+          <t>Informational Technology Intern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Uberlândia, MG, Brasil</t>
+          <t>Serres, Greece</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -760,24 +760,24 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PAT E-Commerce &amp; International Trade</t>
+          <t>POLIECO HELLAS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1337996</t>
+          <t>1337995</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337996</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337995</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Informational Technology Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1337995</t>
+          <t>1337973</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337995</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337973</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Sales at GEMSA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Serres, Greece</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -844,29 +844,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>POLIECO HELLAS</t>
+          <t>GEMSA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1337973</t>
+          <t>1337964</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337973</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337964</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sales at GEMSA</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,34 +876,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>GEMSA</t>
+          <t>Merck Group Panamá</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1337964</t>
+          <t>1337963</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337964</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337963</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>37 applicants</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -928,29 +928,29 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Merck Group Panamá</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1337963</t>
+          <t>1337959</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337963</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337959</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -970,19 +970,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1337959</t>
+          <t>1337958</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337959</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337958</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1019,22 +1019,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1337958</t>
+          <t>1337938</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337958</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337938</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Graphic Designer Intern - Mid term</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1044,34 +1044,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1337938</t>
+          <t>1337937</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337938</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337937</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Graphic Designer Intern - Mid term</t>
+          <t>Graphic Designer Intern - Short Term</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1337937</t>
+          <t>1337886</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337937</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337886</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Graphic Designer Intern - Short Term</t>
+          <t>IT Research Interns (Duplicated) (Duplicated) (Duplicated)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Aronj, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1128,39 +1128,39 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>FS University</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1337886</t>
+          <t>1337880</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337886</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337880</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IT Research Interns (Duplicated) (Duplicated) (Duplicated)</t>
+          <t>Practical training on market research and product promotion in Asian countries</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aronj, Uttar Pradesh, India</t>
+          <t>日本、神奈川県藤沢市</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1170,39 +1170,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FS University</t>
+          <t>NISSEI ECO CO.,LTD.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1337880</t>
+          <t>1337879</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337880</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337879</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Practical training on market research and product promotion in Asian countries</t>
+          <t>IT Research Interns (Duplicated) (Duplicated)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>日本、神奈川県藤沢市</t>
+          <t>Aronj, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1212,39 +1212,39 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NISSEI ECO CO.,LTD.</t>
+          <t>FS University</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1337879</t>
+          <t>1337878</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337879</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337878</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IT Research Interns (Duplicated) (Duplicated)</t>
+          <t>Training on Care Product Utilization Models for Addressing Aging Population Challenges in Home Countries</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aronj, Uttar Pradesh, India</t>
+          <t>日本、大阪府東大阪市</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1254,39 +1254,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FS University</t>
+          <t>Yamatoyo Sangyo Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1337878</t>
+          <t>1337875</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337878</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337875</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Training on Care Product Utilization Models for Addressing Aging Population Challenges in Home Countries</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>日本、大阪府東大阪市</t>
+          <t>Ankara, Türkiye</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1296,39 +1296,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Yamatoyo Sangyo Co., Ltd.</t>
+          <t>Akın Global Medikal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1337875</t>
+          <t>1337867</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337875</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337867</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Practical training in engaging web design in a manufacturing company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ankara, Türkiye</t>
+          <t>日本、神奈川県藤沢市</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1338,39 +1338,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Akın Global Medikal</t>
+          <t>NISSEI ECO CO.,LTD.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1337867</t>
+          <t>1337863</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337867</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337863</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Practical training in engaging web design in a manufacturing company</t>
+          <t>Social Media Specialist</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>日本、神奈川県藤沢市</t>
+          <t>中国广东省深圳市龙岗区</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1380,39 +1380,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NISSEI ECO CO.,LTD.</t>
+          <t>Keychron</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1337863</t>
+          <t>1337859</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337863</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337859</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Social Media Specialist</t>
+          <t>Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>中国广东省深圳市龙岗区</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1422,39 +1422,39 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>42 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Keychron</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1337859</t>
+          <t>1337857</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337859</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337857</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>Charneca de Caparica, Portugal</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>67 applicants</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1474,29 +1474,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Indústria dos Óculos</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1337857</t>
+          <t>1337844</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337857</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337844</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Tourism Specialist - Intern</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Charneca de Caparica, Portugal</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1506,39 +1506,39 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>63 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Indústria dos Óculos</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1337844</t>
+          <t>1337809</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337844</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337809</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tourism Specialist - Intern</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Aluthgama, Sri Lanka</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1548,39 +1548,39 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Diyakawa Water Sports Centre Bentota</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1337809</t>
+          <t>1337808</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337809</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337808</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Sales &amp; Impact Trainee</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aluthgama, Sri Lanka</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1590,39 +1590,39 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>56 applicants</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Diyakawa Water Sports Centre Bentota</t>
+          <t>Shayp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1337808</t>
+          <t>1337797</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337808</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337797</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sales &amp; Impact Trainee</t>
+          <t>Sales Representitive</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
+          <t>Istanbul, İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1642,29 +1642,29 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Shayp</t>
+          <t>Aksan Kozmetik</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1337797</t>
+          <t>1337794</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337797</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337794</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sales Representitive</t>
+          <t>Accelerate Romania | Photographer &amp; Videographer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Istanbul, İstanbul, Türkiye</t>
+          <t>Cotnari, Romania</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1674,34 +1674,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Aksan Kozmetik</t>
+          <t>SC CRAMELE COTNARI SA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1337794</t>
+          <t>1337793</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337794</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337793</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Photographer &amp; Videographer</t>
+          <t>Accelerate Romania | Graphic Designer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1733,22 +1733,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1337793</t>
+          <t>1337789</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337793</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337789</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Graphic Designer</t>
+          <t>Medical Affairs Trainee</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cotnari, Romania</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1758,39 +1758,39 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>37 applicants</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SC CRAMELE COTNARI SA</t>
+          <t>Novartis Pharma Logistics, Panama</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1337789</t>
+          <t>1337775</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337789</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337775</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Affairs Trainee</t>
+          <t>Front Office Manager</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Ella, Sri Lanka</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1800,39 +1800,39 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Novartis Pharma Logistics, Panama</t>
+          <t>Area 4 Eco Cubes - Ella</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1337775</t>
+          <t>1337774</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337775</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337774</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Front Office Manager</t>
+          <t>Web Developer Intern</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ella, Sri Lanka</t>
+          <t>Thessaloniki, Greece</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1842,39 +1842,39 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>80 applicants</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Area 4 Eco Cubes - Ella</t>
+          <t>Educational Leadership Association</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1337774</t>
+          <t>1337764</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337774</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337764</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Web Developer Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thessaloniki, Greece</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1884,39 +1884,39 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>78 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Educational Leadership Association</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1337764</t>
+          <t>1337761</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337764</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337761</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Export Manager Assistant</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>İzmir, Türkiye</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>70 applicants</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>27 applicants</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>143 applicants</t>
+          <t>148 applicants</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>42 applicants</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>34 applicants</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>126 applicants</t>
+          <t>130 applicants</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30 applicants</t>
+          <t>32 applicants</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>56 applicants</t>
+          <t>59 applicants</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>59 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>57 applicants</t>
+          <t>59 applicants</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3371,22 +3371,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1337387</t>
+          <t>1337389</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337387</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337389</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Junior software developer - Security</t>
+          <t>[Impact Brazil] - Sales Development Intern (LATAM)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Maringá, PR, Brasil</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3396,34 +3396,34 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>ANYMARKET TECHNOLOGIES</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1337373</t>
+          <t>1337387</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337373</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337387</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Analytics</t>
+          <t>Junior software developer - Security</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1337372</t>
+          <t>1337373</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337372</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337373</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Backend</t>
+          <t>Junior Software Engineer – Analytics</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3497,17 +3497,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1337371</t>
+          <t>1337372</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337371</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337372</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Devops</t>
+          <t>Junior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3539,17 +3539,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1337367</t>
+          <t>1337371</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337367</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337371</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Human Capital Associate – Talent,Payroll,Engagement &amp; Development</t>
+          <t>Junior Software Engineer – Devops</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3581,17 +3581,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1337363</t>
+          <t>1337367</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337363</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337367</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Security</t>
+          <t>Human Capital Associate – Talent,Payroll,Engagement &amp; Development</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3623,17 +3623,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1337362</t>
+          <t>1337363</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337362</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337363</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Junior Software Engineer –UI/UX</t>
+          <t>Junior Software Engineer – Security</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3665,17 +3665,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1337336</t>
+          <t>1337362</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337336</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337362</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Marketing Associate - Content</t>
+          <t>Junior Software Engineer –UI/UX</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3707,17 +3707,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1337335</t>
+          <t>1337336</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337335</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337336</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Marketing Associate - Design</t>
+          <t>Marketing Associate - Content</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3749,17 +3749,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1337333</t>
+          <t>1337335</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337333</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337335</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Marketing Associate - Digital</t>
+          <t>Marketing Associate - Design</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3791,17 +3791,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1337332</t>
+          <t>1337333</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337332</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337333</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Junior Product Associate</t>
+          <t>Marketing Associate - Digital</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1337331</t>
+          <t>1337332</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337331</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337332</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Accounts &amp; Finance Associate</t>
+          <t>Junior Product Associate</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3875,22 +3875,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1337298</t>
+          <t>1337331</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337298</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337331</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Marketing &amp; Retail Intern</t>
+          <t>Accounts &amp; Finance Associate</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3900,39 +3900,39 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>93 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1337297</t>
+          <t>1337298</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337297</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337298</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[Accelerate Serbia] Architectural Intern</t>
+          <t>Marketing &amp; Retail Intern</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3942,39 +3942,39 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>95 applicants</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ARHIM</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1337278</t>
+          <t>1337297</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337278</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337297</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Financial Planning Analyst</t>
+          <t>[Accelerate Serbia] Architectural Intern</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3984,39 +3984,39 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>PSA Panama International Terminal, S.A.</t>
+          <t>ARHIM</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1337254</t>
+          <t>1337278</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337254</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337278</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AI Design &amp; Creative Automation</t>
+          <t>Financial Planning Analyst</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4026,39 +4026,39 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>58 applicants</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>HEDS</t>
+          <t>PSA Panama International Terminal, S.A.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1337248</t>
+          <t>1337254</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337248</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337254</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Public Relations and Marketing</t>
+          <t>AI Design &amp; Creative Automation</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Dehradun, Uttarakhand, India</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4078,29 +4078,29 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Cyber College Educational Society</t>
+          <t>HEDS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1337243</t>
+          <t>1337248</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337248</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Medical Advisor (Serbian Speaker)</t>
+          <t>Public Relations and Marketing</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Dehradun, Uttarakhand, India</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4110,34 +4110,34 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Cyber College Educational Society</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1337242</t>
+          <t>1337243</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Medical Advisor (Bulgarian Speaker)</t>
+          <t>Medical Advisor (Serbian Speaker)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4169,17 +4169,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1337242</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Medical Advisor (Czech Speaker)</t>
+          <t>Medical Advisor (Bulgarian Speaker)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4211,22 +4211,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1337237</t>
+          <t>1337241</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337237</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Medical Advisor (Czech Speaker)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Kartepe, Kocaeli, Türkiye</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4246,29 +4246,29 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>RHİNO TANK</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1337230</t>
+          <t>1337237</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337230</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337237</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Kartepe, Kocaeli, Türkiye</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4278,34 +4278,34 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>63 applicants</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>RHİNO TANK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1337229</t>
+          <t>1337230</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337229</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337230</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4337,12 +4337,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1337228</t>
+          <t>1337229</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337228</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337229</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4379,17 +4379,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1337227</t>
+          <t>1337228</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337228</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4421,22 +4421,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1337220</t>
+          <t>1337227</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337220</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junio Business Administrator / General Manager</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Piatra Neamț, Romania</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4446,39 +4446,39 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>30 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>SC LAPOOL SRL</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1337215</t>
+          <t>1337220</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337215</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337220</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Accelerate Romania | Junio Business Administrator / General Manager</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Piatra Neamț, Romania</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4498,29 +4498,29 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ARMEKA</t>
+          <t>SC LAPOOL SRL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1337213</t>
+          <t>1337215</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337213</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337215</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Junior RevOps Specialist</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Utrecht, Netherlands</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4530,39 +4530,39 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>97 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>MRIGuidance</t>
+          <t>ARMEKA</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1337200</t>
+          <t>1337213</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337200</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337213</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SEO specialist</t>
+          <t>Junior RevOps Specialist</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4572,34 +4572,34 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>99 applicants</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>AL MAQSD</t>
+          <t>MRIGuidance</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1337199</t>
+          <t>1337200</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337199</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337200</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Social Media Content Creator / Content Strategist</t>
+          <t>SEO specialist</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4631,22 +4631,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1337158</t>
+          <t>1337199</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337199</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>Social Media Content Creator / Content Strategist</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>38 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4666,29 +4666,29 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Dirim Metal Anonim Şirketi</t>
+          <t>AL MAQSD</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1337147</t>
+          <t>1337158</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337147</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Architecture Engineer</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4698,39 +4698,39 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MAAP Electro-Mechanical Engineers</t>
+          <t>Dirim Metal Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1337107</t>
+          <t>1337147</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337107</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337147</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Business Development &amp; Research Intern (Green Agenda / EU Funds)</t>
+          <t>Architecture Engineer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4750,29 +4750,29 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>TOMRA COLLECTION</t>
+          <t>MAAP Electro-Mechanical Engineers</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1337103</t>
+          <t>1337107</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337107</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Education Coordinator</t>
+          <t>Business Development &amp; Research Intern (Green Agenda / EU Funds)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4792,29 +4792,29 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
+          <t>TOMRA COLLECTION</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1337100</t>
+          <t>1337103</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Education Coordinator</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4824,29 +4824,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>43 applicants</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1337099</t>
+          <t>1337100</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337099</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1337098</t>
+          <t>1337099</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337098</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337099</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4925,22 +4925,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1336989</t>
+          <t>1337098</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336989</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337098</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Social Media Campaign Manager (German Speaker)</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4950,34 +4950,34 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Ashdud</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1336982</t>
+          <t>1336989</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336982</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336989</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Telemarketing Specialist (German Speaker)</t>
+          <t>Social Media Campaign Manager (German Speaker)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5009,22 +5009,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1336949</t>
+          <t>1336982</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336949</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336982</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Robotics and Automation Intern</t>
+          <t>Telemarketing Specialist (German Speaker)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ambala, Haryana, India</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5034,39 +5034,39 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Ashdud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1336922</t>
+          <t>1336949</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336922</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336949</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sales Representitve</t>
+          <t>Robotics and Automation Intern</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Istanbul, İstanbul, Türkiye</t>
+          <t>Ambala, Haryana, India</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5076,39 +5076,39 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>79 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>KARTEK PASLANMAZ DEMİR İNŞAAT TAAHHÜT SANAYİ VE TİCARET LİMİ</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1336921</t>
+          <t>1336922</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336921</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336922</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>International Sales Representative</t>
+          <t>Sales Representitve</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4780 Santo Tirso, Portugal</t>
+          <t>Istanbul, İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5118,39 +5118,39 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>82 applicants</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CS Plastic</t>
+          <t>KARTEK PASLANMAZ DEMİR İNŞAAT TAAHHÜT SANAYİ VE TİCARET LİMİ</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1336909</t>
+          <t>1336921</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336909</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336921</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Environment Business Development Manager</t>
+          <t>International Sales Representative</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>4780 Santo Tirso, Portugal</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5170,24 +5170,24 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>E.C.O</t>
+          <t>CS Plastic</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1336902</t>
+          <t>1336909</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336902</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336909</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Operations Coordinator [6 Weeks]</t>
+          <t>Environment Business Development Manager</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5212,29 +5212,29 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Infinitum Network Solutions</t>
+          <t>E.C.O</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1336846</t>
+          <t>1336902</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336846</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336902</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Process Engineering Intern – AEC Workflows</t>
+          <t>Operations Coordinator [6 Weeks]</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Satu Mare, Romania</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5254,29 +5254,29 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Parametric Design Solutions</t>
+          <t>Infinitum Network Solutions</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1336845</t>
+          <t>1336846</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336845</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336846</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Junior Sales Development Representative</t>
+          <t>Accelerate Romania - Process Engineering Intern – AEC Workflows</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sibiu, Romania</t>
+          <t>Satu Mare, Romania</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>36 applicants</t>
+          <t>23 applicants</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5296,29 +5296,29 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ATUM Marketing</t>
+          <t>Parametric Design Solutions</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1336833</t>
+          <t>1336845</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336845</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AI &amp; ML Engineering Intern</t>
+          <t>Accelerate Romania - Junior Sales Development Representative</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Sibiu, Romania</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5328,39 +5328,39 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>58 applicants</t>
+          <t>37 applicants</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Altria Consulting (PVT) LTD</t>
+          <t>ATUM Marketing</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1336821</t>
+          <t>1336833</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336821</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336833</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Game Design Intern</t>
+          <t>AI &amp; ML Engineering Intern</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5370,39 +5370,39 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>58 applicants</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Altria Consulting (PVT) LTD</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1336818</t>
+          <t>1336821</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336818</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336821</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ai Intern</t>
+          <t>Game Design Intern</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5422,29 +5422,29 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Shivalik Institute of Real Estate</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1336766</t>
+          <t>1336818</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336766</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336818</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Social Media Marketing Intern (Mandatory Interns only)</t>
+          <t>Ai Intern</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Berlin, Deutschland</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5454,39 +5454,39 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>119 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Voicari GmbH</t>
+          <t>Shivalik Institute of Real Estate</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1336749</t>
+          <t>1336766</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336749</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336766</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Mirai Consumer Analysis</t>
+          <t>Social Media Marketing Intern (Mandatory Interns only)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Berlin, Deutschland</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5496,39 +5496,39 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>122 applicants</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Voicari GmbH</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1336719</t>
+          <t>1336749</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336719</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336749</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Junior Full Stack Developer</t>
+          <t>Mirai Consumer Analysis</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Suceava, Romania</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5548,29 +5548,29 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Poligon Tech SRL</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1336691</t>
+          <t>1336719</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336691</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336719</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Volunteer Management Intern</t>
+          <t>Accelerate Romania - Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Suceava, Romania</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sanjeevani - Life beyond cancer</t>
+          <t>Poligon Tech SRL</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1336689</t>
+          <t>1336691</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336689</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336691</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Community Management Intern</t>
+          <t>Volunteer Management Intern</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5639,17 +5639,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1336688</t>
+          <t>1336689</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336688</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336689</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Research Intern</t>
+          <t>Community Management Intern</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5681,22 +5681,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1336676</t>
+          <t>1336688</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336676</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336688</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Marketing &amp; Social Media Management Intern| Accelerate Romania</t>
+          <t>Research Intern</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Craiova, România</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5716,29 +5716,29 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>NOSCE GROUP</t>
+          <t>Sanjeevani - Life beyond cancer</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1336655</t>
+          <t>1336676</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336655</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336676</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Application Development Intern</t>
+          <t>Marketing &amp; Social Media Management Intern| Accelerate Romania</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Craiova, România</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5758,29 +5758,29 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sanjeevani - Life beyond cancer</t>
+          <t>NOSCE GROUP</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1336522</t>
+          <t>1336655</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336522</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336655</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Guest Relations Intern</t>
+          <t>Application Development Intern</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5790,34 +5790,34 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Welcomhotel by ITC Hotels Mohali Chandigarh</t>
+          <t>Sanjeevani - Life beyond cancer</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1336514</t>
+          <t>1336522</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336514</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336522</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Food and Beverage Service Intern</t>
+          <t>Guest Relations Intern</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5849,22 +5849,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1336453</t>
+          <t>1336514</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336453</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336514</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Animator/Video Editor</t>
+          <t>Food and Beverage Service Intern</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>El Sadat City, Menofia Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5874,39 +5874,39 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Organix (1)</t>
+          <t>Welcomhotel by ITC Hotels Mohali Chandigarh</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1336432</t>
+          <t>1336453</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336432</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336453</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Content Creator and Engagement Intern</t>
+          <t>Animator/Video Editor</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>São Miguel do Oeste, SC, 89900-000, Brasil</t>
+          <t>El Sadat City, Menofia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5926,29 +5926,29 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>KNN Idiomas</t>
+          <t>Organix (1)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1336404</t>
+          <t>1336432</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336432</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Performance &amp; Entertainment Intern</t>
+          <t>[Impact Brazil] - Content Creator and Engagement Intern</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>São Miguel do Oeste, SC, 89900-000, Brasil</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5958,39 +5958,39 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Starbeans Ceylon (Pvt ) Ltd</t>
+          <t>KNN Idiomas</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1336380</t>
+          <t>1336404</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336380</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Business Development Executive</t>
+          <t>Performance &amp; Entertainment Intern</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>NETGAINS</t>
+          <t>Starbeans Ceylon (Pvt ) Ltd</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1336369</t>
+          <t>1336380</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336369</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336380</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Business Development Executive</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6042,39 +6042,39 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>NETGAINS</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1336367</t>
+          <t>1336369</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336367</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336369</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6094,29 +6094,29 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>GloWebMark GWM</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1336365</t>
+          <t>1336367</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336365</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336367</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -6136,29 +6136,29 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>GloWebMark GWM</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1336314</t>
+          <t>1336365</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336314</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336365</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Finance Intern</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6178,24 +6178,24 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>The Address</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1336312</t>
+          <t>1336314</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336312</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336314</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Business Administration Intern</t>
+          <t>Finance Intern</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -6227,22 +6227,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1336276</t>
+          <t>1336312</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336276</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336312</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Accelerate Romania - International Research Internship in Wine Tourism &amp; Wine Studies (Database Development)</t>
+          <t>Business Administration Intern</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6262,24 +6262,24 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Babeș-Bolyai University</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1336275</t>
+          <t>1336276</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336275</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336276</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Accelerate Romania - International Research Internship in Hospitality &amp; Tourism Surveys</t>
+          <t>Accelerate Romania - International Research Internship in Wine Tourism &amp; Wine Studies (Database Development)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6311,17 +6311,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1336274</t>
+          <t>1336275</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336274</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336275</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Design of negotiation and conflict management simulations</t>
+          <t>Accelerate Romania - International Research Internship in Hospitality &amp; Tourism Surveys</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6353,17 +6353,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1336271</t>
+          <t>1336274</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336271</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336274</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Engagement &amp; innovation role in sustainability research projects</t>
+          <t>Accelerate Romania - Design of negotiation and conflict management simulations</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6395,22 +6395,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1336245</t>
+          <t>1336271</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336245</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336271</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Front Office Admin</t>
+          <t>Accelerate Romania - Engagement &amp; innovation role in sustainability research projects</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6420,39 +6420,39 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Seven Oaks Pet Hospital</t>
+          <t>Babeș-Bolyai University</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1336170</t>
+          <t>1336245</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336170</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336245</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Marketing and Sales Intern</t>
+          <t>Front Office Admin</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Malabe, Sri Lanka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6462,39 +6462,39 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Nova Solutions (pvt) Ltd</t>
+          <t>Seven Oaks Pet Hospital</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1336164</t>
+          <t>1336170</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336164</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336170</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Marketing and Sales Intern</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Malabe, Sri Lanka</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6504,39 +6504,39 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>ÇRZ KURUYEMİŞ MAKİNALARI TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Nova Solutions (pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1336151</t>
+          <t>1336164</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336164</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AI Internship</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6546,39 +6546,39 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>ÇRZ KURUYEMİŞ MAKİNALARI TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1336115</t>
+          <t>1336151</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336115</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Law Research Intern</t>
+          <t>AI Internship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Sohna, Haryana 122103, India</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6598,24 +6598,24 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>K.R. Mangalam University</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1336113</t>
+          <t>1336115</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336113</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336115</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>International Accounting Research Intern</t>
+          <t>Law Research Intern</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6647,17 +6647,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1336108</t>
+          <t>1336113</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336113</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Full Stack Development Research Intern</t>
+          <t>International Accounting Research Intern</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6689,17 +6689,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1336106</t>
+          <t>1336108</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336106</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Research Intern</t>
+          <t>Full Stack Development Research Intern</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6731,22 +6731,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1336076</t>
+          <t>1336106</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336076</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336106</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Medical Information Solutions Trainee</t>
+          <t>Artificial Intelligence Research Intern</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Bruxelles, Belgio</t>
+          <t>Sohna, Haryana 122103, India</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6756,39 +6756,39 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>K.R. Mangalam University</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1336045</t>
+          <t>1336104</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336045</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336104</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Motion Graphics Designer</t>
+          <t>Finance Research Intern</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Sohna, Haryana 122103, India</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6798,17 +6798,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>NOYO For Cosmetics</t>
+          <t>K.R. Mangalam University</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>56 applicants</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>90 applicants</t>
+          <t>92 applicants</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>128 applicants</t>
+          <t>129 applicants</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>79 applicants</t>
+          <t>82 applicants</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>242 applicants</t>
+          <t>243 applicants</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>76 applicants</t>
+          <t>77 applicants</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>110 applicants</t>
+          <t>114 applicants</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>77 applicants</t>
+          <t>78 applicants</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>80 applicants</t>
+          <t>81 applicants</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>67 applicants</t>
+          <t>68 applicants</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>70 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>119 applicants</t>
+          <t>121 applicants</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>249 applicants</t>
+          <t>250 applicants</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>70 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>50 applicants</t>
+          <t>51 applicants</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>151 applicants</t>
+          <t>153 applicants</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -14543,22 +14543,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1330393</t>
+          <t>1330158</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330393</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330158</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>[Impact in Belo Horizonte] - Business Development</t>
+          <t>Partnership &amp; Capacity Building Analyst Development Specialist</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Belo Horizonte, MG, Brasil</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -14568,34 +14568,34 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>111 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Group Tech Participações LTDA</t>
+          <t>Krishna Sadan</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1330158</t>
+          <t>1330157</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330158</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330157</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Partnership &amp; Capacity Building Analyst Development Specialist</t>
+          <t>Sustainability Outreach &amp; Community Development Specialist</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -14627,22 +14627,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1330157</t>
+          <t>1330102</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330157</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330102</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Sustainability Outreach &amp; Community Development Specialist</t>
+          <t>Accelerate Romania | Business Development Intern – External Expansion (POS) [GERMANY ONLY]</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Timișoara, Romania</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -14662,29 +14662,29 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Krishna Sadan</t>
+          <t>Vectron</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1330102</t>
+          <t>1330067</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330102</t>
+          <t>https://aiesec.org/opportunity/global-talent/1330067</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Business Development Intern – External Expansion (POS) [GERMANY ONLY]</t>
+          <t>Associate Program Manager (Eu Citizen Only)</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Timișoara, Romania</t>
+          <t>Bruxelles, Belgio</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -14694,39 +14694,39 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>75 applicants</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Vectron</t>
+          <t>The Synergist</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1330067</t>
+          <t>1329929</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1330067</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329929</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Associate Program Manager (Eu Citizen Only)</t>
+          <t>MARKETING &amp; SALES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Bruxelles, Belgio</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>74 applicants</t>
+          <t>56 applicants</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -14746,29 +14746,29 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>The Synergist</t>
+          <t>DOĞAN İNŞ.MLZM.HAFR.NAK.İŞ MAK.SAN.VE TİC.LTD.ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1329929</t>
+          <t>1329520</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329929</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329520</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES</t>
+          <t>Sales Officer</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -14778,39 +14778,39 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>56 applicants</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>DOĞAN İNŞ.MLZM.HAFR.NAK.İŞ MAK.SAN.VE TİC.LTD.ŞTİ.</t>
+          <t>Pedro Barn pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1329520</t>
+          <t>1329458</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329520</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329458</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Sales Officer</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
+          <t>Visakhapatnam, Andhra Pradesh, India</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -14820,34 +14820,34 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Pedro Barn pvt ltd</t>
+          <t>Media3 Training</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1329458</t>
+          <t>1329457</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329458</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329457</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>BA Intern</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -14879,22 +14879,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1329457</t>
+          <t>1329257</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329457</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329257</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>BA Intern</t>
+          <t>SALES MANAGER</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Visakhapatnam, Andhra Pradesh, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -14904,39 +14904,39 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>75 applicants</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Media3 Training</t>
+          <t>ALKA METAL</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1329257</t>
+          <t>1329177</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329257</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329177</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>SALES MANAGER</t>
+          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Porto Alegre, RS, Brazil</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -14946,39 +14946,39 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>74 applicants</t>
+          <t>113 applicants</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>ALKA METAL</t>
+          <t>ESCOLA GIORDANO BRUNO LTDA</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1329177</t>
+          <t>1329104</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329177</t>
+          <t>https://aiesec.org/opportunity/global-talent/1329104</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
+          <t>Sales Intern</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Porto Alegre, RS, Brazil</t>
+          <t>Pannipitiya, Sri Lanka</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -14988,39 +14988,39 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>113 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>ESCOLA GIORDANO BRUNO LTDA</t>
+          <t>Frella International</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1329104</t>
+          <t>1328792</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1329104</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328792</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Sales Intern</t>
+          <t>Accelerate Romania - Marketing Specialist</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Pannipitiya, Sri Lanka</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -15030,34 +15030,34 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>95 applicants</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Frella International</t>
+          <t>GIS Solutions</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1328792</t>
+          <t>1328768</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328792</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328768</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Marketing Specialist</t>
+          <t>Accelerate Romania - Digital Content Intern – Social Media &amp; Website</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>95 applicants</t>
+          <t>90 applicants</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -15082,29 +15082,29 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>GIS Solutions</t>
+          <t>Dog Assist</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1328768</t>
+          <t>1328685</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328768</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328685</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Digital Content Intern – Social Media &amp; Website</t>
+          <t>Medical Advisor (Russian Speaker)</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -15114,39 +15114,39 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>90 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Dog Assist</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1328685</t>
+          <t>1328549</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328685</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328549</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Medical Advisor (Russian Speaker)</t>
+          <t>Motion graphic design</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -15156,39 +15156,39 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>TAR - Company</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1328626</t>
+          <t>1328460</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328626</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328460</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Travel Advisory intern</t>
+          <t>Medical Advisor (Romanian Speaker)</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -15203,34 +15203,34 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Amaavi Luxe Travels</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1328549</t>
+          <t>1328091</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328549</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328091</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Motion graphic design</t>
+          <t>AI and IOT/ Machine Learning</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>35 applicants</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -15250,29 +15250,29 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>TAR - Company</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1328460</t>
+          <t>1328021</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328460</t>
+          <t>https://aiesec.org/opportunity/global-talent/1328021</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Medical Advisor (Romanian Speaker)</t>
+          <t>Guest Relations Officer Intern</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -15282,39 +15282,39 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>The Barn By Starbeans in Ella</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1328091</t>
+          <t>1327922</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328091</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327922</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>AI and IOT/ Machine Learning</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -15324,39 +15324,39 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>48 applicants</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Starbeans Ceylon (Pvt ) Ltd</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1328021</t>
+          <t>1327904</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1328021</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327904</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Guest Relations Officer Intern</t>
+          <t>UX Research Trainee</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Bruxelles, Belgio</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -15366,34 +15366,34 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>310 applicants</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>The Barn By Starbeans in Ella</t>
+          <t>UCB</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1327922</t>
+          <t>1327607</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327922</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327607</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Project Coordinator</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -15418,29 +15418,29 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Starbeans Ceylon (Pvt ) Ltd</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1327904</t>
+          <t>1327381</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327904</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327381</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>UX Research Trainee</t>
+          <t>Product Management Intern</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Bruxelles, Belgio</t>
+          <t>Ümraniye, Elmalıkent, 34764 Ümraniye/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -15450,39 +15450,39 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>308 applicants</t>
+          <t>189 applicants</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>ENTES ELEKTRONİK CİHAZLAR İMALAT VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1327607</t>
+          <t>1327300</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327607</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327300</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Project Coordinator</t>
+          <t>Language Specialist - French</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -15492,39 +15492,39 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Aitken Spence Travels (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1327381</t>
+          <t>1327154</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327381</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327154</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Product Management Intern</t>
+          <t>Guest Relations and Service Captain</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Ümraniye, Elmalıkent, 34764 Ümraniye/İstanbul, Türkiye</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -15534,39 +15534,39 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>187 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>ENTES ELEKTRONİK CİHAZLAR İMALAT VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Concu [Quenelle36 Foodworks Pvt. Ltd.]</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1327300</t>
+          <t>1327149</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327300</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327149</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Language Specialist - French</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -15576,39 +15576,39 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>47 applicants</t>
+          <t>146 applicants</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Aitken Spence Travels (Pvt) Ltd</t>
+          <t>Altria Consulting (PVT) LTD</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1327154</t>
+          <t>1327128</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327154</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327128</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Guest Relations and Service Captain</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Καλλιθέα 630 77, Ελλάδα</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -15618,39 +15618,39 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>101 applicants</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Concu [Quenelle36 Foodworks Pvt. Ltd.]</t>
+          <t>Respirotours</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1327149</t>
+          <t>1327106</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327149</t>
+          <t>https://aiesec.org/opportunity/global-talent/1327106</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sales Assistant (Spanish)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -15660,39 +15660,39 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>146 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Altria Consulting (PVT) LTD</t>
+          <t>Sera Moda</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1327128</t>
+          <t>1326767</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327128</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326767</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Καλλιθέα 630 77, Ελλάδα</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>100 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -15712,29 +15712,29 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Respirotours</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1327106</t>
+          <t>1326765</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1327106</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326765</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Sales Assistant (Spanish)</t>
+          <t>Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -15744,34 +15744,34 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Sera Moda</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1326767</t>
+          <t>1326761</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326767</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326761</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Civil Engineering Intern</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -15803,17 +15803,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1326765</t>
+          <t>1326757</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326765</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326757</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern</t>
+          <t>Architectural Intern</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -15845,17 +15845,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1326761</t>
+          <t>1326756</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326761</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326756</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Civil Engineering Intern</t>
+          <t>Electrical &amp; ML Intern</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -15887,22 +15887,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1326757</t>
+          <t>1326741</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326757</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326741</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Architectural Intern</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -15922,24 +15922,24 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Vigilare biopharma Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1326756</t>
+          <t>1326666</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326756</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326666</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Electrical &amp; ML Intern</t>
+          <t>Computer Engineering Intern</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -15971,22 +15971,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1326741</t>
+          <t>1326658</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326741</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326658</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Business Development Intern (Japanese Speaking Individuals Only)</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Malabe, Sri Lanka</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -15996,34 +15996,34 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>23 applicants</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Vigilare biopharma Pvt Ltd</t>
+          <t>Creative Technology Solutions (Private) Limited</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1326666</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326666</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326639</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Computer Engineering Intern</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -16055,22 +16055,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1326658</t>
+          <t>1326538</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326658</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326538</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Business Development Intern (Japanese Speaking Individuals Only)</t>
+          <t>[Impact in Belo Horizonte] - Digital Marketing</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Malabe, Sri Lanka</t>
+          <t>Belo Horizonte, MG, Brasil</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -16080,39 +16080,39 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>125 applicants</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Creative Technology Solutions (Private) Limited</t>
+          <t>Onfly</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1326639</t>
+          <t>1326081</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326639</t>
+          <t>https://aiesec.org/opportunity/global-talent/1326081</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Sales &amp; Marketing</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -16122,39 +16122,39 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>127 applicants</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>ASM Crane</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1326538</t>
+          <t>1325856</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326538</t>
+          <t>https://aiesec.org/opportunity/global-talent/1325856</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>[Impact in Belo Horizonte] - Digital Marketing</t>
+          <t>SALES ASSISTANT</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Belo Horizonte, MG, Brasil</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>125 applicants</t>
+          <t>88 applicants</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -16174,29 +16174,29 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Onfly</t>
+          <t>MULBERRY HOME</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1326081</t>
+          <t>1325297</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1326081</t>
+          <t>https://aiesec.org/opportunity/global-talent/1325297</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing</t>
+          <t>International Sales Representetive Spanish Speaker</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>126 applicants</t>
+          <t>48 applicants</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -16216,29 +16216,29 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>ASM Crane</t>
+          <t>Esvita Clinic</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1325856</t>
+          <t>1324676</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1325856</t>
+          <t>https://aiesec.org/opportunity/global-talent/1324676</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>SALES ASSISTANT</t>
+          <t>Motivational Speaker</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Nittambuwa, Sri Lanka</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -16248,39 +16248,39 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>88 applicants</t>
+          <t>35 applicants</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>MULBERRY HOME</t>
+          <t>Negombo South International School network</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1325297</t>
+          <t>1324350</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1325297</t>
+          <t>https://aiesec.org/opportunity/global-talent/1324350</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>International Sales Representetive Spanish Speaker</t>
+          <t>Inbound Tour Executive - Mid Term</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -16290,39 +16290,39 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Esvita Clinic</t>
+          <t>Trotter Escapes (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1324676</t>
+          <t>1324164</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1324676</t>
+          <t>https://aiesec.org/opportunity/global-talent/1324164</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Motivational Speaker</t>
+          <t>Receptionist/ Hostess</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Nittambuwa, Sri Lanka</t>
+          <t>Nuwara Eliya, Sri Lanka</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -16332,39 +16332,39 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>94 applicants</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Negombo South International School network</t>
+          <t>Pedro Barn pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1324350</t>
+          <t>1323714</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1324350</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323714</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Inbound Tour Executive - Mid Term</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Oporto, Portugal</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -16374,39 +16374,39 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>165 applicants</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Trotter Escapes (Pvt) Ltd</t>
+          <t>Obras Descomplicadas Lda</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1324164</t>
+          <t>1323507</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1324164</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323507</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Receptionist/ Hostess</t>
+          <t>Sales Intern</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Nuwara Eliya, Sri Lanka</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -16416,39 +16416,39 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>93 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Pedro Barn pvt ltd</t>
+          <t>Wavetec</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1323714</t>
+          <t>1323506</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323714</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323506</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Oporto, Portugal</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -16458,34 +16458,34 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>165 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Obras Descomplicadas Lda</t>
+          <t>Wavetec</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1323507</t>
+          <t>1323504</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323507</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323504</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Sales Intern</t>
+          <t>Management Trainee Officer</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>35 applicants</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -16517,17 +16517,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1323506</t>
+          <t>1323503</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323506</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323503</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Customer Support Engineer</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -16559,17 +16559,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1323504</t>
+          <t>1323391</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323504</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323391</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Management Trainee Officer</t>
+          <t>Business Development Officer</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>34 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -16601,22 +16601,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1323503</t>
+          <t>1323006</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323503</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323006</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Customer Support Engineer</t>
+          <t>OPERATIONS MANAGER</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Kaklık, 20240 Honaz/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>86 applicants</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -16636,29 +16636,29 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Wavetec</t>
+          <t>HEMMER MERMER MADENCİLİK İNŞAAT NAKLİYAT TURİZM İTHALAT İHRACAT SAN. VE TİC.LTD.ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1323391</t>
+          <t>1322716</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323391</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322716</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Business Development Officer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Eindhoven, Nederland</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>682 applicants</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -16678,29 +16678,29 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Wavetec</t>
+          <t>F19 Digital Reporting</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1323006</t>
+          <t>1322346</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323006</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322346</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>OPERATIONS MANAGER</t>
+          <t>Cyber Security and AI Intern</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Kaklık, 20240 Honaz/Denizli, Türkiye</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -16710,49 +16710,49 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>85 applicants</t>
+          <t>69 applicants</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>HEMMER MERMER MADENCİLİK İNŞAAT NAKLİYAT TURİZM İTHALAT İHRACAT SAN. VE TİC.LTD.ŞTİ.</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1322716</t>
+          <t>1322238</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322716</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322238</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>OneERP Management Support</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Eindhoven, Nederland</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>682 applicants</t>
+          <t>611 applicants</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -16762,29 +16762,29 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>F19 Digital Reporting</t>
+          <t>ALFA LAVAL</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1322346</t>
+          <t>1321910</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322346</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321910</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Cyber Security and AI Intern</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -16794,34 +16794,34 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>191 applicants</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Eman Agro Gıda</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1321910</t>
+          <t>1321840</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321910</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321840</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Marketing&amp;Sales</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>191 applicants</t>
+          <t>104 applicants</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -16846,24 +16846,24 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Eman Agro Gıda</t>
+          <t>Hak Makarna</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1321840</t>
+          <t>1321833</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321840</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321833</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Marketing&amp;Sales</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>104 applicants</t>
+          <t>135 applicants</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -16888,29 +16888,29 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Hak Makarna</t>
+          <t>MACRO SIGN REKLAM İÇ VE DIŞ TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1321833</t>
+          <t>1321796</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321796</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>MARKET RESARCH &amp; MARKETİNG | ŞAHİNLER MARBLE</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>134 applicants</t>
+          <t>97 applicants</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -16930,29 +16930,29 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>MACRO SIGN REKLAM İÇ VE DIŞ TİCARET LİMİTED ŞİRKETİ</t>
+          <t>ŞAHİNLER MARBLE</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1321796</t>
+          <t>1321450</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321796</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321450</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>MARKET RESARCH &amp; MARKETİNG | ŞAHİNLER MARBLE</t>
+          <t>Sales and Business Development Intern</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Jaipur, Rajasthan, India</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -16962,39 +16962,39 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>97 applicants</t>
+          <t>56 applicants</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>ŞAHİNLER MARBLE</t>
+          <t>www.Besteduonline.in (IPS Education &amp; Learning)</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1321450</t>
+          <t>1321055</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321450</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321055</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Sales and Business Development Intern</t>
+          <t>International Sales Representetive Italian Speaker</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Jaipur, Rajasthan, India</t>
+          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -17004,34 +17004,34 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>56 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>www.Besteduonline.in (IPS Education &amp; Learning)</t>
+          <t>Esvita Clinic</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1321055</t>
+          <t>1321053</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321055</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321053</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>International Sales Representetive Italian Speaker</t>
+          <t>International Sales Representetive German Speaker</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -17063,17 +17063,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1321053</t>
+          <t>1321052</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321053</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321052</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>International Sales Representetive German Speaker</t>
+          <t>International Sales Representetive</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>216 applicants</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -17105,22 +17105,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1321052</t>
+          <t>1317664</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321052</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317664</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>International Sales Representetive</t>
+          <t>SALES ATTENDED</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>216 applicants</t>
+          <t>68 applicants</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -17140,29 +17140,29 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Esvita Clinic</t>
+          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1317664</t>
+          <t>1317627</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317664</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317627</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>SALES ATTENDED</t>
+          <t>Corporate Partnerships Intern</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -17172,39 +17172,39 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Roligt Foods Pvt.Ltd</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1317627</t>
+          <t>1317170</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317627</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317170</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Corporate Partnerships Intern</t>
+          <t>Guest Relations Officer</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -17214,39 +17214,39 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>53 applicants</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Roligt Foods Pvt.Ltd</t>
+          <t>Lanka Island Resorts Ltd</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1317170</t>
+          <t>1316860</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317170</t>
+          <t>https://aiesec.org/opportunity/global-talent/1316860</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Guest Relations Officer</t>
+          <t>MARKET RESARCH &amp; MARKETİNG</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -17256,39 +17256,39 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>52 applicants</t>
+          <t>132 applicants</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Lanka Island Resorts Ltd</t>
+          <t>NR MARBLE DOĞALTAŞ PETROL İTH. İHR. SANAYİ VE TİC. LTD. ŞTİ</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1316860</t>
+          <t>1316551</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1316860</t>
+          <t>https://aiesec.org/opportunity/global-talent/1316551</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>MARKET RESARCH &amp; MARKETİNG</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>İzmit, Kocaeli, Türkiye</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>132 applicants</t>
+          <t>107 applicants</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -17308,29 +17308,29 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>NR MARBLE DOĞALTAŞ PETROL İTH. İHR. SANAYİ VE TİC. LTD. ŞTİ</t>
+          <t>Akademi Hastanesi</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1316551</t>
+          <t>1315961</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1316551</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315961</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Female Guest Relations Executive - Mid Term</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>İzmit, Kocaeli, Türkiye</t>
+          <t>Kandy, Sri Lanka</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -17340,39 +17340,39 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>107 applicants</t>
+          <t>31 applicants</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Akademi Hastanesi</t>
+          <t>Canora Hotels (pvt) Ltd Grand Kandyan Hotel</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1315961</t>
+          <t>1315189</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315961</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315189</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Female Guest Relations Executive - Mid Term</t>
+          <t>Associate Consultant Internship</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Kandy, Sri Lanka</t>
+          <t>Gurugram, Haryana, India</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>31 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -17392,29 +17392,29 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Canora Hotels (pvt) Ltd Grand Kandyan Hotel</t>
+          <t>Kanvic Consulting Private Limited</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1315189</t>
+          <t>1314902</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315189</t>
+          <t>https://aiesec.org/opportunity/global-talent/1314902</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Associate Consultant Internship</t>
+          <t>SALES &amp; MARKETING - ZİMEK MAKİNE</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -17424,34 +17424,34 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>66 applicants</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Kanvic Consulting Private Limited</t>
+          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1314902</t>
+          <t>1313381</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1314902</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313381</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SALES &amp; MARKETING - ZİMEK MAKİNE</t>
+          <t>Sales Attendant</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>66 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -17476,29 +17476,29 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
+          <t>VAROL TEKSTİL</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1313381</t>
+          <t>1313206</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313381</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313206</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Sales Attendant</t>
+          <t>Digital Media Strategist</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -17508,34 +17508,34 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>66 applicants</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>VAROL TEKSTİL</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1313206</t>
+          <t>1313204</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313206</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313204</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Digital Media Strategist</t>
+          <t>Digital Content Creator</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>66 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -17567,22 +17567,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1313204</t>
+          <t>1312624</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313204</t>
+          <t>https://aiesec.org/opportunity/global-talent/1312624</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Digital Content Creator</t>
+          <t>MARKET RESEARCH/ANALYST</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -17592,39 +17592,39 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>142 applicants</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>YAŞALAR KALIP YEDEK PARÇA SANAYİ VE TİCARET LTD.ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1312624</t>
+          <t>1310418</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1312624</t>
+          <t>https://aiesec.org/opportunity/global-talent/1310418</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>MARKET RESEARCH/ANALYST</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>141 applicants</t>
+          <t>126 applicants</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -17644,29 +17644,29 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>YAŞALAR KALIP YEDEK PARÇA SANAYİ VE TİCARET LTD.ŞTİ.</t>
+          <t>HÜNER</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1310418</t>
+          <t>1308897</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1310418</t>
+          <t>https://aiesec.org/opportunity/global-talent/1308897</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>125 applicants</t>
+          <t>94 applicants</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -17686,29 +17686,29 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>HÜNER</t>
+          <t>İNOPLAST PLASTİK ENJEKSİYON KALIP</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1308897</t>
+          <t>1307772</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1308897</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307772</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>SALES and MARKETING - ZİMEK MAKİNE</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Kocabaş, 20330 Honaz/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>93 applicants</t>
+          <t>143 applicants</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -17728,29 +17728,29 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>İNOPLAST PLASTİK ENJEKSİYON KALIP</t>
+          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1307772</t>
+          <t>1307244</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307772</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SALES and MARKETING - ZİMEK MAKİNE</t>
+          <t>Robotics &amp; Automation</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Kocabaş, 20330 Honaz/Denizli, Türkiye</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -17760,39 +17760,39 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>143 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>ZİMEK MAKİNA MERMER SAN. ve TİC. LTD ŞTİ.</t>
+          <t>Kiet group of Institutions</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1307244</t>
+          <t>1307242</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Robotics &amp; Automation</t>
+          <t>Automotive Mechatronics</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Ghaziabad, India</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -17812,29 +17812,29 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Kiet group of Institutions</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1307242</t>
+          <t>1307150</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307150</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Automotive Mechatronics</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Ghaziabad, India</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -17844,39 +17844,39 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>47 applicants</t>
+          <t>114 applicants</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Göymen Makarna</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1307150</t>
+          <t>1306470</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307150</t>
+          <t>https://aiesec.org/opportunity/global-talent/1306470</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>MARKETING AND SALES - BİRİZ NUTS</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Çal, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>114 applicants</t>
+          <t>90 applicants</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -17896,29 +17896,29 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Göymen Makarna</t>
+          <t>BİRİZ KURUYEMİŞ</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1306470</t>
+          <t>1305239</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1306470</t>
+          <t>https://aiesec.org/opportunity/global-talent/1305239</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>MARKETING AND SALES - BİRİZ NUTS</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Çal, Denizli, Türkiye</t>
+          <t>Eskişehir, Türkiye</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>90 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -17938,29 +17938,29 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>BİRİZ KURUYEMİŞ</t>
+          <t>Esaysan Endüstriyel Metal Ürünleri Sanayi Ve Ticaret</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1305239</t>
+          <t>1304736</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1305239</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304736</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Hotel Entertainer</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Eskişehir, Türkiye</t>
+          <t>Heraklion, Greece</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -17970,39 +17970,39 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>257 applicants</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Esaysan Endüstriyel Metal Ürünleri Sanayi Ve Ticaret</t>
+          <t>Remarc Internation</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1304736</t>
+          <t>1304488</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304736</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304488</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hotel Entertainer</t>
+          <t>Client Consultant | Tourism Sector (German /Dutch speaker) ( Flexible RE dates )</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Heraklion, Greece</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -18012,39 +18012,39 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>257 applicants</t>
+          <t>101 applicants</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Remarc Internation</t>
+          <t>SpeakIT</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1304488</t>
+          <t>1304076</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304488</t>
+          <t>https://aiesec.org/opportunity/global-talent/1304076</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Client Consultant | Tourism Sector (German /Dutch speaker) ( Flexible RE dates )</t>
+          <t>MARKETING &amp; SALES - TOSUNOĞLU</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Athens, Greece</t>
+          <t>Honaz, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -18054,39 +18054,39 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>100 applicants</t>
+          <t>89 applicants</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>SpeakIT</t>
+          <t>TOSUNOĞLU TEKSTİL SANAYİ VE TİC.A.Ş.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1304076</t>
+          <t>1303857</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1304076</t>
+          <t>https://aiesec.org/opportunity/global-talent/1303857</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES - TOSUNOĞLU</t>
+          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Honaz, Denizli, Türkiye</t>
+          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>89 applicants</t>
+          <t>170 applicants</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -18106,19 +18106,19 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>TOSUNOĞLU TEKSTİL SANAYİ VE TİC.A.Ş.</t>
+          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1303857</t>
+          <t>1303853</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1303857</t>
+          <t>https://aiesec.org/opportunity/global-talent/1303853</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>169 applicants</t>
+          <t>142 applicants</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -18155,22 +18155,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1303853</t>
+          <t>1299853</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1303853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1299853</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
+          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
+          <t>Porto Alegre, RS, Brasil</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -18180,39 +18180,39 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>142 applicants</t>
+          <t>162 applicants</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>ESCOLA GIORDANO BRUNO LTDA</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1299853</t>
+          <t>1296051</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1299853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296051</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
+          <t>Sales Support Intern</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Porto Alegre, RS, Brasil</t>
+          <t>Panamá, Panama</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -18222,39 +18222,39 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>162 applicants</t>
+          <t>58 applicants</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>ESCOLA GIORDANO BRUNO LTDA</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1296051</t>
+          <t>1295935</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1296051</t>
+          <t>https://aiesec.org/opportunity/global-talent/1295935</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Sales Support Intern</t>
+          <t>Business Development/HD</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Panamá, Panama</t>
+          <t>Pamukkale, Türkiye</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>56 applicants</t>
+          <t>216 applicants</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -18274,29 +18274,29 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>HD Kauçuk Sanayi ve Tic. Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1295935</t>
+          <t>1289379</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1295935</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289379</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Business Development/HD</t>
+          <t>Medical Advisor Portuguese Speaker</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Pamukkale, Türkiye</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>215 applicants</t>
+          <t>138 applicants</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -18316,24 +18316,24 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>HD Kauçuk Sanayi ve Tic. Anonim Şirketi</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1289379</t>
+          <t>1289378</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289379</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Medical Advisor Portuguese Speaker</t>
+          <t>Medical Advisor (Spanish Speaker)</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>138 applicants</t>
+          <t>150 applicants</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -18365,17 +18365,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1289378</t>
+          <t>1289377</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Medical Advisor (Spanish Speaker)</t>
+          <t>Medical Advisor (Italian Speaker)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>150 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -18407,17 +18407,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1289377</t>
+          <t>1289375</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289375</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Medical Advisor (Italian Speaker)</t>
+          <t>Medical Advisor (German Speaker)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>47 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -18449,22 +18449,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1289375</t>
+          <t>1288548</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289375</t>
+          <t>https://aiesec.org/opportunity/global-talent/1288548</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Medical Advisor (German Speaker)</t>
+          <t>Market Researcher/Sales Assistant on Ergün Özen Machine</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Honaz, Türkiye</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>180 applicants</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -18483,48 +18483,6 @@
         </is>
       </c>
       <c r="H430" t="inlineStr">
-        <is>
-          <t>International Plus</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>1288548</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>https://aiesec.org/opportunity/global-talent/1288548</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>Market Researcher/Sales Assistant on Ergün Özen Machine</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>Honaz, Türkiye</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>180 applicants</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>6 - 18 Months</t>
-        </is>
-      </c>
-      <c r="H431" t="inlineStr">
         <is>
           <t>ERGÜN ÖZEN MACHINA</t>
         </is>

--- a/Yesterday.xlsx
+++ b/Yesterday.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76 applicants</t>
+          <t>86 applicants</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>85 applicants</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,22 +599,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1338098</t>
+          <t>1338112</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338098</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338112</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[Dutch Speaker] Business Development Intern</t>
+          <t>Junior Geospatial analyst</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Coagh, UK</t>
+          <t>Novi Sad, Serbia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -624,39 +624,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>DataDEV</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1338080</t>
+          <t>1338098</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338080</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338098</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Italian-Speaking Purchasing &amp; Negotiation Specialist (EU Citizenship Required) (Duplicated)</t>
+          <t>[Dutch Speaker] Business Development Intern</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Constanța, Romania</t>
+          <t>Coagh, UK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,29 +676,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Veo Wordwide Services - Iași</t>
+          <t>F5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1338068</t>
+          <t>1338080</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338068</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338080</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AI Media Transformation Intern (EU ONLY)</t>
+          <t>Accelerate Romania | Italian-Speaking Purchasing &amp; Negotiation Specialist (EU Citizenship Required) (Duplicated)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Schiphol, Netherlands</t>
+          <t>Constanța, Romania</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -718,24 +718,24 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Vestacy</t>
+          <t>Veo Wordwide Services - Iași</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1338067</t>
+          <t>1338068</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338067</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338068</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Social Media &amp; Creator Insights Intern (EU ONLY)</t>
+          <t>AI Media Transformation Intern (EU ONLY)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -767,22 +767,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1338064</t>
+          <t>1338067</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338064</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338067</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Accounting Trainee (EU ONLY)</t>
+          <t>Social Media &amp; Creator Insights Intern (EU ONLY)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amsterdam, Netherlands</t>
+          <t>Schiphol, Netherlands</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -802,29 +802,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Volkswagen International Finance N.V.</t>
+          <t>Vestacy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1338049</t>
+          <t>1338064</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338049</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338064</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Financial Accounting Trainee (EU ONLY)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Çal, Denizli, Türkiye</t>
+          <t>Amsterdam, Netherlands</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -844,29 +844,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ELİTEPRİME SEEDS GIDA SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Volkswagen International Finance N.V.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1338046</t>
+          <t>1338049</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338046</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338049</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Front-end Developer</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Timișoara, România</t>
+          <t>Çal, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,34 +876,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Webchain</t>
+          <t>ELİTEPRİME SEEDS GIDA SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1338045</t>
+          <t>1338046</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338045</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338046</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Back-end Developer</t>
+          <t>Accelerate Romania | Front-end Developer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -935,22 +935,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1338029</t>
+          <t>1338045</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338029</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338045</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SCM Process Innovation</t>
+          <t>Accelerate Romania | Back-end Developer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Timișoara, România</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -960,34 +960,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Webchain</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1338028</t>
+          <t>1338029</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338028</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338029</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patient Support Program Analyst</t>
+          <t>SCM Process Innovation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1012,29 +1012,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Merck Group Panamá</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1338025</t>
+          <t>1338028</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338025</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338028</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - E-Commerce and International Trade</t>
+          <t>Patient Support Program Analyst</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Uberlândia, MG, Brasil</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1044,39 +1044,39 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PAT E-Commerce &amp; International Trade</t>
+          <t>Merck Group Panamá</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1338017</t>
+          <t>1338025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338017</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>[Impact Brazil] - E-Commerce and International Trade</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ahangama, Sri Lanka</t>
+          <t>Uberlândia, MG, Brasil</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1086,39 +1086,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cassius Investments pvt ltd</t>
+          <t>PAT E-Commerce &amp; International Trade</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1337996</t>
+          <t>1338017</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337996</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338017</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Informational Technology Intern</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Serres, Greece</t>
+          <t>Ahangama, Sri Lanka</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1128,34 +1128,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>POLIECO HELLAS</t>
+          <t>Cassius Investments pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1337995</t>
+          <t>1337996</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337995</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337996</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Informational Technology Intern</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1337983</t>
+          <t>1337995</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337983</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337995</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[Partly Remote] Controlling Analyst HP 2026</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Santiago, Región Metropolitana, Chile</t>
+          <t>Serres, Greece</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1212,39 +1212,39 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Partly Remote</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim in Chile</t>
+          <t>POLIECO HELLAS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1337973</t>
+          <t>1337983</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337973</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337983</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sales at GEMSA</t>
+          <t>[Partly Remote] Controlling Analyst HP 2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Santiago, Región Metropolitana, Chile</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1254,39 +1254,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>Partly Remote</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>GEMSA</t>
+          <t>Boehringer Ingelheim in Chile</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1337964</t>
+          <t>1337973</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337964</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337973</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Sales at GEMSA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1296,34 +1296,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Merck Group Panamá</t>
+          <t>GEMSA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1337963</t>
+          <t>1337964</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337963</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337964</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46 applicants</t>
+          <t>34 applicants</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1348,29 +1348,29 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Merck Group Panamá</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1337959</t>
+          <t>1337963</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337959</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337963</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>48 applicants</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1390,19 +1390,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1337958</t>
+          <t>1337959</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337958</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337959</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1439,22 +1439,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1337938</t>
+          <t>1337958</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337938</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337958</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Graphic Designer Intern - Mid term</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1337937</t>
+          <t>1337938</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337937</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337938</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Graphic Designer Intern - Short Term</t>
+          <t>Graphic Designer Intern - Mid term</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1523,22 +1523,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1337886</t>
+          <t>1337937</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337886</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337937</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IT Research Interns (Duplicated) (Duplicated) (Duplicated)</t>
+          <t>Graphic Designer Intern - Short Term</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aronj, Uttar Pradesh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1548,34 +1548,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>FS University</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1337879</t>
+          <t>1337886</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337879</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337886</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IT Research Interns (Duplicated) (Duplicated)</t>
+          <t>IT Research Interns (Duplicated) (Duplicated) (Duplicated)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1607,22 +1607,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1337878</t>
+          <t>1337879</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337878</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337879</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Training on Care Product Utilization Models for Addressing Aging Population Challenges in Home Countries</t>
+          <t>IT Research Interns (Duplicated) (Duplicated)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>日本、大阪府東大阪市</t>
+          <t>Aronj, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1632,39 +1632,39 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Yamatoyo Sangyo Co., Ltd.</t>
+          <t>FS University</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1337875</t>
+          <t>1337878</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337875</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337878</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Training on Care Product Utilization Models for Addressing Aging Population Challenges in Home Countries</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ankara, Türkiye</t>
+          <t>日本、大阪府東大阪市</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1674,39 +1674,39 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Akın Global Medikal</t>
+          <t>Yamatoyo Sangyo Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1337863</t>
+          <t>1337875</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337863</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337875</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Social Media Specialist</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>中国广东省深圳市龙岗区</t>
+          <t>Ankara, Türkiye</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1716,39 +1716,39 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>42 applicants</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Keychron</t>
+          <t>Akın Global Medikal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1337859</t>
+          <t>1337863</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337859</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337863</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern</t>
+          <t>Social Media Specialist</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>中国广东省深圳市龙岗区</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1758,39 +1758,39 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Keychron</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1337857</t>
+          <t>1337859</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337857</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337859</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Charneca de Caparica, Portugal</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1810,29 +1810,29 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Indústria dos Óculos</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1337844</t>
+          <t>1337857</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337844</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337857</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tourism Specialist - Intern</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Charneca de Caparica, Portugal</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1842,39 +1842,39 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>74 applicants</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Indústria dos Óculos</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1337833</t>
+          <t>1337844</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337844</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Tourism Specialist - Intern</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1894,29 +1894,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1337809</t>
+          <t>1337833</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337809</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337833</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aluthgama, Sri Lanka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1926,39 +1926,39 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Diyakawa Water Sports Centre Bentota</t>
+          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1337808</t>
+          <t>1337809</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337808</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337809</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sales &amp; Impact Trainee</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
+          <t>Aluthgama, Sri Lanka</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1968,39 +1968,39 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>58 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Shayp</t>
+          <t>Diyakawa Water Sports Centre Bentota</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1337797</t>
+          <t>1337808</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337797</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337808</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sales Representitive</t>
+          <t>Sales &amp; Impact Trainee</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Istanbul, İstanbul, Türkiye</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>60 applicants</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2020,29 +2020,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Aksan Kozmetik</t>
+          <t>Shayp</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1337794</t>
+          <t>1337797</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337794</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337797</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Photographer &amp; Videographer</t>
+          <t>Sales Representitive</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cotnari, Romania</t>
+          <t>Istanbul, İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2052,34 +2052,34 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>60 applicants</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SC CRAMELE COTNARI SA</t>
+          <t>Aksan Kozmetik</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1337793</t>
+          <t>1337794</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337793</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337794</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Graphic Designer</t>
+          <t>Accelerate Romania | Photographer &amp; Videographer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2111,22 +2111,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1337789</t>
+          <t>1337793</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337789</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337793</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Medical Affairs Trainee</t>
+          <t>Accelerate Romania | Graphic Designer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Cotnari, Romania</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Novartis Pharma Logistics, Panama</t>
+          <t>SC CRAMELE COTNARI SA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1337775</t>
+          <t>1337789</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337775</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337789</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Front Office Manager</t>
+          <t>Medical Affairs Trainee</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ella, Sri Lanka</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2178,39 +2178,39 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Area 4 Eco Cubes - Ella</t>
+          <t>Novartis Pharma Logistics, Panama</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1337774</t>
+          <t>1337775</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337774</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337775</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Web Developer Intern</t>
+          <t>Front Office Manager</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thessaloniki, Greece</t>
+          <t>Ella, Sri Lanka</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2220,39 +2220,39 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Educational Leadership Association</t>
+          <t>Area 4 Eco Cubes - Ella</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1337764</t>
+          <t>1337774</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337764</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337774</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Web Developer Intern</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Thessaloniki, Greece</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2262,39 +2262,39 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>57 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Educational Leadership Association</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1337761</t>
+          <t>1337764</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337761</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337764</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Export Manager Assistant</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>İzmir, Türkiye</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>60 applicants</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2314,29 +2314,29 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1337748</t>
+          <t>1337761</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337748</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337761</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOCIAL MEDIA MARKETING</t>
+          <t>Export Manager Assistant</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kütahya, Kütahya Merkez/Kütahya, Türkiye</t>
+          <t>İzmir, Türkiye</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2346,39 +2346,39 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>EFEOĞLU BAKLAVA</t>
+          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1337723</t>
+          <t>1337748</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337723</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337748</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UX/UI Designer</t>
+          <t>SOCIAL MEDIA MARKETING</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Charneca de Caparica, Portugal</t>
+          <t>Kütahya, Kütahya Merkez/Kütahya, Türkiye</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2398,29 +2398,29 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Indústria dos Óculos</t>
+          <t>EFEOĞLU BAKLAVA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1337665</t>
+          <t>1337723</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337665</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337723</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chief Corporate Strategy and Administration Officer</t>
+          <t>UX/UI Designer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Charneca de Caparica, Portugal</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2430,39 +2430,39 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30 applicants</t>
+          <t>23 applicants</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Indian Kitchen (Pvt) Ltd</t>
+          <t>Indústria dos Óculos</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1337660</t>
+          <t>1337665</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337660</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337665</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Clinical Operations Coordinator Trainee</t>
+          <t>Chief Corporate Strategy and Administration Officer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2472,34 +2472,34 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>Indian Kitchen (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1337649</t>
+          <t>1337660</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337649</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337660</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Clinical Study Operations Trainee</t>
+          <t>Clinical Operations Coordinator Trainee</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>34 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2531,22 +2531,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1337628</t>
+          <t>1337649</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337628</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337649</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Food and Beverage Trainee</t>
+          <t>Clinical Study Operations Trainee</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2566,29 +2566,29 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Park Hotel International Limited</t>
+          <t>UCB</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1337625</t>
+          <t>1337628</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337625</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337628</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Physiotherapy Intern</t>
+          <t>Food and Beverage Trainee</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Multan, Pakistan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2598,34 +2598,34 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Barki Complex</t>
+          <t>Park Hotel International Limited</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1337624</t>
+          <t>1337625</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337624</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337625</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Web Development Intern</t>
+          <t>Physiotherapy Intern</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2657,17 +2657,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1337622</t>
+          <t>1337624</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337622</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337624</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Social Media Marketing Intern</t>
+          <t>Web Development Intern</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2699,22 +2699,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1337613</t>
+          <t>1337622</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337613</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337622</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Social Media Marketing Intern</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cyberjaya, Selangor, Malaysia</t>
+          <t>Multan, Pakistan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2724,39 +2724,39 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>132 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>IX Telecom Sdn Bhd</t>
+          <t>Barki Complex</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1337608</t>
+          <t>1337613</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337608</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337613</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Android Software Engineer</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aveiro, Portugal</t>
+          <t>Cyberjaya, Selangor, Malaysia</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2766,39 +2766,39 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>132 applicants</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Softi9</t>
+          <t>IX Telecom Sdn Bhd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1337603</t>
+          <t>1337608</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337603</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337608</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Corporate &amp; Media Finance Intern</t>
+          <t>Android Software Engineer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Aveiro, Portugal</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2808,39 +2808,39 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nestle Panama</t>
+          <t>Softi9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1337572</t>
+          <t>1337603</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337572</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337603</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>People &amp; Organization Trainee</t>
+          <t>Corporate &amp; Media Finance Intern</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Panama City, Panamá Province, Panama</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65 applicants</t>
+          <t>62 applicants</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2860,29 +2860,29 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Novartis Pharma Logistics, Panama</t>
+          <t>Nestle Panama</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1337537</t>
+          <t>1337572</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337537</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337572</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>People &amp; Organization Trainee</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Panama City, Panamá Province, Panama</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>65 applicants</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2902,19 +2902,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TBPART OTOMOTİV SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Novartis Pharma Logistics, Panama</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1337536</t>
+          <t>1337537</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337536</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337537</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2934,39 +2934,39 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Dirim Metal Anonim Şirketi</t>
+          <t>TBPART OTOMOTİV SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1337534</t>
+          <t>1337536</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337534</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337536</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Market Analysis and Strategy Formulation Aim to Launch  Hair Care Products in India</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>日本、東京都東京</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>47 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2986,29 +2986,29 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Milbon Co., Ltd.</t>
+          <t>Dirim Metal Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1337508</t>
+          <t>1337534</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337508</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337534</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junior Customer Success &amp; Activation Intern</t>
+          <t>Market Analysis and Strategy Formulation Aim to Launch  Hair Care Products in India</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Galați, Romania</t>
+          <t>日本、東京都東京</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3028,29 +3028,29 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CONTSCAPE TEC SRL</t>
+          <t>Milbon Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1337446</t>
+          <t>1337508</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337446</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337508</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sales Specialist</t>
+          <t>Accelerate Romania | Junior Customer Success &amp; Activation Intern</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Galați, Romania</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3060,34 +3060,34 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>CONTSCAPE TEC SRL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1337445</t>
+          <t>1337446</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337445</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337446</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Media Coverage</t>
+          <t>Sales Specialist</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3119,22 +3119,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1337443</t>
+          <t>1337445</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337443</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337445</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Media Coverage</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3144,39 +3144,39 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>PE-BA TEKSTİL</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1337435</t>
+          <t>1337443</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337435</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337443</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3186,39 +3186,39 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>62 applicants</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>QJ Design Studios (PVT) LTD</t>
+          <t>PE-BA TEKSTİL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1337434</t>
+          <t>1337435</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337434</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337435</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Customer Success Executive</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Córdoba, Argentina</t>
+          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3228,39 +3228,39 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>59 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Teleprom Argentina S.A</t>
+          <t>QJ Design Studios (PVT) LTD</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1337417</t>
+          <t>1337434</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337417</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337434</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Customer Success Executive</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Córdoba, Argentina</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3270,39 +3270,39 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>E.C.O</t>
+          <t>Teleprom Argentina S.A</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1337411</t>
+          <t>1337417</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337411</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337417</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Guest Experience Manager</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3312,39 +3312,39 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Indian Kitchen (Pvt) Ltd</t>
+          <t>E.C.O</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1337408</t>
+          <t>1337411</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337408</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337411</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Guest Experience Manager</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3364,24 +3364,24 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>Indian Kitchen (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1337407</t>
+          <t>1337408</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337407</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337408</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3413,17 +3413,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1337406</t>
+          <t>1337407</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337406</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337407</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1337403</t>
+          <t>1337406</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337403</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337406</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3497,17 +3497,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1337402</t>
+          <t>1337403</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337402</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337403</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3539,17 +3539,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1337400</t>
+          <t>1337402</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337400</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337402</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Media Coverage</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3581,17 +3581,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1337394</t>
+          <t>1337400</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337394</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337400</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Graphic designer</t>
+          <t>Media Coverage</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3623,17 +3623,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1337393</t>
+          <t>1337394</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337393</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337394</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Graphic designer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3665,17 +3665,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1337391</t>
+          <t>1337393</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337391</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337393</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3707,22 +3707,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1337389</t>
+          <t>1337391</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337389</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337391</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Sales Development Intern (LATAM)</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Maringá, PR, Brasil</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3732,39 +3732,39 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ANYMARKET TECHNOLOGIES</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1337388</t>
+          <t>1337389</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337388</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337389</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FP&amp;A Junior Analyst</t>
+          <t>[Impact Brazil] - Sales Development Intern (LATAM)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Maringá, PR, Brasil</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3784,29 +3784,29 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Signify N.V.</t>
+          <t>ANYMARKET TECHNOLOGIES</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1337387</t>
+          <t>1337388</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337387</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337388</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Junior software developer - Security</t>
+          <t>FP&amp;A Junior Analyst</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3816,34 +3816,34 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>Signify N.V.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1337373</t>
+          <t>1337387</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337373</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337387</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Analytics</t>
+          <t>Junior software developer - Security</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3875,17 +3875,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1337372</t>
+          <t>1337373</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337372</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337373</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Backend</t>
+          <t>Junior Software Engineer – Analytics</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3917,17 +3917,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1337371</t>
+          <t>1337372</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337371</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337372</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Devops</t>
+          <t>Junior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3959,17 +3959,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1337367</t>
+          <t>1337371</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337367</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337371</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Human Capital Associate – Talent,Payroll,Engagement &amp; Development</t>
+          <t>Junior Software Engineer – Devops</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4001,22 +4001,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1337366</t>
+          <t>1337367</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337366</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337367</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Human Capital Associate – Talent,Payroll,Engagement &amp; Development</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Zwolle, Nederland</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4026,39 +4026,39 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Webfin Holding B.V.</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1337363</t>
+          <t>1337366</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337363</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337366</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Security</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Zwolle, Nederland</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4068,34 +4068,34 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>Webfin Holding B.V.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1337362</t>
+          <t>1337363</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337362</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337363</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Junior Software Engineer –UI/UX</t>
+          <t>Junior Software Engineer – Security</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4127,17 +4127,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1337336</t>
+          <t>1337362</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337336</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337362</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Marketing Associate - Content</t>
+          <t>Junior Software Engineer –UI/UX</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4169,17 +4169,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1337335</t>
+          <t>1337336</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337335</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337336</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marketing Associate - Design</t>
+          <t>Marketing Associate - Content</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4211,22 +4211,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1337334</t>
+          <t>1337335</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337334</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337335</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Online Marketeer (German-speaking)</t>
+          <t>Marketing Associate - Design</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4236,39 +4236,39 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>SB Supply Europe</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1337333</t>
+          <t>1337334</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337333</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337334</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Marketing Associate - Digital</t>
+          <t>Online Marketeer (German-speaking)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Tilburg, Netherlands</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4278,34 +4278,34 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>SB Supply Europe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1337332</t>
+          <t>1337333</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337332</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337333</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Junior Product Associate</t>
+          <t>Marketing Associate - Digital</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4337,17 +4337,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1337331</t>
+          <t>1337332</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337331</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337332</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Accounts &amp; Finance Associate</t>
+          <t>Junior Product Associate</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4379,22 +4379,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1337298</t>
+          <t>1337331</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337298</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337331</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Marketing &amp; Retail Intern</t>
+          <t>Accounts &amp; Finance Associate</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4404,39 +4404,39 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>98 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1337297</t>
+          <t>1337298</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337297</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337298</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[Accelerate Serbia] Architectural Intern</t>
+          <t>Marketing &amp; Retail Intern</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4446,39 +4446,39 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>99 applicants</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ARHIM</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1337278</t>
+          <t>1337297</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337278</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337297</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Financial Planning Analyst</t>
+          <t>[Accelerate Serbia] Architectural Intern</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4488,39 +4488,39 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>63 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>PSA Panama International Terminal, S.A.</t>
+          <t>ARHIM</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1337254</t>
+          <t>1337278</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337254</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337278</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AI Design &amp; Creative Automation</t>
+          <t>Financial Planning Analyst</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4530,39 +4530,39 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>63 applicants</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>HEDS</t>
+          <t>PSA Panama International Terminal, S.A.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1337248</t>
+          <t>1337254</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337248</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337254</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Public Relations and Marketing</t>
+          <t>AI Design &amp; Creative Automation</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Dehradun, Uttarakhand, India</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4582,29 +4582,29 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Cyber College Educational Society</t>
+          <t>HEDS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1337244</t>
+          <t>1337248</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337244</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337248</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Export Specialist in Istanbul</t>
+          <t>Public Relations and Marketing</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Dehradun, Uttarakhand, India</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4614,34 +4614,34 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Akpa Aluminium</t>
+          <t>Cyber College Educational Society</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1337243</t>
+          <t>1337244</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337244</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Medical Advisor (Serbian Speaker)</t>
+          <t>Export Specialist in Istanbul</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4666,24 +4666,24 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Akpa Aluminium</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1337242</t>
+          <t>1337243</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Medical Advisor (Bulgarian Speaker)</t>
+          <t>Medical Advisor (Serbian Speaker)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4715,17 +4715,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1337242</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Medical Advisor (Czech Speaker)</t>
+          <t>Medical Advisor (Bulgarian Speaker)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4757,22 +4757,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1337237</t>
+          <t>1337241</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337237</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Medical Advisor (Czech Speaker)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Kartepe, Kocaeli, Türkiye</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>64 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4792,29 +4792,29 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>RHİNO TANK</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1337230</t>
+          <t>1337237</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337230</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337237</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Kartepe, Kocaeli, Türkiye</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4824,34 +4824,34 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>65 applicants</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>RHİNO TANK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1337229</t>
+          <t>1337230</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337229</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337230</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4883,12 +4883,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1337228</t>
+          <t>1337229</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337228</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337229</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4925,17 +4925,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1337227</t>
+          <t>1337228</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337228</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4967,22 +4967,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1337220</t>
+          <t>1337227</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337220</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junio Business Administrator / General Manager</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Piatra Neamț, Romania</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4992,39 +4992,39 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>30 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>SC LAPOOL SRL</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1337215</t>
+          <t>1337220</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337215</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337220</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MARKETING</t>
+          <t>Accelerate Romania | Junio Business Administrator / General Manager</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Piatra Neamț, Romania</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>31 applicants</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5044,29 +5044,29 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ARMEKA</t>
+          <t>SC LAPOOL SRL</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1337213</t>
+          <t>1337215</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337213</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337215</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Junior RevOps Specialist</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Utrecht, Netherlands</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5076,39 +5076,39 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>102 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>MRIGuidance</t>
+          <t>ARMEKA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1337200</t>
+          <t>1337213</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337200</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337213</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SEO specialist</t>
+          <t>Junior RevOps Specialist</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Utrecht, Netherlands</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5118,34 +5118,34 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>103 applicants</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>AL MAQSD</t>
+          <t>MRIGuidance</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1337199</t>
+          <t>1337200</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337199</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337200</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Social Media Content Creator / Content Strategist</t>
+          <t>SEO specialist</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5177,22 +5177,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1337158</t>
+          <t>1337199</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337199</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>Social Media Content Creator / Content Strategist</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5212,29 +5212,29 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Dirim Metal Anonim Şirketi</t>
+          <t>AL MAQSD</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1337147</t>
+          <t>1337158</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337147</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Architecture Engineer</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5244,39 +5244,39 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>MAAP Electro-Mechanical Engineers</t>
+          <t>Dirim Metal Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1337107</t>
+          <t>1337147</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337107</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337147</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Business Development &amp; Research Intern (Green Agenda / EU Funds)</t>
+          <t>Architecture Engineer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5296,29 +5296,29 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>TOMRA COLLECTION</t>
+          <t>MAAP Electro-Mechanical Engineers</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1337103</t>
+          <t>1337107</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337107</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Education Coordinator</t>
+          <t>Business Development &amp; Research Intern (Green Agenda / EU Funds)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Belgrade, Serbia</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5338,29 +5338,29 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
+          <t>TOMRA COLLECTION</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1337100</t>
+          <t>1337103</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Education Coordinator</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5370,29 +5370,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>45 applicants</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1337099</t>
+          <t>1337100</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337099</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5429,17 +5429,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1337098</t>
+          <t>1337099</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337098</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337099</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5471,22 +5471,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1336989</t>
+          <t>1337098</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336989</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337098</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Social Media Campaign Manager (German Speaker)</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5496,34 +5496,34 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Ashdud</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1336982</t>
+          <t>1336989</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336982</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336989</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Telemarketing Specialist (German Speaker)</t>
+          <t>Social Media Campaign Manager (German Speaker)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5555,22 +5555,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1336949</t>
+          <t>1336982</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336949</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336982</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Robotics and Automation Intern</t>
+          <t>Telemarketing Specialist (German Speaker)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ambala, Haryana, India</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5580,39 +5580,39 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Ashdud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1336922</t>
+          <t>1336949</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336922</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336949</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sales Representitve</t>
+          <t>Robotics and Automation Intern</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Istanbul, İstanbul, Türkiye</t>
+          <t>Ambala, Haryana, India</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5622,39 +5622,39 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>83 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>KARTEK PASLANMAZ DEMİR İNŞAAT TAAHHÜT SANAYİ VE TİCARET LİMİ</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1336921</t>
+          <t>1336922</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336921</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336922</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>International Sales Representative</t>
+          <t>Sales Representitve</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4780 Santo Tirso, Portugal</t>
+          <t>Istanbul, İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5664,39 +5664,39 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CS Plastic</t>
+          <t>KARTEK PASLANMAZ DEMİR İNŞAAT TAAHHÜT SANAYİ VE TİCARET LİMİ</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1336909</t>
+          <t>1336921</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336909</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336921</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Environment Business Development Manager</t>
+          <t>International Sales Representative</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>4780 Santo Tirso, Portugal</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>73 applicants</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5716,24 +5716,24 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>E.C.O</t>
+          <t>CS Plastic</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1336902</t>
+          <t>1336909</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336902</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336909</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Operations Coordinator [6 Weeks]</t>
+          <t>Environment Business Development Manager</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5758,29 +5758,29 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Infinitum Network Solutions</t>
+          <t>E.C.O</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1336846</t>
+          <t>1336902</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336846</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336902</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Process Engineering Intern – AEC Workflows</t>
+          <t>Operations Coordinator [6 Weeks]</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Satu Mare, Romania</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5800,29 +5800,29 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Parametric Design Solutions</t>
+          <t>Infinitum Network Solutions</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1336845</t>
+          <t>1336846</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336845</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336846</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Junior Sales Development Representative</t>
+          <t>Accelerate Romania - Process Engineering Intern – AEC Workflows</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sibiu, Romania</t>
+          <t>Satu Mare, Romania</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>23 applicants</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5842,29 +5842,29 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ATUM Marketing</t>
+          <t>Parametric Design Solutions</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1336833</t>
+          <t>1336845</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336845</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AI &amp; ML Engineering Intern</t>
+          <t>Accelerate Romania - Junior Sales Development Representative</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Sibiu, Romania</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5874,39 +5874,39 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>37 applicants</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Altria Consulting (PVT) LTD</t>
+          <t>ATUM Marketing</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1336821</t>
+          <t>1336833</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336821</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336833</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Game Design Intern</t>
+          <t>AI &amp; ML Engineering Intern</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5916,39 +5916,39 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>63 applicants</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Altria Consulting (PVT) LTD</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1336818</t>
+          <t>1336821</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336818</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336821</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ai Intern</t>
+          <t>Game Design Intern</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5968,29 +5968,29 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Shivalik Institute of Real Estate</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1336766</t>
+          <t>1336818</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336766</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336818</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Social Media Marketing Intern (Mandatory Interns only)</t>
+          <t>Ai Intern</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Berlin, Deutschland</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6000,39 +6000,39 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>124 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Voicari GmbH</t>
+          <t>Shivalik Institute of Real Estate</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1336749</t>
+          <t>1336766</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336749</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336766</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mirai Consumer Analysis</t>
+          <t>Social Media Marketing Intern (Mandatory Interns only)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Berlin, Deutschland</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6042,39 +6042,39 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>125 applicants</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Voicari GmbH</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1336746</t>
+          <t>1336749</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336746</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336749</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Product manager (German-speaking)</t>
+          <t>Mirai Consumer Analysis</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6084,39 +6084,39 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>51 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Magneds</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1336719</t>
+          <t>1336746</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336719</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336746</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Junior Full Stack Developer</t>
+          <t>Product manager (German-speaking)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Suceava, Romania</t>
+          <t>Tilburg, Netherlands</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6126,39 +6126,39 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>71 applicants</t>
+          <t>51 applicants</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Poligon Tech SRL</t>
+          <t>Magneds</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1336691</t>
+          <t>1336719</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336691</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336719</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Volunteer Management Intern</t>
+          <t>Accelerate Romania - Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Suceava, Romania</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6178,24 +6178,24 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sanjeevani - Life beyond cancer</t>
+          <t>Poligon Tech SRL</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1336689</t>
+          <t>1336691</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336689</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336691</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Community Management Intern</t>
+          <t>Volunteer Management Intern</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -6227,17 +6227,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1336688</t>
+          <t>1336689</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336688</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336689</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Research Intern</t>
+          <t>Community Management Intern</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6269,22 +6269,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1336676</t>
+          <t>1336688</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336676</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336688</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Marketing &amp; Social Media Management Intern| Accelerate Romania</t>
+          <t>Research Intern</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Craiova, România</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6304,29 +6304,29 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>NOSCE GROUP</t>
+          <t>Sanjeevani - Life beyond cancer</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1336655</t>
+          <t>1336676</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336655</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336676</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Application Development Intern</t>
+          <t>Marketing &amp; Social Media Management Intern| Accelerate Romania</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Craiova, România</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>73 applicants</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6346,29 +6346,29 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sanjeevani - Life beyond cancer</t>
+          <t>NOSCE GROUP</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1336522</t>
+          <t>1336655</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336522</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336655</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Guest Relations Intern</t>
+          <t>Application Development Intern</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6378,34 +6378,34 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Welcomhotel by ITC Hotels Mohali Chandigarh</t>
+          <t>Sanjeevani - Life beyond cancer</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1336514</t>
+          <t>1336522</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336514</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336522</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Food and Beverage Service Intern</t>
+          <t>Guest Relations Intern</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6437,22 +6437,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1336453</t>
+          <t>1336514</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336453</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336514</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Animator/Video Editor</t>
+          <t>Food and Beverage Service Intern</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>El Sadat City, Menofia Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6462,39 +6462,39 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Organix (1)</t>
+          <t>Welcomhotel by ITC Hotels Mohali Chandigarh</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1336432</t>
+          <t>1336453</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336432</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336453</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Content Creator and Engagement Intern</t>
+          <t>Animator/Video Editor</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>São Miguel do Oeste, SC, 89900-000, Brasil</t>
+          <t>El Sadat City, Menofia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6514,29 +6514,29 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>KNN Idiomas</t>
+          <t>Organix (1)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1336404</t>
+          <t>1336432</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336432</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Performance &amp; Entertainment Intern</t>
+          <t>[Impact Brazil] - Content Creator and Engagement Intern</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>São Miguel do Oeste, SC, 89900-000, Brasil</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6546,39 +6546,39 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Starbeans Ceylon (Pvt ) Ltd</t>
+          <t>KNN Idiomas</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1336380</t>
+          <t>1336404</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336380</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336404</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Business Development Executive</t>
+          <t>Performance &amp; Entertainment Intern</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6598,29 +6598,29 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>NETGAINS</t>
+          <t>Starbeans Ceylon (Pvt ) Ltd</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1336369</t>
+          <t>1336380</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336369</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336380</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Business Development Executive</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6630,39 +6630,39 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>NETGAINS</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1336367</t>
+          <t>1336369</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336367</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336369</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>GloWebMark GWM</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1336365</t>
+          <t>1336367</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336365</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336367</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6724,29 +6724,29 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Fekretk</t>
+          <t>GloWebMark GWM</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1336314</t>
+          <t>1336365</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336314</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336365</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Finance Intern</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6766,24 +6766,24 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>The Address</t>
+          <t>Fekretk</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1336312</t>
+          <t>1336314</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336312</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336314</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Business Administration Intern</t>
+          <t>Finance Intern</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6815,22 +6815,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1336305</t>
+          <t>1336312</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336305</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336312</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>[Partly Remote] [Impact Brazil] - GTM Engineer Intern</t>
+          <t>Business Administration Intern</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>São Paulo, SP, Brasil</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6840,39 +6840,39 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Partly Remote</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Ecomiles</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1336276</t>
+          <t>1336305</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336276</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336305</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Accelerate Romania - International Research Internship in Wine Tourism &amp; Wine Studies (Database Development)</t>
+          <t>[Partly Remote] [Impact Brazil] - GTM Engineer Intern</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cluj-Napoca, Romania</t>
+          <t>São Paulo, SP, Brasil</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6882,34 +6882,34 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>Partly Remote</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Babeș-Bolyai University</t>
+          <t>Ecomiles</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1336275</t>
+          <t>1336276</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336275</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336276</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Accelerate Romania - International Research Internship in Hospitality &amp; Tourism Surveys</t>
+          <t>Accelerate Romania - International Research Internship in Wine Tourism &amp; Wine Studies (Database Development)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6941,17 +6941,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1336274</t>
+          <t>1336275</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336274</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336275</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Design of negotiation and conflict management simulations</t>
+          <t>Accelerate Romania - International Research Internship in Hospitality &amp; Tourism Surveys</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>41 applicants</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6983,17 +6983,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1336271</t>
+          <t>1336274</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336271</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336274</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Engagement &amp; innovation role in sustainability research projects</t>
+          <t>Accelerate Romania - Design of negotiation and conflict management simulations</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7025,22 +7025,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1336245</t>
+          <t>1336271</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336245</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336271</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Front Office Admin</t>
+          <t>Accelerate Romania - Engagement &amp; innovation role in sustainability research projects</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Cluj-Napoca, Romania</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7050,39 +7050,39 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Seven Oaks Pet Hospital</t>
+          <t>Babeș-Bolyai University</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1336170</t>
+          <t>1336245</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336170</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336245</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Marketing and Sales Intern</t>
+          <t>Front Office Admin</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Malabe, Sri Lanka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7092,39 +7092,39 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Nova Solutions (pvt) Ltd</t>
+          <t>Seven Oaks Pet Hospital</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1336164</t>
+          <t>1336170</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336164</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336170</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Marketing and Sales Intern</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Malabe, Sri Lanka</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7134,39 +7134,39 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ÇRZ KURUYEMİŞ MAKİNALARI TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Nova Solutions (pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1336151</t>
+          <t>1336164</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336164</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AI Internship</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7176,39 +7176,39 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>61 applicants</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>ÇRZ KURUYEMİŞ MAKİNALARI TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1336113</t>
+          <t>1336151</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336113</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336151</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>International Accounting Research Intern</t>
+          <t>AI Internship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sohna, Haryana 122103, India</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -7228,24 +7228,24 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>K.R. Mangalam University</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1336108</t>
+          <t>1336113</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336113</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Full Stack Development Research Intern</t>
+          <t>International Accounting Research Intern</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7277,17 +7277,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1336106</t>
+          <t>1336108</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336106</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336108</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Research Intern</t>
+          <t>Full Stack Development Research Intern</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7319,22 +7319,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1336043</t>
+          <t>1336106</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336043</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336106</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Media Buying Specialist</t>
+          <t>Artificial Intelligence Research Intern</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Sohna, Haryana 122103, India</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7344,39 +7344,39 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NOYO For Cosmetics</t>
+          <t>K.R. Mangalam University</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1335994</t>
+          <t>1336043</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335994</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336043</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Business developement</t>
+          <t>Digital Marketing &amp; Media Buying Specialist</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7386,39 +7386,39 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>NOYO For Cosmetics</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1335929</t>
+          <t>1335994</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335929</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335994</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Business developement</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7428,39 +7428,39 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>NOYO For Cosmetics</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1335925</t>
+          <t>1335929</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335925</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335929</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Digital Business &amp; Technology Intern</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Surat, Gujarat, India</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7470,39 +7470,39 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>37 applicants</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>AlignSoul Connect Pvt. Ltd</t>
+          <t>NOYO For Cosmetics</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1335911</t>
+          <t>1335925</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335911</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335925</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Guest Relations and Service Captain</t>
+          <t>Digital Business &amp; Technology Intern</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Surat, Gujarat, India</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7517,34 +7517,34 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
+          <t>AlignSoul Connect Pvt. Ltd</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1335803</t>
+          <t>1335911</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335803</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335911</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Customer Success Manager Germany</t>
+          <t>Guest Relations and Service Captain</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Eindhoven, Netherlands</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7554,39 +7554,39 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>59 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Returnless</t>
+          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1335757</t>
+          <t>1335803</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335757</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335803</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success Manager Germany</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Eindhoven, Netherlands</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>59 applicants</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7606,29 +7606,29 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sevinçler Sağlık Ürünleri</t>
+          <t>Returnless</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1335678</t>
+          <t>1335757</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335678</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335757</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Gampola, Sri Lanka</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7638,39 +7638,39 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
+          <t>Sevinçler Sağlık Ürünleri</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1335645</t>
+          <t>1335678</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335645</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335678</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Pharmacy Intern</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Rajpura, Punjab, India</t>
+          <t>Gampola, Sri Lanka</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>32 applicants</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7690,29 +7690,29 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Swami Vivekanand Institute of Engineering &amp; Technology</t>
+          <t>Blooming Buds Centre of Education (BBCE) College Internation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1335631</t>
+          <t>1335645</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335631</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335645</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>content creator</t>
+          <t>Pharmacy Intern</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tunis, Tunisie</t>
+          <t>Rajpura, Punjab, India</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7732,24 +7732,24 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>citywork Business Center</t>
+          <t>Swami Vivekanand Institute of Engineering &amp; Technology</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1335630</t>
+          <t>1335631</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335630</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335631</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>community manager</t>
+          <t>content creator</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7781,17 +7781,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1335629</t>
+          <t>1335630</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335629</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335630</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brand strategist</t>
+          <t>community manager</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7823,22 +7823,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1335628</t>
+          <t>1335629</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335628</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335629</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Digital Marketer</t>
+          <t>Brand strategist</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Rades, Tunisia</t>
+          <t>Tunis, Tunisie</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7858,29 +7858,29 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>AmazingPandph Digital Media Management</t>
+          <t>citywork Business Center</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1335624</t>
+          <t>1335628</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335624</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335628</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Communications Intern</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Tunis, Tunisia</t>
+          <t>Rades, Tunisia</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7900,29 +7900,29 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>EFFIOS</t>
+          <t>AmazingPandph Digital Media Management</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1335590</t>
+          <t>1335624</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1335590</t>
+          <t>https://aiesec.org/opportunity/global-talent/1335624</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Understanding Food Sales Management in Japan with Tenpei Co., Ltd.</t>
+          <t>Communications Intern</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>日本、滋賀県高島市</t>
+          <t>Tunis, Tunisia</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Tenpei Co., Ltd.</t>
+          <t>EFFIOS</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>150 applicants</t>
+          <t>151 applicants</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>94 applicants</t>
+          <t>95 applicants</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>30 applicants</t>
+          <t>31 applicants</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>117 applicants</t>
+          <t>118 applicants</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>81 applicants</t>
+          <t>83 applicants</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>69 applicants</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>122 applicants</t>
+          <t>123 applicants</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>255 applicants</t>
+          <t>256 applicants</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>74 applicants</t>
+          <t>75 applicants</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>311 applicants</t>
+          <t>312 applicants</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>688 applicants</t>
+          <t>690 applicants</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>623 applicants</t>
+          <t>630 applicants</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>115 applicants</t>
+          <t>116 applicants</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>84 applicants</t>
+          <t>85 applicants</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61 applicants</t>
+          <t>62 applicants</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">

--- a/Yesterday.xlsx
+++ b/Yesterday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,22 +473,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1338671</t>
+          <t>1305153</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338671</t>
+          <t>https://aiesec.org/opportunity/global-talent/1305153</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[CC] CEO &amp; CFO Communications Intern</t>
+          <t>ACE Program | Spanish Talent Acquisition Specialist</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Friedrich-Wilhelm-Straße 18, 53113 Bonn, Germany</t>
+          <t>Chennai, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78 applicants</t>
+          <t>84 applicants</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -508,29 +508,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DHL Group</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1305153</t>
+          <t>1338909</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1305153</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338909</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACE Program | Spanish Talent Acquisition Specialist</t>
+          <t>[EXP] Project Management and Reporting Data Specialist (Europe)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India</t>
+          <t>Schkeuditz, Germany</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,29 +550,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>DHL Group</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1338354</t>
+          <t>1338671</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338354</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338671</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[DGF] Inside Sales Intern l German Speaker</t>
+          <t>[CC] CEO &amp; CFO Communications Intern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mainz, Germany</t>
+          <t>Friedrich-Wilhelm-Straße 18, 53113 Bonn, Germany</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>94 applicants</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>14 applicants</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -725,22 +725,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1338812</t>
+          <t>1338814</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338812</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338814</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Planning Systems Trainee</t>
+          <t>Information Technology Intern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Breda, Hollandia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Perfetti van Melle</t>
+          <t>Innodays Business Management Limited</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1338784</t>
+          <t>1338812</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338784</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338812</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Creative Advertising Intern ( Mid Term)</t>
+          <t>Data Analytics &amp; Planning Systems Trainee</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Breda, Hollandia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -792,34 +792,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Luxuria Colombo (Pvt) Ltd</t>
+          <t>Perfetti van Melle</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1338782</t>
+          <t>1338784</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338782</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338784</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Creative Advertising Intern ( Short Term)</t>
+          <t>Creative Advertising Intern ( Mid Term)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -851,17 +851,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1338738</t>
+          <t>1338782</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338738</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338782</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Media &amp; Event Coordinator Intern ( Mid Term)</t>
+          <t>Creative Advertising Intern ( Short Term)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -893,17 +893,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1338737</t>
+          <t>1338738</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338737</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338738</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Media &amp; Event Coordinator Intern ( Short Term)</t>
+          <t>Media &amp; Event Coordinator Intern ( Mid Term)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -935,22 +935,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1338724</t>
+          <t>1338737</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338724</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338737</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Media &amp; Event Coordinator Intern ( Short Term)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -970,24 +970,24 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FiberCom</t>
+          <t>Luxuria Colombo (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1338723</t>
+          <t>1338725</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338723</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338725</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Media Buyer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1338722</t>
+          <t>1338724</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338722</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338724</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1061,22 +1061,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1338708</t>
+          <t>1338723</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338708</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338723</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sales Development Intern</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1086,39 +1086,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Web Lankan Global (Pvt) Ltd</t>
+          <t>FiberCom</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1338682</t>
+          <t>1338722</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338682</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338722</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>social media specialist</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1138,29 +1138,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Eureka pharmaceuticals</t>
+          <t>FiberCom</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1338681</t>
+          <t>1338708</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338681</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338708</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UI/UX Designer</t>
+          <t>Sales Development Intern</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1170,34 +1170,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Eureka pharmaceuticals</t>
+          <t>Web Lankan Global (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1338680</t>
+          <t>1338682</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338680</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338682</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UIUX Designer</t>
+          <t>social media specialist</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1338677</t>
+          <t>1338681</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338677</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338681</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>graphic designer</t>
+          <t>UI/UX Designer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1338676</t>
+          <t>1338680</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338676</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338680</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Data analysist</t>
+          <t>UIUX Designer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1313,22 +1313,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1338627</t>
+          <t>1338677</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338627</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338677</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sales Represantative</t>
+          <t>graphic designer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1338,39 +1338,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Enorm Teknoloji ve Yazılım Anonim Şirketi</t>
+          <t>Eureka pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1338619</t>
+          <t>1338676</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338619</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338676</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Product Management Senior Support</t>
+          <t>Data analysist</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1380,39 +1380,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Eureka pharmaceuticals</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1338602</t>
+          <t>1338627</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338602</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338627</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>social media specialist</t>
+          <t>Sales Represantative</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1422,29 +1422,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>43 applicants</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Techno Genius</t>
+          <t>Enorm Teknoloji ve Yazılım Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1338601</t>
+          <t>1338602</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338601</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338602</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1481,22 +1481,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1338585</t>
+          <t>1338601</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338585</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338601</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Furniture designer</t>
+          <t>social media specialist</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1516,24 +1516,24 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>kremastos</t>
+          <t>Techno Genius</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1338584</t>
+          <t>1338585</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338584</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338585</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Landscape designer</t>
+          <t>Furniture designer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1565,22 +1565,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1338581</t>
+          <t>1338584</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338581</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338584</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Preventive Maintenance in CNC Manufacturing</t>
+          <t>Landscape designer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31073 Delligsen, Deutschland</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1590,34 +1590,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bornemann Gewindetechnik</t>
+          <t>kremastos</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1338571</t>
+          <t>1338581</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338571</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338581</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product Catalog and Online Store</t>
+          <t>Preventive Maintenance in CNC Manufacturing</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>28 applicants</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1649,22 +1649,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1338560</t>
+          <t>1338571</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338560</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338571</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Product Catalog and Online Store</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>31073 Delligsen, Deutschland</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1674,39 +1674,39 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The Address</t>
+          <t>Bornemann Gewindetechnik</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1338546</t>
+          <t>1338560</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338546</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338560</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hotel Operations Intern</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1716,39 +1716,39 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tamarind Tree Garden Resort</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1338541</t>
+          <t>1338546</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338541</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338546</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marketing specialist</t>
+          <t>Hotel Operations Intern</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cairo, Cairo Governorate, Egypt</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1758,39 +1758,39 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Mega2M</t>
+          <t>Tamarind Tree Garden Resort</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1338536</t>
+          <t>1338541</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338536</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338541</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Voice Chat Product Operation - Spender</t>
+          <t>Marketing specialist</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>中国上海市黄浦区</t>
+          <t>Cairo, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1800,39 +1800,39 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PopUp</t>
+          <t>Mega2M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1338524</t>
+          <t>1338536</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338524</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338536</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Content &amp; Social Media Marketing Intern</t>
+          <t>Voice Chat Product Operation - Spender</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Unawatuna, Sri Lanka</t>
+          <t>中国上海市黄浦区</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1852,29 +1852,29 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Angel Beach Club Unawatuna</t>
+          <t>PopUp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1338521</t>
+          <t>1338524</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338521</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338524</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Robotics Intern</t>
+          <t>Content &amp; Social Media Marketing Intern</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Phagwara, Punjab, India</t>
+          <t>Unawatuna, Sri Lanka</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1894,24 +1894,24 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>GNA University</t>
+          <t>Angel Beach Club Unawatuna</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1338520</t>
+          <t>1338521</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338520</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338521</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Software Development Intern</t>
+          <t>Robotics Intern</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1338489</t>
+          <t>1338520</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338489</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338520</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Administrative Assistant (AI &amp; Digital Operations)</t>
+          <t>Software Development Intern</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Phagwara, Punjab, India</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1968,39 +1968,39 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>55 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Wong's Limited</t>
+          <t>GNA University</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1338484</t>
+          <t>1338489</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338484</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338489</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cloud Computing Intern</t>
+          <t>Administrative Assistant (AI &amp; Digital Operations)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Phagwara, Punjab, India</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2010,34 +2010,34 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>57 applicants</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>GNA University</t>
+          <t>Wong's Limited</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1338483</t>
+          <t>1338484</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338483</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338484</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyber Security Intern</t>
+          <t>Cloud Computing Intern</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2069,17 +2069,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1338482</t>
+          <t>1338483</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338482</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338483</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Cyber Security Intern</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2111,17 +2111,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1338481</t>
+          <t>1338482</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338481</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338482</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2153,17 +2153,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1338479</t>
+          <t>1338481</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338479</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338481</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Data Analyst Intern</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2195,22 +2195,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1338450</t>
+          <t>1338479</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338450</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338479</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Graphic Design Intern</t>
+          <t>Data Analyst Intern</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Phagwara, Punjab, India</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2220,39 +2220,39 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CGC JHANJERI MOHALI</t>
+          <t>GNA University</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1338412</t>
+          <t>1338450</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338412</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338450</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Graphic Design Intern</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Phagwara, Punjab, India</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2262,39 +2262,39 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>GNA University</t>
+          <t>CGC JHANJERI MOHALI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1338407</t>
+          <t>1338412</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338407</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338412</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Accelerate Romania|Marketing &amp; Communications Intern (Europe Only)</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Timișoara, România</t>
+          <t>Phagwara, Punjab, India</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2304,39 +2304,39 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Cowork Timisoara</t>
+          <t>GNA University</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1338381</t>
+          <t>1338407</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338381</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338407</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junior Sales Closer / Business Consultant</t>
+          <t>Accelerate Romania|Marketing &amp; Communications Intern (Europe Only)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Piatra Neamț, Romania</t>
+          <t>Timișoara, România</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2346,34 +2346,34 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>REHub</t>
+          <t>Cowork Timisoara</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1338380</t>
+          <t>1338381</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338380</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338381</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junio Business Development Specialist / Lead Generation Specialist</t>
+          <t>Accelerate Romania | Junior Sales Closer / Business Consultant</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2405,22 +2405,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1338355</t>
+          <t>1338380</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338355</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338380</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Procurement Support</t>
+          <t>Accelerate Romania | Junio Business Development Specialist / Lead Generation Specialist</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Piatra Neamț, Romania</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2430,39 +2430,39 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nestle Panama</t>
+          <t>REHub</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1338348</t>
+          <t>1338355</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338348</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338355</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Business Development Manager</t>
+          <t>Procurement Support</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2472,81 +2472,81 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Moasher</t>
+          <t>Nestle Panama</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1338347</t>
+          <t>1338354</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338347</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338354</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>[DGF] Inside Sales Intern l German Speaker</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Mainz, Germany</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Moasher</t>
+          <t>DHL Group</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1338306</t>
+          <t>1338348</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338306</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338348</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>People Team Analyst</t>
+          <t>Business Development Manager</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2556,39 +2556,39 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>41 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>Moasher</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1338303</t>
+          <t>1338347</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338303</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338347</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Data &amp; AI Product Analyst</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2598,39 +2598,39 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Telered Panama</t>
+          <t>Moasher</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1338299</t>
+          <t>1338306</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338299</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338306</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>People Team Analyst</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,39 +2640,39 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>43 applicants</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1338298</t>
+          <t>1338303</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338298</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338303</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Python Developer Intern (AI/ML)</t>
+          <t>Data &amp; AI Product Analyst</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2682,34 +2682,34 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Telered Panama</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1338296</t>
+          <t>1338299</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338296</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338299</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Social media specialist</t>
+          <t>Video Editor</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2741,22 +2741,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1338295</t>
+          <t>1338298</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338295</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338298</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Python Developer Intern (AI/ML)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2766,34 +2766,34 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1338294</t>
+          <t>1338296</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338294</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338296</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Social media specialist</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2825,22 +2825,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1338290</t>
+          <t>1338295</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338290</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338295</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Front Office Executive</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Nuwara Eliya, Sri Lanka</t>
+          <t>Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2850,39 +2850,39 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>13 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Hotel Glendower</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1338288</t>
+          <t>1338294</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338288</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338294</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Front Office Executive</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Nuwara Eliya, Sri Lanka</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2892,39 +2892,39 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pedro Barn pvt ltd</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1338282</t>
+          <t>1338290</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338282</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338290</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Web Developer Intern</t>
+          <t>Front Office Executive</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Phagwara, Punjab, India</t>
+          <t>Nuwara Eliya, Sri Lanka</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2944,29 +2944,29 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>GNA University</t>
+          <t>Hotel Glendower</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1338281</t>
+          <t>1338288</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338281</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338288</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Sales Intern</t>
+          <t>Front Office Executive</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pannipitiya, Sri Lanka</t>
+          <t>Nuwara Eliya, Sri Lanka</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Frella International</t>
+          <t>Pedro Barn pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1338279</t>
+          <t>1338282</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338279</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338282</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Client Services Executive</t>
+          <t>Web Developer Intern</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Phagwara, Punjab, India</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3018,39 +3018,39 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>GNA University</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1338273</t>
+          <t>1338281</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338273</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338281</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Digital Marketing &amp; Sales Intern</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Pannipitiya, Sri Lanka</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>36 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3070,29 +3070,29 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Michael Page International Panamá S.A.</t>
+          <t>Frella International</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1338263</t>
+          <t>1338279</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338263</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338279</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Electrical engineering intern</t>
+          <t>Client Services Executive</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3112,29 +3112,29 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1338261</t>
+          <t>1338273</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338261</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338273</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mechanical engineer</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kartepe, Kocaeli, Türkiye</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3154,29 +3154,29 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>dağgaz enerji</t>
+          <t>Michael Page International Panamá S.A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1338257</t>
+          <t>1338263</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338257</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338263</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>International Business Development Manager</t>
+          <t>Electrical engineering intern</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3196,29 +3196,29 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>GUJARAT TEA PROCESSORS AND PACKERS LIMITED</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1338226</t>
+          <t>1338261</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338226</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338261</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Accountant</t>
+          <t>mechanical engineer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Birmingham, UK</t>
+          <t>Kartepe, Kocaeli, Türkiye</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>128 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3238,29 +3238,29 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MISTECH GLOBAL LTD</t>
+          <t>dağgaz enerji</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1338219</t>
+          <t>1338257</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338219</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338257</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marketing &amp; Commercial Specialist</t>
+          <t>International Business Development Manager</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3270,39 +3270,39 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>51 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nestle Panama</t>
+          <t>GUJARAT TEA PROCESSORS AND PACKERS LIMITED</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1338209</t>
+          <t>1338226</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338209</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338226</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Guest Relations Executive</t>
+          <t>Accountant</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Galle, Sri Lanka</t>
+          <t>Birmingham, UK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3312,39 +3312,39 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>135 applicants</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sino Lanka Hotels Colombo (Pvt) Ltd</t>
+          <t>MISTECH GLOBAL LTD</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1338197</t>
+          <t>1338219</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338197</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338219</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Marketing &amp; Commercial Specialist</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3354,39 +3354,39 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>52 applicants</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>The Address</t>
+          <t>Nestle Panama</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1338193</t>
+          <t>1338209</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338193</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338209</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Psychology Management Intern</t>
+          <t>Guest Relations Executive</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Galle, Sri Lanka</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3396,39 +3396,39 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SKIPS University</t>
+          <t>Sino Lanka Hotels Colombo (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1338190</t>
+          <t>1338197</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338190</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338197</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3438,39 +3438,39 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>The Address</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1338187</t>
+          <t>1338193</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338187</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338193</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mobile Application</t>
+          <t>Psychology Management Intern</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3490,24 +3490,24 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>SKIPS University</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1338186</t>
+          <t>1338190</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338186</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338190</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3539,17 +3539,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1338185</t>
+          <t>1338187</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338185</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338187</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Business development</t>
+          <t>Mobile Application</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3581,17 +3581,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1338182</t>
+          <t>1338186</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338182</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338186</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3623,17 +3623,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1338181</t>
+          <t>1338185</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338181</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338185</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Marketing Specialists</t>
+          <t>Business development</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3665,17 +3665,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1338180</t>
+          <t>1338182</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338180</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338182</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3707,17 +3707,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1338179</t>
+          <t>1338181</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338179</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338181</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Marketing Specialists</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3749,17 +3749,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1338178</t>
+          <t>1338180</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338178</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338180</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Media Coverage</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3791,17 +3791,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1338177</t>
+          <t>1338179</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338177</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338179</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Media Coverage</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1338176</t>
+          <t>1338178</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338176</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338178</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Media Coverage</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3875,22 +3875,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1338136</t>
+          <t>1338177</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338136</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338177</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Digital Communication Intern</t>
+          <t>Media Coverage</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Santiago do Cacém, Portugal</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>45 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3910,29 +3910,29 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Destilaria Black Pig Alentejo Unip. Lda.</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1338115</t>
+          <t>1338176</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338115</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338176</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[Remote] Software Application Support and Development</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>No location available</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3942,39 +3942,39 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>75 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>dJava Factory Sdn Bhd</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1338112</t>
+          <t>1338136</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338112</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338136</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Junior Geospatial analyst</t>
+          <t>Digital Communication Intern</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Novi Sad, Serbia</t>
+          <t>Santiago do Cacém, Portugal</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3994,29 +3994,29 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DataDEV</t>
+          <t>Destilaria Black Pig Alentejo Unip. Lda.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1338098</t>
+          <t>1338115</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338098</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338115</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[Dutch Speaker] Business Development Intern</t>
+          <t>[Remote] Software Application Support and Development</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Coagh, UK</t>
+          <t>No location available</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4026,39 +4026,39 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>79 applicants</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>dJava Factory Sdn Bhd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1338068</t>
+          <t>1338112</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338068</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338112</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AI Media Transformation Intern (EU ONLY)</t>
+          <t>Junior Geospatial analyst</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Schiphol, Netherlands</t>
+          <t>Novi Sad, Serbia</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4068,34 +4068,34 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>20 applicants</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Vestacy</t>
+          <t>DataDEV</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1338067</t>
+          <t>1338068</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338067</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338068</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Social Media &amp; Creator Insights Intern (EU ONLY)</t>
+          <t>AI Media Transformation Intern (EU ONLY)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4127,22 +4127,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1338064</t>
+          <t>1338067</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338064</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338067</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Financial Accounting Trainee (EU ONLY)</t>
+          <t>Social Media &amp; Creator Insights Intern (EU ONLY)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Amsterdam, Netherlands</t>
+          <t>Schiphol, Netherlands</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4162,29 +4162,29 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Volkswagen International Finance N.V.</t>
+          <t>Vestacy</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1338049</t>
+          <t>1338064</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338049</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338064</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Financial Accounting Trainee (EU ONLY)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Çal, Denizli, Türkiye</t>
+          <t>Amsterdam, Netherlands</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>91 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4204,29 +4204,29 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ELİTEPRİME SEEDS GIDA SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Volkswagen International Finance N.V.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1338046</t>
+          <t>1338049</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338046</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338049</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Front-end Developer</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Timișoara, România</t>
+          <t>Çal, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4236,34 +4236,34 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>94 applicants</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Webchain</t>
+          <t>ELİTEPRİME SEEDS GIDA SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1338045</t>
+          <t>1338046</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338045</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338046</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Back-end Developer</t>
+          <t>Accelerate Romania | Front-end Developer</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>36 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1338035</t>
+          <t>1338045</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338035</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338045</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Accelerate Romania | Back-end Developer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Timișoara, România</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4320,39 +4320,39 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>37 applicants</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>G Square International PVT LTD</t>
+          <t>Webchain</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1338025</t>
+          <t>1338035</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1338025</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338035</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - E-Commerce Creative Content &amp; Listing Marketing Intern</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Uberlândia, MG, Brasil</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4362,39 +4362,39 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>28 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>PAT E-Commerce &amp; International Trade</t>
+          <t>G Square International PVT LTD</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1337996</t>
+          <t>1338029</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337996</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338029</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Informational Technology Intern</t>
+          <t>SCM Process Innovation</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Serres, Greece</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4404,39 +4404,39 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>60 applicants</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>POLIECO HELLAS</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1337995</t>
+          <t>1338025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337995</t>
+          <t>https://aiesec.org/opportunity/global-talent/1338025</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>[Impact Brazil] - E-Commerce Creative Content &amp; Listing Marketing Intern</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Serres, Greece</t>
+          <t>Uberlândia, MG, Brasil</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>22 applicants</t>
+          <t>29 applicants</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4456,29 +4456,29 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>POLIECO HELLAS</t>
+          <t>PAT E-Commerce &amp; International Trade</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1337973</t>
+          <t>1337996</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337973</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337996</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sales at GEMSA</t>
+          <t>Informational Technology Intern</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
+          <t>Serres, Greece</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4498,29 +4498,29 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>GEMSA</t>
+          <t>POLIECO HELLAS</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1337959</t>
+          <t>1337995</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337959</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337995</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
+          <t>Serres, Greece</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4530,39 +4530,39 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>53 applicants</t>
+          <t>22 applicants</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
+          <t>POLIECO HELLAS</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1337958</t>
+          <t>1337973</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337958</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337973</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Sales at GEMSA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
+          <t>Adana, Reşatbey, Seyhan/Adana, Türkiye</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4572,39 +4572,39 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
+          <t>GEMSA</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1337938</t>
+          <t>1337959</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337938</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337959</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Graphic Designer Intern - Mid term</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>56 applicants</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1337937</t>
+          <t>1337958</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337937</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337958</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Graphic Designer Intern - Short Term</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Altındere, 20050 Denizli Merkezefendi/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4656,39 +4656,39 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Özstar Kuruyemiş Makina Sanayi ve Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1337886</t>
+          <t>1337938</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337886</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337938</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IT Research Interns (Duplicated) (Duplicated) (Duplicated)</t>
+          <t>Graphic Designer Intern - Mid term</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Aronj, Uttar Pradesh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4708,29 +4708,29 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>FS University</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1337879</t>
+          <t>1337937</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337879</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337937</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IT Research Interns (Duplicated) (Duplicated)</t>
+          <t>Graphic Designer Intern - Short Term</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Aronj, Uttar Pradesh, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4740,39 +4740,39 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>8 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>FS University</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1337875</t>
+          <t>1337886</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337875</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337886</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>IT Research Interns (Duplicated) (Duplicated) (Duplicated)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ankara, Türkiye</t>
+          <t>Aronj, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4792,29 +4792,29 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Akın Global Medikal</t>
+          <t>FS University</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1337863</t>
+          <t>1337879</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337863</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337879</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Social Media Specialist</t>
+          <t>IT Research Interns (Duplicated) (Duplicated)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>中国广东省深圳市龙岗区</t>
+          <t>Aronj, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4824,39 +4824,39 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>80 applicants</t>
+          <t>8 applicants</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Keychron</t>
+          <t>FS University</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1337859</t>
+          <t>1337875</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337859</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337875</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>Ankara, Türkiye</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4866,39 +4866,39 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>69 applicants</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Akın Global Medikal</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1337844</t>
+          <t>1337863</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337844</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337863</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tourism Specialist - Intern</t>
+          <t>Social Media Specialist</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>中国广东省深圳市龙岗区</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4908,39 +4908,39 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>25 applicants</t>
+          <t>81 applicants</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Keychron</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1337835</t>
+          <t>1337859</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337835</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337859</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Architecture Intern</t>
+          <t>Electrical Engineering Intern</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4960,29 +4960,29 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Galenta Interiors</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1337833</t>
+          <t>1337844</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337844</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Tourism Specialist - Intern</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5002,29 +5002,29 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1337809</t>
+          <t>1337835</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337809</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337835</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Digital Marketing Intern</t>
+          <t>Architecture Intern</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Aluthgama, Sri Lanka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5044,29 +5044,29 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Diyakawa Water Sports Centre Bentota</t>
+          <t>Galenta Interiors</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1337808</t>
+          <t>1337833</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337808</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337833</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sales &amp; Impact Trainee</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5076,39 +5076,39 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>95 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Shayp</t>
+          <t>Suprnova [Quenelle36 Foodworks Pvt. Ltd]</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1337794</t>
+          <t>1337809</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337794</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337809</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Photographer &amp; Videographer</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cotnari, Romania</t>
+          <t>Aluthgama, Sri Lanka</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>17 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5128,29 +5128,29 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>SC CRAMELE COTNARI SA</t>
+          <t>Diyakawa Water Sports Centre Bentota</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1337793</t>
+          <t>1337808</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337793</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337808</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Graphic Designer</t>
+          <t>Sales &amp; Impact Trainee</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cotnari, Romania</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5160,39 +5160,39 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>96 applicants</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SC CRAMELE COTNARI SA</t>
+          <t>Shayp</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1337764</t>
+          <t>1337794</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337764</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337794</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Accelerate Romania | Photographer &amp; Videographer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Cotnari, Romania</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5202,39 +5202,39 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>97 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>SC CRAMELE COTNARI SA</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1337761</t>
+          <t>1337793</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337761</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337793</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Export Manager Assistant</t>
+          <t>Accelerate Romania | Graphic Designer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>İzmir, Türkiye</t>
+          <t>Cotnari, Romania</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5244,39 +5244,39 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>99 applicants</t>
+          <t>17 applicants</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
+          <t>SC CRAMELE COTNARI SA</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1337723</t>
+          <t>1337761</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337723</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337761</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>UX/UI Designer</t>
+          <t>Export Manager Assistant</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Charneca de Caparica, Portugal</t>
+          <t>İzmir, Türkiye</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5286,39 +5286,39 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>101 applicants</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Indústria dos Óculos</t>
+          <t>ACUNAL GIDA TARIM ÜRÜNLERİ MAKİNA İTHALAT İHRACAT SANAYİ VE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1337665</t>
+          <t>1337734</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337665</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337734</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chief Corporate Strategy and Administration Officer</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Tanta, Tanta Qism 2, Tanta, Gharbia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5328,39 +5328,39 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>39 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Indian Kitchen (Pvt) Ltd</t>
+          <t>print shop</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1337649</t>
+          <t>1337723</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337649</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337723</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Clinical Study Operations Trainee</t>
+          <t>UX/UI Designer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
+          <t>Charneca de Caparica, Portugal</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5370,39 +5370,39 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>UCB</t>
+          <t>Indústria dos Óculos</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1337628</t>
+          <t>1337665</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337628</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337665</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Food and Beverage Trainee</t>
+          <t>Chief Corporate Strategy and Administration Officer</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5412,39 +5412,39 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Park Hotel International Limited</t>
+          <t>Indian Kitchen (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1337625</t>
+          <t>1337649</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337625</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337649</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Physiotherapy Intern</t>
+          <t>Clinical Study Operations Trainee</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Multan, Pakistan</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5454,39 +5454,39 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Barki Complex</t>
+          <t>UCB</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1337624</t>
+          <t>1337628</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337624</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337628</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Web Development Intern</t>
+          <t>Food and Beverage Trainee</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Multan, Pakistan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5496,34 +5496,34 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Barki Complex</t>
+          <t>Park Hotel International Limited</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1337622</t>
+          <t>1337625</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337622</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337625</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Social Media Marketing Intern</t>
+          <t>Physiotherapy Intern</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5555,22 +5555,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1337613</t>
+          <t>1337624</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337613</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337624</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Web Development Intern</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cyberjaya, Selangor, Malaysia</t>
+          <t>Multan, Pakistan</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5580,39 +5580,39 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>174 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>IX Telecom Sdn Bhd</t>
+          <t>Barki Complex</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1337548</t>
+          <t>1337622</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337548</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337622</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Algorithm Engineer</t>
+          <t>Social Media Marketing Intern</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Zürich, Switzerland</t>
+          <t>Multan, Pakistan</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5622,39 +5622,39 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>34 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sennheiser</t>
+          <t>Barki Complex</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1337537</t>
+          <t>1337613</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337537</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337613</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Cyberjaya, Selangor, Malaysia</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>70 applicants</t>
+          <t>177 applicants</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>TBPART OTOMOTİV SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
+          <t>IX Telecom Sdn Bhd</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1337534</t>
+          <t>1337548</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337534</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337548</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Market Analysis and Strategy Formulation Aim to Launch  Hair Care Products in India</t>
+          <t>Algorithm Engineer</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>日本、東京都東京</t>
+          <t>Zürich, Switzerland</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5706,39 +5706,39 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>58 applicants</t>
+          <t>38 applicants</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Milbon Co., Ltd.</t>
+          <t>Sennheiser</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1337508</t>
+          <t>1337537</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337508</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337537</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junior Customer Success &amp; Activation Intern</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Galați, Romania</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5748,39 +5748,39 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>32 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CONTSCAPE TEC SRL</t>
+          <t>TBPART OTOMOTİV SANAYİ VE TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1337475</t>
+          <t>1337534</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337475</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337534</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Deep Learning Intern</t>
+          <t>Market Analysis and Strategy Formulation Aim to Launch  Hair Care Products in India</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Udupi, Karnataka, India</t>
+          <t>日本、東京都東京</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5790,39 +5790,39 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>15 applicants</t>
+          <t>60 applicants</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Milbon Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1337446</t>
+          <t>1337508</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337446</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337508</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sales Specialist</t>
+          <t>Accelerate Romania | Junior Customer Success &amp; Activation Intern</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Galați, Romania</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5832,39 +5832,39 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>34 applicants</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>CONTSCAPE TEC SRL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1337445</t>
+          <t>1337475</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337445</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337475</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Media Coverage</t>
+          <t>Deep Learning Intern</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Udupi, Karnataka, India</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5884,29 +5884,29 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1337435</t>
+          <t>1337446</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337435</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337446</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Sales Specialist</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5926,29 +5926,29 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>QJ Design Studios (PVT) LTD</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1337433</t>
+          <t>1337445</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337433</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337445</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IT Systems &amp; Business Applications Specialist</t>
+          <t>Media Coverage</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6th of October City, Giza Governorate, Egypt</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5968,29 +5968,29 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Olven White</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1337417</t>
+          <t>1337435</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337417</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337435</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Dehiwala-Mount Lavinia, Sri Lanka</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6000,39 +6000,39 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>E.C.O</t>
+          <t>QJ Design Studios (PVT) LTD</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1337411</t>
+          <t>1337433</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337411</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337433</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Guest Experience Manager</t>
+          <t>IT Systems &amp; Business Applications Specialist</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>6th of October City, Giza Governorate, Egypt</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>20 applicants</t>
+          <t>40 applicants</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6052,29 +6052,29 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Indian Kitchen (Pvt) Ltd</t>
+          <t>Olven White</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1337408</t>
+          <t>1337417</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337408</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337417</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6084,39 +6084,39 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>24 applicants</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>E.C.O</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1337407</t>
+          <t>1337411</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337407</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337411</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Guest Experience Manager</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -6136,24 +6136,24 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Egypt holiday travel</t>
+          <t>Indian Kitchen (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1337406</t>
+          <t>1337408</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337406</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337408</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6185,17 +6185,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1337403</t>
+          <t>1337407</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337403</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337407</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6227,17 +6227,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1337402</t>
+          <t>1337406</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337402</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337406</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Graphic Designer</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6269,17 +6269,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1337400</t>
+          <t>1337403</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337400</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337403</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Media Coverage</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6311,17 +6311,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1337394</t>
+          <t>1337402</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337394</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337402</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Graphic designer</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6353,17 +6353,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1337393</t>
+          <t>1337400</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337393</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337400</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Business Developer</t>
+          <t>Media Coverage</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6395,17 +6395,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1337391</t>
+          <t>1337394</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337391</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337394</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Graphic designer</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6437,22 +6437,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1337389</t>
+          <t>1337393</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337389</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337393</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[Impact Brazil] - Sales Development Intern (LATAM)</t>
+          <t>Business Developer</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Maringá, PR, Brasil</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6462,39 +6462,39 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>33 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ANYMARKET TECHNOLOGIES</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1337387</t>
+          <t>1337391</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337387</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337391</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Junior software developer - Security</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6504,39 +6504,39 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>Egypt holiday travel</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1337373</t>
+          <t>1337389</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337373</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337389</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Analytics</t>
+          <t>[Impact Brazil] - Sales Development Intern (LATAM)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Maringá, PR, Brasil</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6546,34 +6546,34 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>33 applicants</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>ANYMARKET TECHNOLOGIES</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1337372</t>
+          <t>1337387</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337372</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337387</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Backend</t>
+          <t>Junior software developer - Security</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6605,17 +6605,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1337371</t>
+          <t>1337373</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337371</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337373</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Devops</t>
+          <t>Junior Software Engineer – Analytics</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6647,17 +6647,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1337367</t>
+          <t>1337372</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337367</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337372</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Human Capital Associate – Talent,Payroll,Engagement &amp; Development</t>
+          <t>Junior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6689,22 +6689,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1337366</t>
+          <t>1337371</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337366</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337371</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Junior Software Engineer – Devops</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Zwolle, Nederland</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6714,34 +6714,34 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>37 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Webfin Holding B.V.</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1337363</t>
+          <t>1337367</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337363</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337367</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Junior Software Engineer – Security</t>
+          <t>Human Capital Associate – Talent,Payroll,Engagement &amp; Development</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>9 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6773,22 +6773,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1337362</t>
+          <t>1337366</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337362</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337366</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Junior Software Engineer –UI/UX</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Zwolle, Nederland</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6798,34 +6798,34 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>46 applicants</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>Webfin Holding B.V.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1337336</t>
+          <t>1337363</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337336</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337363</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Marketing Associate - Content</t>
+          <t>Junior Software Engineer – Security</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>7 applicants</t>
+          <t>9 applicants</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6857,17 +6857,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1337335</t>
+          <t>1337362</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337335</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337362</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Marketing Associate - Design</t>
+          <t>Junior Software Engineer –UI/UX</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6899,22 +6899,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1337334</t>
+          <t>1337336</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337334</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337336</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Online Marketeer (German-speaking)</t>
+          <t>Marketing Associate - Content</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6924,34 +6924,34 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>7 applicants</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>SB Supply Europe</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1337333</t>
+          <t>1337335</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337333</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337335</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Marketing Associate - Digital</t>
+          <t>Marketing Associate - Design</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6983,22 +6983,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1337332</t>
+          <t>1337334</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337332</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337334</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Junior Product Associate</t>
+          <t>Online Marketeer (German-speaking)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India</t>
+          <t>Tilburg, Netherlands</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7008,34 +7008,34 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
+          <t>SB Supply Europe</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1337331</t>
+          <t>1337333</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337331</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337333</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Accounts &amp; Finance Associate</t>
+          <t>Marketing Associate - Digital</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>14 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7067,22 +7067,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1337298</t>
+          <t>1337332</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337298</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337332</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Marketing &amp; Retail Intern</t>
+          <t>Junior Product Associate</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7092,39 +7092,39 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>122 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Samsung Electronics Latinoamerica SELA Panama</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1337278</t>
+          <t>1337331</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337278</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337331</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Corporate Finance Analyst</t>
+          <t>Accounts &amp; Finance Associate</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Panamá, Provincia de Panamá, Panamá</t>
+          <t>Mumbai, Maharashtra, India</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7134,34 +7134,34 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>89 applicants</t>
+          <t>15 applicants</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>PSA Panama International Terminal, S.A.</t>
+          <t>LogiSprint Solutions Private Limited (“LogiNext”)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1337271</t>
+          <t>1337298</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337271</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337298</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Marketing &amp; Retail Intern</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>66 applicants</t>
+          <t>124 applicants</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -7186,29 +7186,29 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>HILTI Panama</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1337248</t>
+          <t>1337278</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337248</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337278</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Public Relations and Marketing</t>
+          <t>Corporate Finance Analyst</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Dehradun, Uttarakhand, India</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7218,39 +7218,39 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>91 applicants</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Cyber College Educational Society</t>
+          <t>PSA Panama International Terminal, S.A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1337244</t>
+          <t>1337271</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337244</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337271</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Export Specialist in Istanbul</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Panamá, Provincia de Panamá, Panamá</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>34 applicants</t>
+          <t>68 applicants</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7270,29 +7270,29 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Akpa Aluminium</t>
+          <t>HILTI Panama</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1337243</t>
+          <t>1337248</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337248</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Medical Advisor (Serbian Speaker)</t>
+          <t>Public Relations and Marketing</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Dehradun, Uttarakhand, India</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7307,29 +7307,29 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>International Plus</t>
+          <t>Cyber College Educational Society</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1337242</t>
+          <t>1337243</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337243</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Medical Advisor (Bulgarian Speaker)</t>
+          <t>Medical Advisor (Serbian Speaker)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7361,17 +7361,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1337242</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337242</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Medical Advisor (Czech Speaker)</t>
+          <t>Medical Advisor (Bulgarian Speaker)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7403,22 +7403,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1337230</t>
+          <t>1337241</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337230</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337241</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Medical Advisor (Czech Speaker)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7428,34 +7428,34 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1337229</t>
+          <t>1337230</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337229</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337230</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>5 applicants</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1337228</t>
+          <t>1337229</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337228</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337229</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7529,17 +7529,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1337227</t>
+          <t>1337228</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337228</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7571,22 +7571,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1337220</t>
+          <t>1337227</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337220</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337227</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Accelerate Romania | Junio Business Administrator / General Manager</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Piatra Neamț, Romania</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7596,39 +7596,39 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>43 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>SC LAPOOL SRL</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1337199</t>
+          <t>1337220</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337199</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337220</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Social Media Content Creator / Content Strategist</t>
+          <t>Accelerate Romania | Junio Business Administrator / General Manager</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
+          <t>Piatra Neamț, Romania</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>49 applicants</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7648,29 +7648,29 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>AL MAQSD</t>
+          <t>SC LAPOOL SRL</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1337158</t>
+          <t>1337199</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337199</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sales Responsible</t>
+          <t>Social Media Content Creator / Content Strategist</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Konya, Türkiye</t>
+          <t>Mansoura, Mansoura Qism 2, El Mansoura, Dakahlia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>53 applicants</t>
+          <t>12 applicants</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7690,29 +7690,29 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Dirim Metal Anonim Şirketi</t>
+          <t>AL MAQSD</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1337103</t>
+          <t>1337196</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337196</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Education Coordinator</t>
+          <t>Interior Design</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Tanta, Tanta Qism 2, Tanta, Gharbia Governorate, Egypt</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7722,39 +7722,39 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
+          <t>Elaf Engineering</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1337100</t>
+          <t>1337158</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337158</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sales Responsible</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Konya, Türkiye</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1 applicant</t>
+          <t>54 applicants</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7774,29 +7774,29 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>Dirim Metal Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1337099</t>
+          <t>1337103</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337099</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337103</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Education Coordinator</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7806,34 +7806,34 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>70 applicants</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Alphanumeric Ideas Pvt Ltd</t>
+          <t>Pechom Endüstri ve Makina Ticaret Anonim Şirketi</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1337098</t>
+          <t>1337100</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1337098</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337100</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>1 applicant</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7865,22 +7865,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1336989</t>
+          <t>1337099</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336989</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337099</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Social Media Campaign Manager (German Speaker)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7890,39 +7890,39 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>4 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Ashdud</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1336982</t>
+          <t>1337098</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336982</t>
+          <t>https://aiesec.org/opportunity/global-talent/1337098</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Telemarketing Specialist (German Speaker)</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>New Cairo City, Cairo Governorate, Egypt</t>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7937,34 +7937,34 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Ashdud</t>
+          <t>Alphanumeric Ideas Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1336949</t>
+          <t>1336989</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336949</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336989</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Robotics and Automation Intern</t>
+          <t>Social Media Campaign Manager (German Speaker)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ambala, Haryana, India</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7974,39 +7974,39 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>4 applicants</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Ashdud</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1336909</t>
+          <t>1336982</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336909</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336982</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Environment Business Development Manager</t>
+          <t>Telemarketing Specialist (German Speaker)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Cairo City, Cairo Governorate, Egypt</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8016,39 +8016,39 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>11 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>E.C.O</t>
+          <t>Ashdud</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1336902</t>
+          <t>1336949</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336902</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336949</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Operations Coordinator [6 Weeks]</t>
+          <t>Robotics and Automation Intern</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Ambala, Haryana, India</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>3 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Infinitum Network Solutions</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1336845</t>
+          <t>1336909</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336845</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336909</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Accelerate Romania - Junior Sales Development Representative</t>
+          <t>Environment Business Development Manager</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Sibiu, Romania</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>11 applicants</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8110,29 +8110,29 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ATUM Marketing</t>
+          <t>E.C.O</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1336833</t>
+          <t>1336902</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336902</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>AI &amp; ML Engineering Intern</t>
+          <t>Operations Coordinator [6 Weeks]</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Nugegoda, Sri Lanka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -8142,39 +8142,39 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>3 applicants</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Altria Consulting (PVT) LTD</t>
+          <t>Infinitum Network Solutions</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1336821</t>
+          <t>1336833</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336821</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336833</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Game Design Intern</t>
+          <t>AI &amp; ML Engineering Intern</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Mullana, Haryana 133203, India</t>
+          <t>Nugegoda, Sri Lanka</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8184,39 +8184,39 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>6 applicants</t>
+          <t>69 applicants</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>MM(DU) Mullana</t>
+          <t>Altria Consulting (PVT) LTD</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1336818</t>
+          <t>1336821</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336818</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336821</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ai Intern</t>
+          <t>Game Design Intern</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India</t>
+          <t>Mullana, Haryana 133203, India</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -8236,29 +8236,29 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Shivalik Institute of Real Estate</t>
+          <t>MM(DU) Mullana</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1336749</t>
+          <t>1336818</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336749</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336818</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mirai Consumer Analysis</t>
+          <t>Ai Intern</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Ahmedabad, Gujarat, India</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -8278,29 +8278,29 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>Shivalik Institute of Real Estate</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1336746</t>
+          <t>1336749</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1336746</t>
+          <t>https://aiesec.org/opportunity/global-talent/1336749</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Product manager (German-speaking)</t>
+          <t>Mirai Consumer Analysis</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8310,17 +8310,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>2 applicants</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Magneds</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>80 applicants</t>
+          <t>81 applicants</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>5 applicants</t>
+          <t>6 applicants</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>111 applicants</t>
+          <t>113 applicants</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>70 applicants</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>184 applicants</t>
+          <t>185 applicants</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>38 applicants</t>
+          <t>39 applicants</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>24 applicants</t>
+          <t>25 applicants</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>29 applicants</t>
+          <t>30 applicants</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>104 applicants</t>
+          <t>106 applicants</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>12 applicants</t>
+          <t>13 applicants</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>78 applicants</t>
+          <t>79 applicants</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>34 applicants</t>
+          <t>36 applicants</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>95 applicants</t>
+          <t>96 applicants</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>256 applicants</t>
+          <t>257 applicants</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>27 applicants</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>132 applicants</t>
+          <t>133 applicants</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>141 applicants</t>
+          <t>144 applicants</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>84 applicants</t>
+          <t>85 applicants</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>70 applicants</t>
+          <t>71 applicants</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>93 applicants</t>
+          <t>95 applicants</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>166 applicants</t>
+          <t>167 applicants</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>103 applicants</t>
+          <t>104 applicants</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>81 applicants</t>
+          <t>82 applicants</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>54 applicants</t>
+          <t>55 applicants</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>95 applicants</t>
+          <t>96 applicants</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>49 applicants</t>
+          <t>50 applicants</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>62 applicants</t>
+          <t>64 applicants</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>51 applicants</t>
+          <t>53 applicants</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>149 applicants</t>
+          <t>150 applicants</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -16895,22 +16895,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1323558</t>
+          <t>1323507</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323558</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323507</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Construction Project Manager (Civil Engineer/Architect)</t>
+          <t>Sales Intern</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Lissabon, Portugal</t>
+          <t>Karachi, Pakistan</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>75 applicants</t>
+          <t>19 applicants</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -16930,24 +16930,24 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Grupo Casais</t>
+          <t>Wavetec</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1323507</t>
+          <t>1323506</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323507</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323506</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Sales Intern</t>
+          <t>Marketing Intern</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>19 applicants</t>
+          <t>18 applicants</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -16979,17 +16979,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1323506</t>
+          <t>1323504</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323506</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323504</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Marketing Intern</t>
+          <t>Management Trainee Officer</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>18 applicants</t>
+          <t>35 applicants</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -17021,17 +17021,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1323504</t>
+          <t>1323503</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323504</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323503</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Management Trainee Officer</t>
+          <t>Customer Support Engineer</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>35 applicants</t>
+          <t>21 applicants</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -17063,17 +17063,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1323503</t>
+          <t>1323391</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323503</t>
+          <t>https://aiesec.org/opportunity/global-talent/1323391</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Customer Support Engineer</t>
+          <t>Business Development Officer</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>21 applicants</t>
+          <t>16 applicants</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -17105,22 +17105,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1323391</t>
+          <t>1322346</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1323391</t>
+          <t>https://aiesec.org/opportunity/global-talent/1322346</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Business Development Officer</t>
+          <t>Cyber Security and AI Intern</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Karachi, Pakistan</t>
+          <t>Manipal, Karnataka, India</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -17130,39 +17130,39 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>16 applicants</t>
+          <t>72 applicants</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Wavetec</t>
+          <t>M.A.H.E.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1322346</t>
+          <t>1321910</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1322346</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321910</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Cyber Security and AI Intern</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Manipal, Karnataka, India</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -17172,34 +17172,34 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>72 applicants</t>
+          <t>203 applicants</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>M.A.H.E.</t>
+          <t>Eman Agro Gıda</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1321910</t>
+          <t>1321833</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321910</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321833</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>203 applicants</t>
+          <t>140 applicants</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -17224,29 +17224,29 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Eman Agro Gıda</t>
+          <t>MACRO SIGN REKLAM İÇ VE DIŞ TİCARET LİMİTED ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1321840</t>
+          <t>1321450</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321840</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321450</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Marketing&amp;Sales</t>
+          <t>Sales and Business Development Intern</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Jaipur, Rajasthan, India</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -17256,39 +17256,39 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>115 applicants</t>
+          <t>56 applicants</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Hak Makarna</t>
+          <t>www.Besteduonline.in (IPS Education &amp; Learning)</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1321833</t>
+          <t>1321076</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321833</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321076</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Corporate Sales Executive</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Mehrauli, Delhi, India</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>140 applicants</t>
+          <t>0 applicants</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -17308,29 +17308,29 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>MACRO SIGN REKLAM İÇ VE DIŞ TİCARET LİMİTED ŞİRKETİ</t>
+          <t>Empathy Relocations</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1321450</t>
+          <t>1321055</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321450</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321055</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Sales and Business Development Intern</t>
+          <t>International Sales Representetive Italian Speaker</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Jaipur, Rajasthan, India</t>
+          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -17340,39 +17340,39 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>56 applicants</t>
+          <t>26 applicants</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>www.Besteduonline.in (IPS Education &amp; Learning)</t>
+          <t>Esvita Clinic</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1321076</t>
+          <t>1321053</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321076</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321053</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Corporate Sales Executive</t>
+          <t>International Sales Representetive German Speaker</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Mehrauli, Delhi, India</t>
+          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>0 applicants</t>
+          <t>27 applicants</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -17392,24 +17392,24 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Empathy Relocations</t>
+          <t>Esvita Clinic</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1321055</t>
+          <t>1321052</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321055</t>
+          <t>https://aiesec.org/opportunity/global-talent/1321052</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>International Sales Representetive Italian Speaker</t>
+          <t>International Sales Representetive</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>26 applicants</t>
+          <t>229 applicants</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -17441,22 +17441,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1321053</t>
+          <t>1317664</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321053</t>
+          <t>https://aiesec.org/opportunity/global-talent/1317664</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>International Sales Representetive German Speaker</t>
+          <t>SALES ATTENDED</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>69 applicants</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -17476,29 +17476,29 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Esvita Clinic</t>
+          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1321052</t>
+          <t>1316860</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1321052</t>
+          <t>https://aiesec.org/opportunity/global-talent/1316860</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>International Sales Representetive</t>
+          <t>MARKET RESARCH &amp; MARKETİNG</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Maslak, Sarıyer/İstanbul, Türkiye</t>
+          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>227 applicants</t>
+          <t>134 applicants</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -17518,29 +17518,29 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Esvita Clinic</t>
+          <t>NR MARBLE DOĞALTAŞ PETROL İTH. İHR. SANAYİ VE TİC. LTD. ŞTİ</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1317664</t>
+          <t>1316099</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1317664</t>
+          <t>https://aiesec.org/opportunity/global-talent/1316099</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SALES ATTENDED</t>
+          <t>Sales &amp; BD Junior Manager</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Puzi City, Chiayi County, Taiwan 613</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>69 applicants</t>
+          <t>131 applicants</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -17560,29 +17560,29 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>COTTON CASTLE TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Singform Enterprise Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1316860</t>
+          <t>1315961</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1316860</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315961</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>MARKET RESARCH &amp; MARKETİNG</t>
+          <t>Female Guest Relations Executive - Mid Term</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Denizli, Kumkısık, Denizli, Türkiye</t>
+          <t>Kandy, Sri Lanka</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -17592,39 +17592,39 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>134 applicants</t>
+          <t>41 applicants</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>NR MARBLE DOĞALTAŞ PETROL İTH. İHR. SANAYİ VE TİC. LTD. ŞTİ</t>
+          <t>Canora Hotels (pvt) Ltd Grand Kandyan Hotel</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1316099</t>
+          <t>1315189</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1316099</t>
+          <t>https://aiesec.org/opportunity/global-talent/1315189</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Sales &amp; BD Junior Manager</t>
+          <t>Associate Consultant Internship</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Puzi City, Chiayi County, Taiwan 613</t>
+          <t>Gurugram, Haryana, India</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -17634,39 +17634,39 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>131 applicants</t>
+          <t>10 applicants</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>3 - 6 Months</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Singform Enterprise Co., Ltd.</t>
+          <t>Kanvic Consulting Private Limited</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1315961</t>
+          <t>1313882</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315961</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313882</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Female Guest Relations Executive - Mid Term</t>
+          <t>Customer Service</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Kandy, Sri Lanka</t>
+          <t>Bảo Yên, Thanh Thủy, Phú Thọ, Việt Nam</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -17676,39 +17676,39 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>40 applicants</t>
+          <t>260 applicants</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Canora Hotels (pvt) Ltd Grand Kandyan Hotel</t>
+          <t>LYNN TIMES HOTELS &amp; RESORTS</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1315189</t>
+          <t>1313813</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1315189</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313813</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Associate Consultant Internship</t>
+          <t>Receptionist</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India</t>
+          <t>Bảo Yên, Thanh Thủy, Phú Thọ, Việt Nam</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -17718,39 +17718,39 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>10 applicants</t>
+          <t>193 applicants</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>3 - 6 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Kanvic Consulting Private Limited</t>
+          <t>LYNN TIMES HOTELS &amp; RESORTS</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1313882</t>
+          <t>1313793</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313882</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313793</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>IT Sales Executive</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Bảo Yên, Thanh Thủy, Phú Thọ, Việt Nam</t>
+          <t>Kim Chung, Hoài Đức, Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>258 applicants</t>
+          <t>156 applicants</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -17770,29 +17770,29 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>LYNN TIMES HOTELS &amp; RESORTS</t>
+          <t>MOHA SOFTWARE JOINT STOCK COMPANY</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1313813</t>
+          <t>1313206</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313813</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313206</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Receptionist</t>
+          <t>Digital Media Strategist</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Bảo Yên, Thanh Thủy, Phú Thọ, Việt Nam</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>192 applicants</t>
+          <t>68 applicants</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -17812,29 +17812,29 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>LYNN TIMES HOTELS &amp; RESORTS</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1313793</t>
+          <t>1313204</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313793</t>
+          <t>https://aiesec.org/opportunity/global-talent/1313204</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>IT Sales Executive</t>
+          <t>Digital Content Creator</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Kim Chung, Hoài Đức, Hà Nội, Việt Nam</t>
+          <t>Colombo, Sri Lanka</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>156 applicants</t>
+          <t>44 applicants</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -17854,29 +17854,29 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>MOHA SOFTWARE JOINT STOCK COMPANY</t>
+          <t>Brand Corridor (Pvt) Ltd</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1313206</t>
+          <t>1308897</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313206</t>
+          <t>https://aiesec.org/opportunity/global-talent/1308897</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Digital Media Strategist</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Bursa, Türkiye</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -17886,39 +17886,39 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>68 applicants</t>
+          <t>98 applicants</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>İNOPLAST PLASTİK ENJEKSİYON KALIP</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1313204</t>
+          <t>1307244</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1313204</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Digital Content Creator</t>
+          <t>Robotics &amp; Automation</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Colombo, Sri Lanka</t>
+          <t>Ghaziabad, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>44 applicants</t>
+          <t>27 applicants</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -17938,29 +17938,29 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Brand Corridor (Pvt) Ltd</t>
+          <t>Kiet group of Institutions</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1308897</t>
+          <t>1307242</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1308897</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Automotive Mechatronics</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Bursa, Türkiye</t>
+          <t>Ghaziabad, India</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -17970,39 +17970,39 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>98 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>İNOPLAST PLASTİK ENJEKSİYON KALIP</t>
+          <t>KIET group of institutions</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1307244</t>
+          <t>1307150</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307244</t>
+          <t>https://aiesec.org/opportunity/global-talent/1307150</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Robotics &amp; Automation</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Ghaziabad, Uttar Pradesh, India</t>
+          <t>Gaziantep, Türkiye</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -18012,39 +18012,39 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>27 applicants</t>
+          <t>127 applicants</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Kiet group of Institutions</t>
+          <t>Göymen Makarna</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1307242</t>
+          <t>1303857</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307242</t>
+          <t>https://aiesec.org/opportunity/global-talent/1303857</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Automotive Mechatronics</t>
+          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Ghaziabad, India</t>
+          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -18054,39 +18054,39 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>47 applicants</t>
+          <t>177 applicants</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>KIET group of institutions</t>
+          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1307150</t>
+          <t>1303853</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1307150</t>
+          <t>https://aiesec.org/opportunity/global-talent/1303853</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Gaziantep, Türkiye</t>
+          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>127 applicants</t>
+          <t>146 applicants</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -18106,29 +18106,29 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Göymen Makarna</t>
+          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1303857</t>
+          <t>1301470</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1303857</t>
+          <t>https://aiesec.org/opportunity/global-talent/1301470</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
+          <t>Operation Specialist in İstanbul</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
+          <t>Fatih, Türkiye</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>176 applicants</t>
+          <t>169 applicants</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -18148,29 +18148,29 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>Esenyel&amp;Partners Lawyers/Consultants</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1303853</t>
+          <t>1299853</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1303853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1299853</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>MARKETING &amp; SALES / ABC TEKSTİL</t>
+          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Pınarkent, 20180 Pamukkale/Denizli, Türkiye</t>
+          <t>Porto Alegre, RS, Brasil</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -18180,39 +18180,39 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>145 applicants</t>
+          <t>167 applicants</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>6 - 18 Months</t>
+          <t>9 - 12 Weeks</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>ABC TEKSTİL SANAYİ VE TİCARET ANONİM ŞİRKETİ</t>
+          <t>ESCOLA GIORDANO BRUNO LTDA</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1301470</t>
+          <t>1296387</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1301470</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296387</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Operation Specialist in İstanbul</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Fatih, Türkiye</t>
+          <t>Şehitkamil, Türkiye</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>169 applicants</t>
+          <t>78 applicants</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -18232,29 +18232,29 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Esenyel&amp;Partners Lawyers/Consultants</t>
+          <t>Big Brands Dış Ticaret Limited Şirketi</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1299853</t>
+          <t>1296051</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1299853</t>
+          <t>https://aiesec.org/opportunity/global-talent/1296051</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>[Impact Porto Alegre] - Social Media Intern – Intercultural Engagement Program</t>
+          <t>Sales Support Intern</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Porto Alegre, RS, Brasil</t>
+          <t>Panamá, Panama</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -18264,39 +18264,39 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>167 applicants</t>
+          <t>85 applicants</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>9 - 12 Weeks</t>
+          <t>6 - 18 Months</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>ESCOLA GIORDANO BRUNO LTDA</t>
+          <t>Samsung Electronics Latinoamerica SELA Panama</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1296387</t>
+          <t>1293928</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1296387</t>
+          <t>https://aiesec.org/opportunity/global-talent/1293928</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Şehitkamil, Türkiye</t>
+          <t>Odunpazarı, Türkiye</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>78 applicants</t>
+          <t>212 applicants</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -18316,29 +18316,29 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Big Brands Dış Ticaret Limited Şirketi</t>
+          <t>API Prime Yazılım Teknolojileri</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1293928</t>
+          <t>1289379</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1293928</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289379</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Medical Advisor Portuguese Speaker</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Odunpazarı, Türkiye</t>
+          <t>İstanbul, Türkiye</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>212 applicants</t>
+          <t>139 applicants</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -18358,24 +18358,24 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>API Prime Yazılım Teknolojileri</t>
+          <t>International Plus</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1289379</t>
+          <t>1289378</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289379</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Medical Advisor Portuguese Speaker</t>
+          <t>Medical Advisor (Spanish Speaker)</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>139 applicants</t>
+          <t>154 applicants</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -18407,17 +18407,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1289378</t>
+          <t>1289377</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289378</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Medical Advisor (Spanish Speaker)</t>
+          <t>Medical Advisor (Italian Speaker)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>154 applicants</t>
+          <t>47 applicants</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -18449,17 +18449,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1289377</t>
+          <t>1289375</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289377</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289375</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Medical Advisor (Italian Speaker)</t>
+          <t>Medical Advisor (German Speaker)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>47 applicants</t>
+          <t>48 applicants</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -18491,22 +18491,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1289375</t>
+          <t>1289255</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289375</t>
+          <t>https://aiesec.org/opportunity/global-talent/1289255</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Medical Advisor (German Speaker)</t>
+          <t>Medical Advisor French Speaker</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>İstanbul, Türkiye</t>
+          <t>Fatih, Türkiye</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>48 applicants</t>
+          <t>705 applicants</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -18525,48 +18525,6 @@
         </is>
       </c>
       <c r="H431" t="inlineStr">
-        <is>
-          <t>International Plus</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>1289255</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>https://aiesec.org/opportunity/global-talent/1289255</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>Medical Advisor French Speaker</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>Fatih, Türkiye</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>703 applicants</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>6 - 18 Months</t>
-        </is>
-      </c>
-      <c r="H432" t="inlineStr">
         <is>
           <t>International Plus</t>
         </is>
